--- a/marketing/무진사 데이터 컨텐츠마케팅 프로세스_260317.xlsx
+++ b/marketing/무진사 데이터 컨텐츠마케팅 프로세스_260317.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="24810" windowHeight="11430" firstSheet="5"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11460" firstSheet="5" activeTab="2"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="1. 문제정의" sheetId="1" r:id="rId4"/>
@@ -21,25 +21,154 @@
     <x:sheet name="7. RFM(optional)" sheetId="7" r:id="rId10"/>
     <x:sheet name="8. STP" sheetId="8" r:id="rId11"/>
     <x:sheet name="9. Persona" sheetId="9" r:id="rId12"/>
-    <x:sheet name="8. Ads Campaign" sheetId="10" r:id="rId13"/>
+    <x:sheet name="10. SWOT" sheetId="10" r:id="rId13"/>
+    <x:sheet name="11. NPD" sheetId="11" r:id="rId14"/>
   </x:sheets>
   <x:calcPr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" mc:Ignorable="hs" hs:hclCalcId="904"/>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="193">
-  <x:si>
-    <x:t xml:space="preserve">- 위에서 발견한 고객 성향에 따른 자사 경쟁력 &amp; 개선할 부분까지 나열 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>30일 이내 구매한 한달에 3회 이상 구매한, 총 18만원 이상을 지불한 금액</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 인구통계학적 질문/ 업계 및 브랜드 관심도/ 구매행동기반 / 컨텐츠 소비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 힉의 법칙 =&gt; 사람은 너무 많은 성택지를 주먼 오히려 선택을 힘들어한다.</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="289">
+  <x:si>
+    <x:t>3) Positioning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-패션 관심도 매우 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-SNS컨텐츠 소비를 많이하는 고객</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">- </x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; User id &gt; Avg order value</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1) 브랜드 및 상품 정체성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 필요에 의해서 단발성 구매</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KR</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+        <x:b val="1"/>
+      </x:rPr>
+      <x:t xml:space="preserve">-Objective </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t>(미시적목표): 패션에 관심을 가지고 있는 일반 사용자들이 우리 홈페이지(브랜드)에 안정적,지속적 유입</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>https://docs.google.com/forms/d/e/1FAIpQLSdXs6_v4ofkPICNDYSSmO6x1yRrk0WiNohaSWJVGXX6soOiBQ/viewform</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 페이지 체류시간 매우 짧음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-충동구매가능</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 가격보다 상품,브랜드 ,플랫폼 이미지 중요</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>8. STP</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>Activation(사용자 경험 및 실행)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>무진사:</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">구조 개선이 필요한 단계 : </x:t>
+  </x:si>
+  <x:si>
+    <x:t>(*Before VS After: 채널별 유입 비중 -&gt; Paid Social  / Organic Search/ Organic Social )</x:t>
+  </x:si>
+  <x:si>
+    <x:t>product = 실물 상품만 의미 X (플랫폼, 서비스, 교육, 컨텐츠 등)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 어느 방향을 향해 나아갈 것인가 = 고객 머리속에 우리는 어떤 이미지로 남고 싶은가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 목적에 따른 특정 아이템 빠르게 검색 후 구매</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-상품 구매후 만족시, 재구매 가능성이 매우 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-가격대비 만족도 높아야하는 고객 = 가성비 추구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt;CRM (Customer Relationship Management). Email 발송 후클릭률 8% 이상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(*CTR 데이터 수집,분석 : page_view 이벤트 / click_purchase_button 이벤트)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1순위: Revenue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3) FGI: Focus Croup Interview</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- RFM분석 대상 -&gt; 구매경험 1,050명 대상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 광고 캠페인을 활용한 유입비중 40% 이상 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AI 활용 기술적 업그레이드 -&gt; 맞춤 추천 기술 도입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 참여도 획득 보고서를 통해서 평슌 세션 확인 가능</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; SNS 및 포털사이트를 통한 외부유입 15% 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 지난 3개월 시간 무진사 홈페이지(브랜드) 실적 가정</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">-우리 홈페이지(브랜드)를 통해서 매출, 이익이 발생 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt;평균세션(Avg Session) 시간 2분 이상 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상품 상세페이지 내 리뷰정보 요약 노출, 패션 코디 제안</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 추천 링크를 활용한 구매 발생 비율 10% 이상 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-(오픈마켓, 종합몰, 편집샵, 독립목,소셜커머스 등</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">                               </x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 계속적으로 트랜드한 브랜드, 아이템 추종(유목민)</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -56,91 +185,13 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">-우리 홈페이지(브랜드)를 통해서 매출, 이익이 발생 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt;평균세션(Avg Session) 시간 2분 이상 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 광고 캠페인을 활용한 유입비중 40% 이상 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3) FGI: Focus Croup Interview</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 참여도 획득 보고서를 통해서 평슌 세션 확인 가능</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 추천 링크를 활용한 구매 발생 비율 10% 이상 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상품 상세페이지 내 리뷰정보 요약 노출, 패션 코디 제안</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AI 활용 기술적 업그레이드 -&gt; 맞춤 추천 기술 도입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; SNS 및 포털사이트를 통한 외부유입 15% 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-(오픈마켓, 종합몰, 편집샵, 독립목,소셜커머스 등</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- RFM분석 대상 -&gt; 구매경험 1,050명 대상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 지난 3개월 시간 무진사 홈페이지(브랜드) 실적 가정</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">                               </x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 계속적으로 트랜드한 브랜드, 아이템 추종(유목민)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt;GA4,GTM 등의 트래픽 수집, 분석 툴 데이터 취합 비교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문제 3: 유입 존재, 구매전환률 보통, 재방문 거의 전무/ 우리 홈페이지(브랜드) 기술적, 시각적,기능적 차별화 포인트 부재</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; SNS 등 Owned Media를 통한 유입비중 10% 이상 증가 &amp; 우리 홈페이지(브랜드) 접속시 CTR 3% 이상 기록</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-Objective (미지적목표): 패션에 관심을 가지고 있는 일반 사용자들이 우리 홈페이지(브랜드)에 안정적,지속적 유입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 상품 목록페이지 (PLP= Product List Page) -&gt; 상품 상세페이지 이동할때 발생하는 클릭률 35% 이상 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2) Field Research: 해당 업종 관계자, 전문가 섭외, 인터뷰</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 스크롤 깊이(Scroll Depth) 50% 이상 도달률 40% 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt;GTM활용 10,25,50,75,90  세부적인 스크롤 깊이 단위까지 확인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- Objective (미시적 목표) : 사용자가 자발적으로 Earned Media에 가서 상품 및 서비스를 공유, 광고 비율 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 동질집단 분석 보고서(cohort=동질집단). 1월 2주차 프로모션 행사를 통해서 유입된 사용자들의 7일내 재방문율 25% 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> -Objective (미시적 목표): 사용자가 및 방문자가 실제 상품을 구매할 수 있는 직.간접적인 행위의 지표가 상승</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 앞에서 수집한 고객정보를 기반으로 최우선 고객집단(그룹)을 정의하는데 있어서 단순 경험, 의견을 바탕으로 결정 X</x:t>
-  </x:si>
-  <x:si>
     <x:t>- 신규 스타트업 비즈니스 모델 적용X// 이미 비즈니스가 운영되고 있는 경우에 한함</x:t>
   </x:si>
   <x:si>
+    <x:t>문제 2: 유입은 발생, 구매전환률이 낮음/ 우리 홈페이지(브랜드) 신뢰도 낮음</x:t>
+  </x:si>
+  <x:si>
     <x:t>-가성비 있는 상품을 기준으로 빠른 구매결정 &amp; 검색 비교를 선호하는 성향 고객</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문제 2: 유입은 발생, 구매전환률이 낮음/ 우리 홈페이지(브랜드) 신뢰도 낮음</x:t>
   </x:si>
   <x:si>
     <x:t>-경쟁사 역시, 위에서 분석한 고객 성향에 따른 차별점= 특징 &amp; 개선할 부분 유츄+ 정보수집</x:t>
@@ -163,13 +214,58 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>(*CTR 데이터 수집,분석 : page_view 이벤트 / click_purchase_button 이벤트)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt;CRM (Customer Relationship Management). Email 발송 후클릭률 8% 이상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(*Before VS After: 채널별 유입 비중 -&gt; Paid Social  / Organic Search/ Organic Social )</x:t>
+    <x:t>- Objective (미시적 목표) : 사용자가 자발적으로 Earned Media에 가서 상품 및 서비스를 공유, 광고 비율 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 동질집단 분석 보고서(cohort=동질집단). 1월 2주차 프로모션 행사를 통해서 유입된 사용자들의 7일내 재방문율 25% 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문제 3: 유입 존재, 구매전환률 보통, 재방문 거의 전무/ 우리 홈페이지(브랜드) 기술적, 시각적,기능적 차별화 포인트 부재</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; SNS 등 Owned Media를 통한 유입비중 10% 이상 증가 &amp; 우리 홈페이지(브랜드) 접속시 CTR 3% 이상 기록</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 상품 목록페이지 (PLP= Product List Page) -&gt; 상품 상세페이지 이동할때 발생하는 클릭률 35% 이상 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 상세페이지 및 컨텐츠 내 기존 소비자 리뷰만족도를 어필할 수 있는 컨텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 이전에 온라인으로 출근룩 구매 -&gt; 생각보다 저품질, 소재,주변반응 별로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) Field Research: 해당 업종 관계자, 전문가 섭외, 인터뷰</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; 주간 구매 사용자수(Weekly Purchasing Users) 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">- 위에서 발견한 고객 성향에 따른 자사 경쟁력 &amp; 개선할 부분까지 나열 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 스크롤 깊이(Scroll Depth) 50% 이상 도달률 40% 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; STP전략의 Positioning에서 도출된 방향성과 정체성 반드시 일치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 인구통계학적 질문/ 업계 및 브랜드 관심도/ 구매행동기반 / 컨텐츠 소비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 힉의 법칙 =&gt; 사람은 너무 많은 성택지를 주먼 오히려 선택을 힘들어한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt;GTM활용 10,25,50,75,90  세부적인 스크롤 깊이 단위까지 확인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30일 이내 구매한 한달에 3회 이상 구매한, 총 18만원 이상을 지불한 금액</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 1개의 의류상춤 +화장품+악세사리까지 토탈 코디네이션 &amp; 출근룩 큐레이션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-구매하기 전까지 많은 정보 수집, 비교 -&gt; 구매가지 걸리는 시간 많음</x:t>
   </x:si>
   <x:si>
     <x:t>&gt; UTM url 생성 후 eamil 발송 시, 삽입 -&gt; 해당 url을 통해서 유입한 사용자수 등을 확인</x:t>
@@ -178,6 +274,309 @@
     <x:t xml:space="preserve"> -Objective (미시적 목표): 구매 가능성이 높은 기존 구매 사용자의 재방문 효과적으로 유도</x:t>
   </x:si>
   <x:si>
+    <x:t>- 앞에서 수집한 고객정보를 기반으로 최우선 고객집단(그룹)을 정의하는데 있어서 단순 경험, 의견을 바탕으로 결정 X</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> -Objective (미시적 목표): 사용자가 및 방문자가 실제 상품을 구매할 수 있는 직.간접적인 행위의 지표가 상승</x:t>
+  </x:si>
+  <x:si>
+    <x:t>차선고객 = 성장가능 고객</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30일 이내-&gt; High</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3) Competitor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 평균 객단가 22만원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 회원가입:3,200명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 구매자: 1,050명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 사용자가 관심상품으로 선택한 상품을 재조회하는 재조회률 30% 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 포털 사이트 등을 통한 자연 검색 유입 비중 20% 이상 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(*세션-&gt; 30분 시간을 기준으로 사용자의 액션행위 체크 단위)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 상품 목록페이지 기준, 상품 상세페이지 이동 유입경로 분석 보고서</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(*우리 홈페이지에 유입되는 신규사용자 -New Visitor 수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 전자상거래 이벤트 -&gt;purchase conversion rate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문제1: 실제 유입이 저조/ 우리 홈페이지(브랜드 ) 인지도 낮음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1) Desk Research: 오픈 서베이, 메조미디너, 나스미디어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 공유하기 버튼 클릭횟수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. FUNNEL 구조 설계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-Key Results</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4) Form활용 리서치</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1) 유입 -&gt;  첫인상 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt;KPI(핵심성과지표)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>개선 (solution)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비교하기 쉽게 보고싶어!</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">290명: L/L/L </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">280명 : M/L/L </x:t>
+  </x:si>
+  <x:si>
+    <x:t>160명: RFM H/H/H</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-첫 구매 만족도 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-할인 시즌만 겨냥해서 구매</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 브랜드 충성도 매우 낮음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8만원 이하 -&gt;Lovw</x:t>
+  </x:si>
+  <x:si>
+    <x:t>90일 이상 -&gt; Low</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5) 이탈 또는 재방문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- KeyResults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5. Journey map</x:t>
+  </x:si>
+  <x:si>
+    <x:t>320명 : H/M/M</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이탈/재방문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 문제정의</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유입/첫인상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상세검토</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고객생각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고객행동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7. RFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구매결정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61이상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>관심 + 불안</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mid(2점)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미완성 기억</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8만원 이하</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8~18만원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31~60일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>관심 + 피로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구매횟수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18만원 이상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>총 구매금액</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최우선 고객</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Low(1점)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- KPI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recency</x:t>
+  </x:si>
+  <x:si>
+    <x:t>탐색/비교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3) Competitior``</x:t>
+  </x:si>
+  <x:si>
+    <x:t>혜택, 신뢰, 시의성, 긴급성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Acquisition (유입단계)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구체적이며 동종업계 -&gt;경쟁사 나열</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RFM Score 기준 테이블</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 채널별 경쟁사, 아이템별 경쟁자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여러상품 클릭, 가격/리뷰 비교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불편한점 (pain point)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설득할 수 있을만한 요소 부족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt;월 신규 방문자 5,000명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4. User Reaserch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지금 구매하는것이 현명한 선택일까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2회</x:t>
+  </x:si>
+  <x:si>
+    <x:t>`</x:t>
+  </x:si>
+  <x:si>
+    <x:t>,</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> </x:t>
+  </x:si>
+  <x:si>
+    <x:t>단계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호기심</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1회</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Segment 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4) 구매의사결정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3회 이상 구매</x:t>
+  </x:si>
+  <x:si>
+    <x:t>재방문할 명문 부족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1) Customer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신뢰할만한 정보 부족</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">&gt; 재방문 세션수 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) Company</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Frequency</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 리뷰 작성률 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Segment 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Segment 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Recency </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Segment 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1회 -&gt; Low</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2회 -&gt;Mid</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30일 이내 구매</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Monetary</x:t>
+  </x:si>
+  <x:si>
+    <x:t>High (3점)</x:t>
+  </x:si>
+  <x:si>
     <x:t>내 취향에 맞는 사이트인가?</x:t>
   </x:si>
   <x:si>
@@ -193,256 +592,64 @@
     <x:t>&gt; 구매전환율 2.5% 달성</x:t>
   </x:si>
   <x:si>
+    <x:t>3) 상세검토 -&gt; 확신형성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정보 구조 미비, 정보 부족</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">2) 탐색 -&gt; 비교 </x:t>
   </x:si>
   <x:si>
-    <x:t>3) 상세검토 -&gt; 확신형성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정보 구조 미비, 정보 부족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 공유하기 버튼 클릭횟수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Retention(재방문)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3. FUNNEL 구조 설계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-Key Results</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-&gt;KPI(핵심성과지표)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Revenue(매출향상)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4) Form활용 리서치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- KeyResults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>개선 (solution)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5) 이탈 또는 재방문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5. Journey map</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1) 유입 -&gt;  첫인상 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>비교하기 쉽게 보고싶어!</x:t>
+    <x:t>60일 이내 -&gt; mid</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 25~34세 직장인 68%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 출근룩 카테고리 구매 비중 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>=&gt; 차선고객이 최우선 고객에 비해 너무 많은 경우 그 부분이 FUNNEL구조에서의 개선점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 목록 페이지 내 클릭 이벤트 세팅 (목록페이지 유입대비, 해당버튼 클릭 수 =&gt; 클릴률</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 상품상세페이지 (PDP= Product Detail Page) 조회율 60%이상 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> -Objective (미시적 목표): 실질적인 상품 구매 전활융 향상 및 매출 이익 증대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 브랜드 인지도 : 정석 시간 + 비용 꾸준한 투자 //SNS활용 재치,  개성 콘텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt;GA4,GTM 등의 트래픽 수집, 분석 툴 데이터 취합 비교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; cart conversion rate(장바구니 전환율)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 자사 경쟁력(상품, 플랫폼, 서비스, 기술 등) 기반 분석</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필터 및 검색기능 강화, 상품정보 큐레이션 UI/UX 개선</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; GA4 &gt; 데이터 스트림 코드를 통해서 삽압 vs 구글</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-트랜디함을 좋아하는 고객들로 추정, 우연하게 브랜드 노출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>찜, 쿠폰, CRM, 리타게팅 마케팅을 통해서 재방문율 증가</x:t>
   </x:si>
   <x:si>
     <x:t>장바구니, 구매 고민</x:t>
   </x:si>
   <x:si>
     <x:t>가장 높은 피로감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4. User Reaserch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Acquisition (유입단계)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt;월 신규 방문자 5,000명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여러상품 클릭, 가격/리뷰 비교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3) Competitior``</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8만원 이하 -&gt;Lovw</x:t>
-  </x:si>
-  <x:si>
-    <x:t>320명 : H/M/M</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">290명: L/L/L </x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">280명 : M/L/L </x:t>
-  </x:si>
-  <x:si>
-    <x:t>160명: RFM H/H/H</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-첫 구매 만족도 높음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-할인 시즌만 겨냥해서 구매</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 브랜드 충성도 매우 낮음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 평균 객단가 22만원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>차선고객 = 성장가능 고객</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 회원가입:3,200명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30일 이내-&gt; High</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3) Competitor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 구매자: 1,050명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>60일 이내 -&gt; mid</x:t>
-  </x:si>
-  <x:si>
-    <x:t>90일 이상 -&gt; Low</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3회이상 -&gt; High</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18만원 이상 -&gt;High</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8~18만원 -&gt; Mid</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(*세션-&gt; 30분 시간을 기준으로 사용자의 액션행위 체크 단위)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 상품 목록페이지 기준, 상품 상세페이지 이동 유입경로 분석 보고서</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 포털 사이트 등을 통한 자연 검색 유입 비중 20% 이상 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문제1: 실제 유입이 저조/ 우리 홈페이지(브랜드 ) 인지도 낮음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 전자상거래 이벤트 -&gt;purchase conversion rate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(*우리 홈페이지에 유입되는 신규사용자 -New Visitor 수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1) Desk Research: 오픈 서베이, 메조미디너, 나스미디어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-&gt; 주간 구매 사용자수(Weekly Purchasing Users)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 사용자가 관심상품으로 선택한 상품을 재조회하는 재조회률 30% 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2회</x:t>
-  </x:si>
-  <x:si>
-    <x:t>단계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>,</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> </x:t>
-  </x:si>
-  <x:si>
-    <x:t>호기심</x:t>
-  </x:si>
-  <x:si>
-    <x:t>`</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1회</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지금 구매하는것이 현명한 선택일까?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>혜택, 신뢰, 시의성, 긴급성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설득할 수 있을만한 요소 부족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구체적이며 동종업계 -&gt;경쟁사 나열</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RFM Score 기준 테이블</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 채널별 경쟁사, 아이템별 경쟁자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불편한점 (pain point)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Monetary</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2회 -&gt;Mid</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Segment 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1회 -&gt; Low</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Recency </x:t>
-  </x:si>
-  <x:si>
-    <x:t>Frequency</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 리뷰 작성률 높음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30일 이내 구매</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Segment 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Segment 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>High (3점)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3회 이상 구매</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Segment 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신뢰할만한 정보 부족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>재방문할 명문 부족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2) Company</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -459,166 +666,96 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>&gt; 25~34세 직장인 68%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 출근룩 카테고리 구매 비중 높음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 상품상세페이지 (PDP= Product Detail Page) 조회율 60%이상 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 목록 페이지 내 클릭 이벤트 세팅 (목록페이지 유입대비, 해당버튼 클릭 수 =&gt; 클릴률</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> -Objective (미시적 목표): 실질적인 상품 구매 전활융 향상 및 매출 이익 증대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>=&gt; 차선고객이 최우선 고객에 비해 너무 많은 경우 그 부분이 FUNNEL구조에서의 개선점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1) Customer</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">&gt; 재방문 세션수 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>4) 구매의사결정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 문제정의</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유입/첫인상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상세검토</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고객생각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이탈/재방문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>총 구매금액</x:t>
-  </x:si>
-  <x:si>
-    <x:t>관심 + 피로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>탐색/비교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- KPI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>관심 + 불안</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고객행동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7. RFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최우선 고객</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구매횟수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mid(2점)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recency</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구매결정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미완성 기억</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Low(1점)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18만원 이상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31~60일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8만원 이하</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61이상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8~18만원</x:t>
+    <x:r>
+      <x:t>Revenue(매출향상)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>8~18만원 -&gt; Mid</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18만원 이상 -&gt;High</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3회이상 -&gt; High</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+          <x:rPr hs:extension="1">
+            <x:rFont val="맑은 고딕"/>
+            <x:sz val="15"/>
+            <x:color rgb="ff000000"/>
+            <hs:size val="100"/>
+            <hs:ratio val="100"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:rPr>
+        </mc:Choice>
+        <mc:Fallback>
+          <x:rPr>
+            <x:rFont val="맑은 고딕"/>
+            <x:sz val="15"/>
+            <x:color rgb="ff000000"/>
+          </x:rPr>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <x:t>1) Segmentation</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t xml:space="preserve">    =&gt; 우리 고객의 유형을 빠르게 파악한 후 그에 맞는 전략 실행</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>- 전략적으로 타겟(과녁) 고객을 선정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 장바구지-&gt; 구매 전활율 전호나 35%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 리뷰작성빈도 및 작성률 (SQL)</x:t>
   </x:si>
   <x:si>
     <x:t>2. NSM 정의: 거시적 목표 =큰목표</x:t>
   </x:si>
   <x:si>
-    <x:t>&gt; 리뷰작성빈도 및 작성률 (SQL)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Referral (주변추천, 바이럴 단계)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Activation(사용자 경험 및 실행)</x:t>
+    <x:t>보류 후 종료 또는 재방문 구매 의사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상세페이지, 리뷰, 포토 혹은 동영상 조회</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 두번째 재구매로 이어지는 비중이 약함</x:t>
   </x:si>
   <x:si>
     <x:t>&gt; 후기 작성률, 기존 대비 10% 증가</x:t>
   </x:si>
   <x:si>
-    <x:t>- 두번째 재구매로 이어지는 비중이 약함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 장바구지-&gt; 구매 전활율 전호나 35%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보류 후 종료 또는 재방문 구매 의사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상세페이지, 리뷰, 포토 혹은 동영상 조회</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; cart conversion rate(장바구니 전환율)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필터 및 검색기능 강화, 상품정보 큐레이션 UI/UX 개선</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 자사 경쟁력(상품, 플랫폼, 서비스, 기술 등) 기반 분석</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; GA4 &gt; 데이터 스트림 코드를 통해서 삽압 vs 구글</x:t>
-  </x:si>
-  <x:si>
-    <x:t>찜, 쿠폰, CRM, 리타게팅 마케팅을 통해서 재방문율 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-트랜디함을 좋아하는 고객들로 추정, 우연하게 브랜드 노출</x:t>
+    <x:t>&gt; 상품 공유하기 버튼 클릭율 3% 이상 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; Returning User = Visiors</x:t>
+  </x:si>
+  <x:si>
+    <x:t>처음 구매를 하려고 하는데, 실패하지 않을까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- SNS 광고 통해서 유입한 고객 (대부분)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; Google Form / Naver Form</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-리뷰가 존재x, 할인 비시즌 거의 활동 전무</x:t>
   </x:si>
   <x:si>
     <x:t>&gt; 우리 홈페이지의 인기상품군들의 구매비중 50%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; Google Form / Naver Form</x:t>
-  </x:si>
-  <x:si>
-    <x:t>처음 구매를 하려고 하는데, 실패하지 않을까?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- SNS 광고 통해서 유입한 고객 (대부분)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-리뷰가 존재x, 할인 비시즌 거의 활동 전무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 상품 공유하기 버튼 클릭율 3% 이상 증가</x:t>
   </x:si>
   <x:si>
     <x:t>다시는 마주하고 싶지 않다.
@@ -628,13 +765,7 @@
     <x:t>⇒ 방문을통해서 구매전환까지 매력도(설들력) 약함</x:t>
   </x:si>
   <x:si>
-    <x:t>&gt; User id &gt; Avg arder value</x:t>
-  </x:si>
-  <x:si>
     <x:t>&gt; 평균 주문 구매금액 7만원 유지(평균객단가)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; Returning User = Visiors</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -664,12 +795,335 @@
       <x:t>탐색 중심소비패턴</x:t>
     </x:r>
   </x:si>
+  <x:si>
+    <x:t>- 쇼핑성향 : 월평균 1~2회 온라인 의류쇼핑 진행 / 1회 구매시, 약 7만원/ 3개월 20만원 구매</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 4계절 존재 -&gt; 시즌 트랜드가 빠르게 흘러감</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>Retention(재방문)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>Referral (주변추천, 바이럴 단계)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>- 패션성향 : 출근룩, 데일리 캐주얼룩 중심/ 너무 튀는 스타일 부담 &amp; 세련됨 +무난함추구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>* 출근시 착용가능한 출근룩 고민많음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 리뷰/평점 확인 필수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; 확고한 1위 독점적 지위 확보</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; K-패션, 스타일 관심도 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>W- Weakness(약점)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>2) 장기적인 비전  제시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-특히 신상품 출시 많은 관심</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 충성도가 매우 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-특정 브랜드의 충성도보다 본인만의 개성적인 스타일 중요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 브랜드 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 가격 민감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>* 상품 리뷰 의존도 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 직업: IT 기업 마케팅 매니저</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 컨텐츠 전략 :</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>2) Targeting</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>- 월소득 :350만원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 이름 : 김서연</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+        <x:b val="1"/>
+      </x:rPr>
+      <x:t>&gt; Segement C</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t xml:space="preserve"> (목적 구매형)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+        <x:b val="1"/>
+      </x:rPr>
+      <x:t>&gt;Segemet D(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t>감성추구 지향형)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+        <x:b val="1"/>
+      </x:rPr>
+      <x:t>&gt; Segmentation A(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t>트랜드 탐색, 검색 선호하는 유형)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>- 소비성향 : 합리적이고 가성비있는 소비 지향/ 가격대비 활용도 중요/ 브랜드 이름보다는 스타일링 및 코디 관심</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> &gt;Primary Target</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 나이 : 31세</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9. Persona</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- Pain Point:</x:t>
+  </x:si>
+  <x:si>
+    <x:t>* 가성비(가격 민감성) &amp; 품질 어느정도 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+          <x:rPr hs:extension="1">
+            <x:rFont val="맑은 고딕"/>
+            <x:sz val="11"/>
+            <x:color rgb="ffff0000"/>
+            <x:b val="1"/>
+            <hs:size val="100"/>
+            <hs:ratio val="100"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:rPr>
+        </mc:Choice>
+        <mc:Fallback>
+          <x:rPr>
+            <x:rFont val="맑은 고딕"/>
+            <x:sz val="11"/>
+            <x:color rgb="ffff0000"/>
+            <x:b val="1"/>
+          </x:rPr>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <x:t xml:space="preserve">&gt; Segment B </x:t>
+    </x:r>
+    <x:r>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+          <x:rPr hs:extension="1">
+            <x:rFont val="맑은 고딕"/>
+            <x:sz val="11"/>
+            <x:color rgb="ffff0000"/>
+            <hs:size val="100"/>
+            <hs:ratio val="100"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:rPr>
+        </mc:Choice>
+        <mc:Fallback>
+          <x:rPr>
+            <x:rFont val="맑은 고딕"/>
+            <x:sz val="11"/>
+            <x:color rgb="ffff0000"/>
+          </x:rPr>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <x:t>(합리적인 소비 선호 유형)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>- 컨텐츠 만족에 따른 구매전환율 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- Solution:</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 합리적 소비를 위한 상품비교가 익숙한 25-34 직장인 여성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; SKU 부족: 상품 다양성 부족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최종카드= WT전략: 약점을 개선해서 시장의 위협요소에 최대한 덜 노출시키겠다는 전략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 다양한 플랫폼 대비, 직장인 출근룩을 디테일하게 큐레이션하는 플랫폼, 서비스 부재</x:t>
+  </x:si>
+  <x:si>
+    <x:t>* 재방문 유입 확률 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>&gt;Secondary Target</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>- 트랜드 패션에 관심이 높은 2530 프리랜서 여성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 트랜드 민감, SNS검색 후 비교 및 자기개성 어필</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-구체적인 브랜드 혹은 상품 슬로건(Just do it, nothing is impossible)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 컨텐츠 기획 기본 방향 수립（광고 톤앤매너, 배경컬러, 웹사이트 메인베너, 상세페이지, CRM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11. NPD</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>T-Threat (위협)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 직장인을 위한 합리적인 데일리룩 큐레이션 쇼핑몰</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2순위: Retention</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>10. SWOT</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>O-Opportunity (기회)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 직장인 코디네이션 및 큐레이팅 최대한 어필될 수 있는 컨텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 성.비수기 존재</x:t>
+  </x:si>
+  <x:si>
+    <x:t>: 어떤 강점을 어필하고, 어떤 약점을 빠르게 보완할 것이며, 어떤 타이밍에 좋은 기회를 포착할 것인가, 최악의 리스크를 어떻게하면 피할 수 있을까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; 생존과 가장 밀접</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">&gt; 자사 자산을 스캔, 검색, 조회를 통해 인지 +리뷰 데이터 조회 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 기술력, 가격, 가성비, 컨텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; 2인자의 전략</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>S- Strength (강점)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>ST전략: 강점을 활용한 시장의 위협요소 방어전략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; New Product Development</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 가성비 : 원가 절감 // 대량생산</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 가격 경쟁 치열 - 출혈경쟁으로 인한 사업성 악화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SO전략: 강점을 활용한 시장의 기회요소를 포착하겠다는 전략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 중국산 값싼 브랜드,플랫폼의 국내 진출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; 약점대비 현재 업종의 활황기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Objective: 실질적 상품 구매전환률 향상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 국내 소비자 트랜드 &amp; 대중심리 민감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WO전략: 약점의 개선으로 시장의 기회요소를 최대한 활용하겠다는 전략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>*각 전략마다 3-5개 정도 수립</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">- 지금 당장 고객들이 원하는 니즈 파악 + 장기적인 방향? </x:t>
+  </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="13">
+  <x:fonts count="19">
     <x:font>
       <x:name val="맑은 고딕"/>
       <x:sz val="11"/>
@@ -716,13 +1170,17 @@
       <x:name val="Arial"/>
       <x:sz val="11"/>
       <x:color rgb="ff000000"/>
-      <x:b val="1"/>
+    </x:font>
+    <x:font>
+      <x:name val="Arial"/>
+      <x:sz val="12"/>
+      <x:color rgb="ff000000"/>
     </x:font>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:font hs:extension="1">
           <x:name val="Arial"/>
-          <x:sz val="11"/>
+          <x:sz val="18"/>
           <x:color rgb="ff000000"/>
           <hs:size val="100"/>
           <hs:ratio val="100"/>
@@ -733,36 +1191,11 @@
       <mc:Fallback>
         <x:font>
           <x:name val="Arial"/>
-          <x:sz val="11"/>
+          <x:sz val="18"/>
           <x:color rgb="ff000000"/>
         </x:font>
       </mc:Fallback>
     </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Arial"/>
-          <x:sz val="12"/>
-          <x:color rgb="ff000000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Arial"/>
-          <x:sz val="12"/>
-          <x:color rgb="ff000000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <x:font>
-      <x:name val="Arial"/>
-      <x:sz val="18"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:font hs:extension="1">
@@ -780,6 +1213,159 @@
           <x:name val="맑은 고딕"/>
           <x:sz val="14"/>
           <x:color rgb="ffff0000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="맑은 고딕"/>
+          <x:sz val="11"/>
+          <x:color rgb="ffff0000"/>
+          <x:b val="1"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="맑은 고딕"/>
+          <x:sz val="11"/>
+          <x:color rgb="ffff0000"/>
+          <x:b val="1"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Arial"/>
+          <x:sz val="11"/>
+          <x:color rgb="ffff0000"/>
+          <x:b val="1"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Arial"/>
+          <x:sz val="11"/>
+          <x:color rgb="ffff0000"/>
+          <x:b val="1"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="맑은 고딕"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff0000ff"/>
+          <x:u/>
+          <hs:underlineType val="1"/>
+          <hs:underlineShape val="solid"/>
+          <hs:underlineColor rgb="ff0000ff"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="맑은 고딕"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff0000ff"/>
+          <x:u/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="맑은 고딕"/>
+          <x:sz val="14"/>
+          <x:color rgb="ffff0000"/>
+          <x:b val="1"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="맑은 고딕"/>
+          <x:sz val="14"/>
+          <x:color rgb="ffff0000"/>
+          <x:b val="1"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="맑은 고딕"/>
+          <x:sz val="11"/>
+          <x:color rgb="ffff0000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="맑은 고딕"/>
+          <x:sz val="11"/>
+          <x:color rgb="ffff0000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="맑은 고딕"/>
+          <x:sz val="15"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="맑은 고딕"/>
+          <x:sz val="15"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="맑은 고딕"/>
+          <x:sz val="15"/>
+          <x:color rgb="ff000000"/>
+          <x:b val="1"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="맑은 고딕"/>
+          <x:sz val="15"/>
+          <x:color rgb="ff000000"/>
+          <x:b val="1"/>
         </x:font>
       </mc:Fallback>
     </mc:AlternateContent>
@@ -822,13 +1408,16 @@
       </x:bottom>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="1">
+  <x:cellStyleXfs count="2">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <x:cellXfs count="29">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -853,45 +1442,42 @@
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
-    </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+        <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center" wrapText="1"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+        <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center" wrapText="1"/>
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+        <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+        <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -949,8 +1535,47 @@
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
-  <x:cellStyles count="1">
+  <x:cellStyles count="2">
     <x:cellStyle name="표준" xfId="0" builtinId="0"/>
   </x:cellStyles>
   <x:dxfs count="12">
@@ -1618,47 +2243,258 @@
   <x:sheetData>
     <x:row r="8" spans="3:3">
       <x:c r="C8" t="s">
-        <x:v>141</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="3:3">
       <x:c r="C9" t="s">
-        <x:v>35</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:3">
       <x:c r="C11" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="3:3">
       <x:c r="C12" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="3:3">
       <x:c r="C13" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="3:3">
       <x:c r="C14" s="3" t="s">
-        <x:v>187</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104492" right="0.69999998807907104492" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet11"/>
+  <x:dimension ref="C6:Q34"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
+  <x:sheetData>
+    <x:row r="6" spans="3:3" ht="22.05000000000000071054">
+      <x:c r="C6" s="28" t="s">
+        <x:v>267</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="3:3">
+      <x:c r="C7" t="s">
+        <x:v>271</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="3:3">
+      <x:c r="C9" s="16" t="s">
+        <x:v>276</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="3:3">
+      <x:c r="C10" t="s">
+        <x:v>274</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="3:3">
+      <x:c r="C11" t="s">
+        <x:v>273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="15:17">
+      <x:c r="O12" s="19"/>
+      <x:c r="P12" s="19"/>
+      <x:c r="Q12" s="19"/>
+    </x:row>
+    <x:row r="13" spans="3:17">
+      <x:c r="C13" s="16" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="O13" s="19"/>
+      <x:c r="P13" s="19"/>
+      <x:c r="Q13" s="19"/>
+    </x:row>
+    <x:row r="14" spans="3:17">
+      <x:c r="C14" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="O14" s="19"/>
+      <x:c r="P14" s="19"/>
+      <x:c r="Q14" s="19"/>
+    </x:row>
+    <x:row r="15" spans="3:17">
+      <x:c r="C15" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="O15" s="19"/>
+      <x:c r="P15" s="19"/>
+      <x:c r="Q15" s="19"/>
+    </x:row>
+    <x:row r="16" spans="3:17">
+      <x:c r="C16" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="O16" s="19"/>
+      <x:c r="P16" s="19"/>
+      <x:c r="Q16" s="19"/>
+    </x:row>
+    <x:row r="17" spans="15:17">
+      <x:c r="O17" s="19"/>
+      <x:c r="P17" s="19"/>
+      <x:c r="Q17" s="19"/>
+    </x:row>
+    <x:row r="18" spans="3:17">
+      <x:c r="C18" s="16" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="O18" s="19"/>
+      <x:c r="P18" s="19"/>
+      <x:c r="Q18" s="19"/>
+    </x:row>
+    <x:row r="19" spans="3:17">
+      <x:c r="C19" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="O19" s="19"/>
+      <x:c r="P19" s="19"/>
+      <x:c r="Q19" s="19"/>
+    </x:row>
+    <x:row r="20" spans="3:17">
+      <x:c r="C20" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="O20" s="19"/>
+      <x:c r="P20" s="19"/>
+      <x:c r="Q20" s="19"/>
+    </x:row>
+    <x:row r="21" spans="15:17">
+      <x:c r="O21" s="19"/>
+      <x:c r="P21" s="19"/>
+      <x:c r="Q21" s="19"/>
+    </x:row>
+    <x:row r="22" spans="3:3">
+      <x:c r="C22" s="16" t="s">
+        <x:v>264</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="3:3">
+      <x:c r="C23" t="s">
+        <x:v>282</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="3:3">
+      <x:c r="C24" t="s">
+        <x:v>280</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="3:3">
+      <x:c r="C25" t="s">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="3:3">
+      <x:c r="C26" t="s">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="3:3">
+      <x:c r="C27" t="s">
+        <x:v>270</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="3:3">
+      <x:c r="C30" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="3:12">
+      <x:c r="C31" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="L31" s="21" t="s">
+        <x:v>226</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="3:12">
+      <x:c r="C32" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="L32" s="21" t="s">
+        <x:v>275</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="3:12">
+      <x:c r="C33" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="L33" s="21" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="3:12">
+      <x:c r="C34" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="L34" s="21" t="s">
+        <x:v>272</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet10"/>
-  <x:dimension ref="A1:A1"/>
+  <x:dimension ref="C3:C11"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
-  <x:sheetData/>
-  <x:pageMargins left="0.69999998807907104492" right="0.69999998807907104492" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:sheetData>
+    <x:row r="3" spans="3:3" ht="22.05000000000000071054">
+      <x:c r="C3" s="28" t="s">
+        <x:v>263</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="3:3">
+      <x:c r="C4" t="s">
+        <x:v>278</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="3:3">
+      <x:c r="C5" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="3:3">
+      <x:c r="C7" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="3:3">
+      <x:c r="C8" s="21" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="3:3">
+      <x:c r="C10" t="s">
+        <x:v>229</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="3:3">
+      <x:c r="C11" s="21" t="s">
+        <x:v>288</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
@@ -1671,17 +2507,17 @@
   <x:sheetData>
     <x:row r="8" spans="3:3">
       <x:c r="C8" t="s">
-        <x:v>165</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="3:3">
       <x:c r="C9" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:3">
       <x:c r="C10" s="2" t="s">
-        <x:v>96</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:3">
@@ -1694,7 +2530,7 @@
       <x:c r="C13" s="1"/>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104492" right="0.69999998807907104492" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
@@ -1702,317 +2538,338 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet3"/>
-  <x:dimension ref="C7:F70"/>
+  <x:dimension ref="C7:Q70"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
   <x:sheetData>
     <x:row r="7" spans="4:4">
       <x:c r="D7" t="s">
-        <x:v>52</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="4:4">
       <x:c r="D9" s="3" t="s">
-        <x:v>66</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:4">
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:4">
       <x:c r="C11" s="2"/>
       <x:c r="D11" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="3:5">
       <x:c r="C12" s="1"/>
       <x:c r="E12" t="s">
-        <x:v>67</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="3:5">
       <x:c r="C13" s="1"/>
       <x:c r="E13" t="s">
-        <x:v>7</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="3:5">
       <x:c r="C14" s="1"/>
       <x:c r="E14" t="s">
-        <x:v>91</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="5:5">
       <x:c r="E15" t="s">
-        <x:v>21</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="6:6">
       <x:c r="F16" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="6:6">
       <x:c r="F17" t="s">
-        <x:v>19</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="6:6">
       <x:c r="F18" t="s">
-        <x:v>94</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="6:6">
       <x:c r="F19" t="s">
-        <x:v>89</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="6:6">
       <x:c r="F20" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="6:6">
       <x:c r="F21" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="4:4">
-      <x:c r="D23" t="s">
-        <x:v>168</x:v>
+      <x:c r="D23" s="16" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="4:4">
       <x:c r="D24" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="4:4">
       <x:c r="D25" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="4:4">
       <x:c r="D26" t="s">
-        <x:v>134</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="4:4">
       <x:c r="D27" t="s">
-        <x:v>6</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="4:4">
       <x:c r="D28" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="4:4">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="4:16">
       <x:c r="D29" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="P29" s="19" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="5:16">
+      <x:c r="E30" s="4" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="P30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="5:16">
+      <x:c r="E31" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="P31" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="5:5">
-      <x:c r="E30" s="4" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="5:5">
-      <x:c r="E31" t="s">
-        <x:v>90</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="5:5">
+    <x:row r="32" spans="5:16">
       <x:c r="E32" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="5:5">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="P32" t="s">
+        <x:v>284</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="5:17">
       <x:c r="E33" t="s">
-        <x:v>135</x:v>
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="P33" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="Q33" s="21" t="s">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="5:5">
       <x:c r="E34" t="s">
-        <x:v>26</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="4:4">
-      <x:c r="D36" t="s">
-        <x:v>51</x:v>
+      <x:c r="D36" s="16" t="s">
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="4:4">
       <x:c r="D37" s="2" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="4:4">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="4:16">
       <x:c r="D38" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="P38" s="19" t="s">
+        <x:v>266</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="4:4">
       <x:c r="D39" t="s">
-        <x:v>28</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="4:4">
       <x:c r="D40" t="s">
-        <x:v>38</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="4:4">
       <x:c r="D41" t="s">
-        <x:v>45</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="4:4">
       <x:c r="D42" t="s">
-        <x:v>97</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="4:5">
       <x:c r="D43" t="s">
-        <x:v>103</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E43" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="5:5">
       <x:c r="E44" t="s">
-        <x:v>190</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="5:5">
       <x:c r="E45" t="s">
-        <x:v>139</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="5:5">
       <x:c r="E46" t="s">
-        <x:v>40</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="5:5">
       <x:c r="E47" t="s">
-        <x:v>177</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="4:4">
-      <x:c r="D49" t="s">
-        <x:v>55</x:v>
+      <x:c r="D49" s="16" t="s">
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="4:4">
       <x:c r="D50" s="2" t="s">
-        <x:v>136</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="4:4">
       <x:c r="D51" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="4:4">
       <x:c r="D52" t="s">
-        <x:v>46</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="4:4">
       <x:c r="D53" t="s">
-        <x:v>171</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="4:4">
       <x:c r="D54" t="s">
-        <x:v>189</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="4:4">
       <x:c r="D55" t="s">
-        <x:v>180</x:v>
+        <x:v>213</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="5:5">
       <x:c r="E56" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="5:5">
       <x:c r="E57" t="s">
-        <x:v>93</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="5:5">
       <x:c r="E58" t="s">
-        <x:v>174</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="5:5">
       <x:c r="E59" t="s">
-        <x:v>188</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="4:4" ht="17.14999999999999857891">
-      <x:c r="D61" s="5" t="s">
-        <x:v>167</x:v>
+      <x:c r="D61" s="17" t="s">
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="4:4" ht="17.14999999999999857891">
-      <x:c r="D62" s="7" t="s">
-        <x:v>27</x:v>
+      <x:c r="D62" s="6" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="5:5" ht="17.14999999999999857891">
-      <x:c r="E63" s="7" t="s">
-        <x:v>57</x:v>
+      <x:c r="E63" s="6" t="s">
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="5:5" ht="17.14999999999999857891">
-      <x:c r="E64" s="7" t="s">
-        <x:v>185</x:v>
+      <x:c r="E64" s="6" t="s">
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="5:5" ht="17.14999999999999857891">
-      <x:c r="E65" s="7" t="s">
-        <x:v>13</x:v>
+      <x:c r="E65" s="6" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="5:5" ht="17.14999999999999857891">
-      <x:c r="E66" s="7" t="s">
-        <x:v>169</x:v>
+      <x:c r="E66" s="6" t="s">
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="5:5" ht="17.14999999999999857891">
-      <x:c r="E67" s="7" t="s">
-        <x:v>10</x:v>
+      <x:c r="E67" s="6" t="s">
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="5:6" ht="18.55000000000000071054">
-      <x:c r="E68" s="8"/>
-      <x:c r="F68" s="6" t="s">
-        <x:v>149</x:v>
+      <x:c r="E68" s="7"/>
+      <x:c r="F68" s="5" t="s">
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="5:6" ht="18.55000000000000071054">
-      <x:c r="E69" s="8"/>
-      <x:c r="F69" s="7" t="s">
-        <x:v>50</x:v>
+      <x:c r="E69" s="7"/>
+      <x:c r="F69" s="6" t="s">
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="5:6" ht="18.55000000000000071054">
-      <x:c r="E70" s="8"/>
-      <x:c r="F70" s="7" t="s">
-        <x:v>166</x:v>
+      <x:c r="E70" s="7"/>
+      <x:c r="F70" s="6" t="s">
+        <x:v>201</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104492" right="0.69999998807907104492" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
@@ -2025,52 +2882,55 @@
   <x:sheetData>
     <x:row r="5" spans="5:5">
       <x:c r="E5" t="s">
-        <x:v>65</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="5:5">
       <x:c r="E6" t="s">
-        <x:v>95</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="5:5">
       <x:c r="E7" t="s">
-        <x:v>24</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="5:5">
       <x:c r="E8" t="s">
-        <x:v>8</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="4:5">
       <x:c r="D9" s="3"/>
       <x:c r="E9" t="s">
-        <x:v>56</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:5">
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
       <x:c r="E10" t="s">
-        <x:v>181</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:5">
       <x:c r="C11" s="2"/>
       <x:c r="D11" s="4"/>
       <x:c r="E11" t="s">
-        <x:v>2</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="3:5">
       <x:c r="C12" s="1"/>
       <x:c r="E12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="3:3">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="3:5">
       <x:c r="C13" s="1"/>
+      <x:c r="E13" s="18" t="s">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" spans="3:3">
       <x:c r="C14" s="1"/>
@@ -2112,7 +2972,10 @@
       <x:c r="D63" s="2"/>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104492" right="0.69999998807907104492" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:hyperlinks>
+    <x:hyperlink ref="E13:E13" r:id="rId1"/>
+  </x:hyperlinks>
+  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
@@ -2123,45 +2986,45 @@
   <x:dimension ref="C5:J63"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
-    <x:col min="5" max="5" width="10.75" customWidth="1"/>
-    <x:col min="6" max="6" width="23.125" bestFit="1" customWidth="1"/>
-    <x:col min="7" max="7" width="27" bestFit="1" customWidth="1"/>
-    <x:col min="8" max="8" width="11.75" bestFit="1" customWidth="1"/>
+    <x:col min="5" max="5" width="21.80078125" bestFit="1" customWidth="1"/>
+    <x:col min="6" max="6" width="59.14453125" bestFit="1" customWidth="1"/>
+    <x:col min="7" max="7" width="66.5" bestFit="1" customWidth="1"/>
+    <x:col min="8" max="8" width="25.5703125" bestFit="1" customWidth="1"/>
     <x:col min="9" max="9" width="45" bestFit="1" customWidth="1"/>
     <x:col min="10" max="10" width="88.375" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="5" spans="5:5">
       <x:c r="E5" t="s">
-        <x:v>60</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="5:5">
       <x:c r="E6" t="s">
-        <x:v>61</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="5:5">
       <x:c r="E7" t="s">
-        <x:v>47</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="5:5">
       <x:c r="E8" t="s">
-        <x:v>48</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="4:5">
       <x:c r="D9" s="3"/>
       <x:c r="E9" t="s">
-        <x:v>140</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:5">
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
       <x:c r="E10" t="s">
-        <x:v>59</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:4">
@@ -2176,123 +3039,123 @@
     </x:row>
     <x:row r="14" spans="3:10" ht="27.10000000000000142109">
       <x:c r="C14" s="1"/>
-      <x:c r="E14" s="9" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="F14" s="9" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="G14" s="9" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="H14" s="9" t="s">
+      <x:c r="E14" s="8" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="F14" s="8" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G14" s="8" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="H14" s="8" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="I14" s="8" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="J14" s="8" t="s">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="5:10" ht="53.39999999999999857891">
+      <x:c r="E15" s="8" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="I14" s="9" t="s">
+      <x:c r="F15" s="8" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="G15" s="8" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="H15" s="8" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="I15" s="8" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="J15" s="8" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="5:10" ht="53.39999999999999857891">
+      <x:c r="E16" s="8" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="F16" s="8" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G16" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H16" s="8" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="I16" s="8" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="J16" s="8" t="s">
+        <x:v>187</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="5:10" ht="79.70000000000000284217">
+      <x:c r="E17" s="8" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F17" s="8" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G17" s="8" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="H17" s="8" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="I17" s="8" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="J17" s="9" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="5:10" ht="79.70000000000000284217">
+      <x:c r="E18" s="8" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F18" s="8" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G18" s="8" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H18" s="8" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="I18" s="8" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="J18" s="8" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="5:10" ht="79.70000000000000284217">
+      <x:c r="E19" s="8" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F19" s="8" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G19" s="8" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="H19" s="8" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="J14" s="9" t="s">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="5:10" ht="53.39999999999999857891">
-      <x:c r="E15" s="9" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="F15" s="9" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G15" s="9" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H15" s="9" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="I15" s="9" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="J15" s="9" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="5:10" ht="53.39999999999999857891">
-      <x:c r="E16" s="9" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="F16" s="9" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G16" s="9" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="H16" s="9" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="I16" s="9" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="J16" s="9" t="s">
-        <x:v>175</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="5:10" ht="79.70000000000000284217">
-      <x:c r="E17" s="9" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="F17" s="9" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="G17" s="9" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="H17" s="9" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="I17" s="9" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="J17" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="5:10" ht="79.70000000000000284217">
-      <x:c r="E18" s="9" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="F18" s="9" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G18" s="9" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="H18" s="9" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="I18" s="9" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="J18" s="9" t="s">
-        <x:v>109</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="5:10" ht="79.70000000000000284217">
-      <x:c r="E19" s="9" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="F19" s="9" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="G19" s="9" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="H19" s="9" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="I19" s="9" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="J19" s="10" t="s">
-        <x:v>178</x:v>
+      <x:c r="I19" s="8" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="J19" s="9" t="s">
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="4:4">
@@ -2329,7 +3192,7 @@
       <x:c r="D63" s="2"/>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104492" right="0.69999998807907104492" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
@@ -2342,92 +3205,92 @@
   <x:sheetData>
     <x:row r="11" spans="4:4">
       <x:c r="D11" t="s">
-        <x:v>106</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="4:4">
       <x:c r="D12" t="s">
-        <x:v>138</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="4:4">
       <x:c r="D13" t="s">
-        <x:v>192</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="3:4">
       <x:c r="C14" t="s">
-        <x:v>100</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D14" t="s">
-        <x:v>36</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="4:4">
       <x:c r="D15" t="s">
-        <x:v>131</x:v>
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="4:4">
       <x:c r="D16" t="s">
-        <x:v>191</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="4:4">
       <x:c r="D17" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="4:4">
       <x:c r="D19" t="s">
-        <x:v>130</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="4:4">
       <x:c r="D20" s="2" t="s">
-        <x:v>176</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="4:4">
       <x:c r="D21" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="4:4">
       <x:c r="D23" t="s">
-        <x:v>82</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="4:4">
       <x:c r="D24" t="s">
-        <x:v>111</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="4:4">
       <x:c r="D25" s="2" t="s">
-        <x:v>113</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="4:9">
       <x:c r="D26" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I26" t="s">
-        <x:v>101</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="4:4">
       <x:c r="D27" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="4:4">
       <x:c r="D35" t="s">
-        <x:v>69</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104492" right="0.69999998807907104492" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
@@ -2444,307 +3307,307 @@
   </x:cols>
   <x:sheetData>
     <x:row r="9" spans="3:3" ht="20.64999999999999857891">
-      <x:c r="C9" s="11" t="s">
-        <x:v>152</x:v>
+      <x:c r="C9" s="10" t="s">
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:3">
       <x:c r="C10" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:3">
       <x:c r="C11" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="3:3">
       <x:c r="C12" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="3:3">
       <x:c r="C14" t="s">
-        <x:v>16</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="3:3">
       <x:c r="C15" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="3:3">
       <x:c r="C16" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="3:3">
       <x:c r="C17" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="3:3">
       <x:c r="C18" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="3:3">
-      <x:c r="C20" s="12" t="s">
-        <x:v>119</x:v>
+      <x:c r="C20" s="11" t="s">
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="3:3">
       <x:c r="C21" t="s">
-        <x:v>81</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="3:3">
       <x:c r="C22" t="s">
-        <x:v>84</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="3:3">
       <x:c r="C23" t="s">
-        <x:v>85</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="3:3">
-      <x:c r="C26" s="12" t="s">
-        <x:v>120</x:v>
+      <x:c r="C26" s="11" t="s">
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="3:3">
       <x:c r="C27" t="s">
-        <x:v>154</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="3:3">
       <x:c r="C28" t="s">
-        <x:v>86</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="3:3">
       <x:c r="C29" t="s">
-        <x:v>116</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="3:3">
       <x:c r="C30" t="s">
-        <x:v>118</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="3:3">
-      <x:c r="C33" s="12" t="s">
-        <x:v>115</x:v>
+      <x:c r="C33" s="11" t="s">
+        <x:v>166</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="3:3">
       <x:c r="C34" t="s">
-        <x:v>146</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="3:3">
       <x:c r="C35" t="s">
-        <x:v>87</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="3:3">
       <x:c r="C36" t="s">
-        <x:v>88</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="3:3">
       <x:c r="C37" t="s">
-        <x:v>70</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="3:3">
       <x:c r="C39" t="s">
-        <x:v>1</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="3:3">
-      <x:c r="C42" s="12" t="s">
-        <x:v>117</x:v>
+      <x:c r="C42" s="11" t="s">
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="3:3">
       <x:c r="C43" t="s">
-        <x:v>153</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="3:3">
       <x:c r="C44" t="s">
-        <x:v>74</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="3:3">
       <x:c r="C45" t="s">
-        <x:v>132</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="3:3">
       <x:c r="C46" t="s">
-        <x:v>133</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="3:3">
       <x:c r="C47" t="s">
-        <x:v>121</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="3:3">
       <x:c r="C48" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="3:3">
-      <x:c r="C50" s="12" t="s">
-        <x:v>123</x:v>
+      <x:c r="C50" s="11" t="s">
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="3:3">
       <x:c r="C51" t="s">
-        <x:v>79</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="3:8">
       <x:c r="C52" t="s">
-        <x:v>71</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H52" s="2" t="s">
-        <x:v>137</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="3:3">
       <x:c r="C53" s="2" t="s">
-        <x:v>75</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="3:3">
       <x:c r="C54" s="2" t="s">
-        <x:v>170</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="3:3">
-      <x:c r="C57" s="12" t="s">
-        <x:v>124</x:v>
+      <x:c r="C57" s="11" t="s">
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="3:3">
       <x:c r="C58" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="3:3">
       <x:c r="C59" s="2" t="s">
-        <x:v>183</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="3:3">
       <x:c r="C60" s="2" t="s">
-        <x:v>179</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="3:3">
       <x:c r="C61" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="3:3">
-      <x:c r="C64" s="12" t="s">
-        <x:v>127</x:v>
+      <x:c r="C64" s="11" t="s">
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="3:3">
       <x:c r="C65" t="s">
-        <x:v>72</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="3:3">
       <x:c r="C66" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="3:3">
       <x:c r="C67" s="2" t="s">
-        <x:v>184</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="3:3">
       <x:c r="C68" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="3:6">
-      <x:c r="C72" s="16" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="D72" s="16"/>
-      <x:c r="E72" s="13"/>
-      <x:c r="F72" s="13"/>
+      <x:c r="C72" s="15" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D72" s="15"/>
+      <x:c r="E72" s="12"/>
+      <x:c r="F72" s="12"/>
     </x:row>
     <x:row r="73" spans="3:6">
-      <x:c r="C73" s="15" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="D73" s="14" t="s">
+      <x:c r="C73" s="14" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D73" s="13" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E73" s="13" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="F73" s="13" t="s">
+        <x:v>123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="3:6">
+      <x:c r="C74" s="14" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="E73" s="14" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="F73" s="14" t="s">
-        <x:v>159</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" spans="3:6">
-      <x:c r="C74" s="15" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="D74" s="13" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E74" s="13" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="F74" s="13" t="s">
-        <x:v>163</x:v>
+      <x:c r="D74" s="12" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="E74" s="12" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="F74" s="12" t="s">
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="3:6">
-      <x:c r="C75" s="15" t="s">
+      <x:c r="C75" s="14" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="D75" s="12" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="E75" s="12" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="F75" s="12" t="s">
+        <x:v>148</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="3:6">
+      <x:c r="C76" s="14" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="D76" s="12" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="D75" s="13" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="E75" s="13" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="F75" s="13" t="s">
-        <x:v>107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" spans="3:6">
-      <x:c r="C76" s="15" t="s">
+      <x:c r="E76" s="12" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F76" s="12" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="D76" s="13" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="E76" s="13" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="F76" s="13" t="s">
-        <x:v>162</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells count="1">
     <x:mergeCell ref="C72:D72"/>
   </x:mergeCells>
-  <x:pageMargins left="0.69999998807907104492" right="0.69999998807907104492" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
@@ -2752,10 +3615,181 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet8"/>
-  <x:dimension ref="A1:A1"/>
+  <x:dimension ref="C3:I31"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
-  <x:sheetData/>
-  <x:pageMargins left="0.69999998807907104492" right="0.69999998807907104492" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:cols>
+    <x:col min="3" max="3" width="51.12890625" bestFit="1" customWidth="1"/>
+    <x:col min="5" max="5" width="59.98828125" bestFit="1" customWidth="1"/>
+    <x:col min="7" max="7" width="41.00390625" bestFit="1" customWidth="1"/>
+    <x:col min="9" max="9" width="37.96875" bestFit="1" customWidth="1"/>
+    <x:col min="10" max="10" width="5.375" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="3" spans="3:3" ht="20.64999999999999857891">
+      <x:c r="C3" s="20" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="3:3" ht="22.05000000000000071054">
+      <x:c r="C6" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="3:9">
+      <x:c r="C7" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="E7" s="23" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="G7" s="19" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="I7" s="19" t="s">
+        <x:v>242</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="3:9">
+      <x:c r="C8" s="21" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="22" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="G8" s="22" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I8" s="22" t="s">
+        <x:v>233</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="3:9">
+      <x:c r="C9" s="21" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="E9" s="22" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G9" s="22" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I9" s="22" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="3:9">
+      <x:c r="C10" s="21" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E10" s="22" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G10" s="22" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I10" s="22" t="s">
+        <x:v>231</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="3:9">
+      <x:c r="C11" s="21" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E11" s="22" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G11" s="22" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="I11" s="19"/>
+    </x:row>
+    <x:row r="12" spans="3:7">
+      <x:c r="C12" s="21" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="G12" s="22" t="s">
+        <x:v>234</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="3:3" ht="22.05000000000000071054">
+      <x:c r="C15" s="25" t="s">
+        <x:v>238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="3:3">
+      <x:c r="C16" s="22" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="3:5">
+      <x:c r="C17" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E17" s="24" t="s">
+        <x:v>258</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="3:5">
+      <x:c r="C18" s="21" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="E18" s="21" t="s">
+        <x:v>259</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="3:5">
+      <x:c r="C19" s="21" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="E19" s="21" t="s">
+        <x:v>260</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="3:5">
+      <x:c r="C20" s="21" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="E20" s="21" t="s">
+        <x:v>251</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="3:3">
+      <x:c r="C21" s="21" t="s">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="3:3">
+      <x:c r="C22" s="21" t="s">
+        <x:v>257</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="3:3" ht="22.05000000000000071054">
+      <x:c r="C26" s="26" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="3:3">
+      <x:c r="C27" s="21" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="3:3">
+      <x:c r="C28" s="21" t="s">
+        <x:v>261</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="3:3">
+      <x:c r="C30" s="19" t="s">
+        <x:v>265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="3:3">
+      <x:c r="C31" t="s">
+        <x:v>262</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
@@ -2763,10 +3797,89 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet9"/>
-  <x:dimension ref="A1:A1"/>
+  <x:dimension ref="U4:V20"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
-  <x:sheetData/>
-  <x:pageMargins left="0.69999998807907104492" right="0.69999998807907104492" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:cols>
+    <x:col min="21" max="21" width="12.74609375" bestFit="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="4" spans="21:21" ht="22.05000000000000071054">
+      <x:c r="U4" s="27" t="s">
+        <x:v>247</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="21:21">
+      <x:c r="U6" s="21" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="21:21">
+      <x:c r="U7" s="21" t="s">
+        <x:v>246</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="21:21">
+      <x:c r="U8" s="21" t="s">
+        <x:v>236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="21:21">
+      <x:c r="U9" s="21" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="21:21">
+      <x:c r="U10" s="21" t="s">
+        <x:v>244</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="21:21">
+      <x:c r="U11" s="21" t="s">
+        <x:v>223</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="21:21">
+      <x:c r="U12" s="21" t="s">
+        <x:v>219</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="21:21">
+      <x:c r="U14" s="22" t="s">
+        <x:v>237</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="22:22">
+      <x:c r="V15" t="s">
+        <x:v>269</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="22:22">
+      <x:c r="V16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="21:21">
+      <x:c r="U17" s="22" t="s">
+        <x:v>248</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="22:22">
+      <x:c r="V18" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="21:21">
+      <x:c r="U19" s="21" t="s">
+        <x:v>252</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="22:22">
+      <x:c r="V20" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
--- a/marketing/무진사 데이터 컨텐츠마케팅 프로세스_260317.xlsx
+++ b/marketing/무진사 데이터 컨텐츠마케팅 프로세스_260317.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11460" firstSheet="5" activeTab="2"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="14115" windowHeight="11430" tabRatio="599" firstSheet="5" activeTab="21"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="1. 문제정의" sheetId="1" r:id="rId4"/>
@@ -23,36 +23,576 @@
     <x:sheet name="9. Persona" sheetId="9" r:id="rId12"/>
     <x:sheet name="10. SWOT" sheetId="10" r:id="rId13"/>
     <x:sheet name="11. NPD" sheetId="11" r:id="rId14"/>
+    <x:sheet name="12. WBS" sheetId="12" r:id="rId15"/>
+    <x:sheet name="13. 4P" sheetId="13" r:id="rId16"/>
+    <x:sheet name="14. PLC" sheetId="14" r:id="rId17"/>
+    <x:sheet name="15. 컨텐츠 기획" sheetId="15" r:id="rId18"/>
+    <x:sheet name="16. 무드 보드" sheetId="16" r:id="rId19"/>
+    <x:sheet name="17. WireFrame" sheetId="17" r:id="rId20"/>
+    <x:sheet name="18. 컨텐츠 제작" sheetId="18" r:id="rId21"/>
+    <x:sheet name="19. 3P Media Mix" sheetId="19" r:id="rId22"/>
+    <x:sheet name="20. Ads Campaign" sheetId="20" r:id="rId23"/>
+    <x:sheet name="21.메타 비즈니스 광고 캠페인 세팅" sheetId="21" r:id="rId24"/>
+    <x:sheet name="Sheet1" sheetId="22" r:id="rId25"/>
+    <x:sheet name="23.구글 애즈 유튜브 광고" sheetId="23" r:id="rId26"/>
+    <x:sheet name="24. 구글 애즈 &amp;유튜브 광고" sheetId="24" r:id="rId27"/>
   </x:sheets>
   <x:calcPr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" mc:Ignorable="hs" hs:hclCalcId="904"/>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="289">
-  <x:si>
-    <x:t>3) Positioning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-패션 관심도 매우 높음</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="699">
+  <x:si>
+    <x:t>자사 브랜드 및 상품의 인지도를 최대한 많이 효과적으로 높이거나 알리고자 할때</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">유튜브 내 특정 키워드 검색시, 검색바 우측 상단 |하단 값과 함께 노출되는 광고 (썸네일이미지+ 텍스트 방식) -&gt; 썸네일 클릭시 요금 부과                                                                                                                                 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>광고메세지는 굉장히 감성 0 -&gt; 우리 타겟고객에게는 잘 와닿지않는 메세지x</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-타겟 중요성: 너무 좁혀놓고 모집단(모수)너무 적은 상황 -&gt; 예산 소진 x</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 테스트 진행 시, 변수는 1개 원칙 (실무적으로 최소화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 단순히 광고소재를 여러개 만들어서 집행 -&gt; A/B x</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; GA4: 사용자들이 우리 사이트 유입,방문 &gt; 어ᄄᅠᆫ 페이지,얼만큼 시간 체류 이탈&gt; 이벤트 활용 /전환/재방문 =&gt; 세션전환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://docs.google.com/forms/d/e/1FAIpQLSdXs6_v4ofkPICNDYSSmO6x1yRrk0WiNohaSWJVGXX6soOiBQ/viewform</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 똑같은 매체에서 상품,서비스를 판매하더라도 메인,서브, 상세페이지, 상푸 ㅁ목로페이지 등 다양한 채널에서 각각 높은 비율을 차지하고 있는 페이지를 선별-&gt; 극대화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6) 피츠의 법칙 : 클수록, 화려할수록 클릭을 하고 싶은 욕구가 커진다 (로그인, 회원가입, 구매하기, 신청하기)-&gt; 엑센트 컬러 강조, 일반 버튼 사이즈보다 키워줌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 매력적 요소 컨텐츠 : 전혀 기대안했는데, 있음으로써 매우 큰 감동을 느끼는 컨텐츠 (AI기반 추천 시스템 기능)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 앞에서 수집한 고객정보를 기반으로 최우선 고객집단(그룹)을 정의하는데 있어서 단순 경험, 의견을 바탕으로 결정 X</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 일원적 요소 컨텐츠: 있으면 있을수록 만족하지만, 없으면 없을수록 불편한 컨텐츠
+(ex) 쇼핑몰 - 상세 필터기능)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) 픽셀 추적 코드 : 이벤트 설정 -&gt; 사용자의 액션행위 수집 -&gt; 기반 리타겟팅 광고 캠페인(*광고 효율성 극대화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> -Objective (미시적 목표): 사용자가 및 방문자가 실제 상품을 구매할 수 있는 직.간접적인 행위의 지표가 상승</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 출근룩 카테고리 구매 비중 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 25~34세 직장인 68%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>텍스트 신쟁 시, 변수는 1개 원칙</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> &gt;Primary Target</x:t>
+  </x:si>
+  <x:si>
+    <x:t>행동-&gt; 추천받기 /지금 보기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>광고 컨텐츠 소재 기획, 제작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불편한점 (pain point)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>핵심 상품 특장점 소개 전략 문서</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20. Ads Campaign</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-특히 신상품 출시 많은 관심</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설득할 수 있을만한 요소 부족</x:t>
   </x:si>
   <x:si>
     <x:t>-SNS컨텐츠 소비를 많이하는 고객</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">- </x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; User id &gt; Avg order value</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1) 브랜드 및 상품 정체성</x:t>
+    <x:t>4. User Reaserch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 채널별 경쟁사, 아이템별 경쟁자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Media 활용 순서 및 흐름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지금 구매하는것이 현명한 선택일까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; SKU 부족: 상품 다양성 부족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 페이지 체류시간 매우 짧음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여러상품 클릭, 가격/리뷰 비교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리뷰좋은 데일리룩 추천을 발견</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; 확고한 1위 독점적 지위 확보</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키워드 경쟁력: RoAS, ROI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>O-Opportunity (기회)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 상품 상세페이지 진입률 상승</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt;Secondary Target</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-Product Life Cycle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키워드 예산// 검색정도//클릭률</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRM 채널 설계 및 프로세스 구축</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; K-패션, 스타일 관심도 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 직업: IT 기업 마케팅 매니저</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 기술력, 가격, 가성비, 컨텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RFM Score 기준 테이블</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt;월 신규 방문자 5,000명</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">구조 개선이 필요한 단계 : </x:t>
+  </x:si>
+  <x:si>
+    <x:t>상품 판매.할인가 포지셔닝 정의</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Acquisition (유입단계)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>혜택, 신뢰, 시의성, 긴급성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 출근 준비가 훨씬 가벼워진 하루</x:t>
   </x:si>
   <x:si>
     <x:t>- 필요에 의해서 단발성 구매</x:t>
   </x:si>
   <x:si>
-    <x:t>KR</x:t>
+    <x:t>S- Strength (강점)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상품 기본정보 서비스 요약정리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 컨텐츠: 가치 추구형 컨텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 네이버 광고 센터 - 연관키워드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구체적이며 동종업계 -&gt;경쟁사 나열</x:t>
+  </x:si>
+  <x:si>
+    <x:t>*각 전략마다 3-5개 정도 수립</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; 약점대비 현재 업종의 활황기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; High End :고가전략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가치-&gt; 리뷰좋은 /가성비/인기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직접 오프라인 방문 유도를 위함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-조회,구독 높아지는 경향:자극적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잠재고객의 어ᄄᅠᆫ 행위가 발생</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bottom of Funneel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감정 -&gt; 고민끝/ 자신감/ 편안함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상품 판매효과 극대화 광고탬페인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>건너뛸 수 없는 일반 광고(CPM)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19. 3P Media Mix</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오프라인 매장 방문 및 프로모션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가치: 리뷰기반 가성비 스타일 추구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상황-&gt; 출근룩/ 데일리룩/오피스룩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 키워드 확인 &amp; 예산 결정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6) 메타 비즈니스 관리자 접속</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1000회 노출당 광고 과금 방식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사용자의 참여유도를 위한 광고캠페인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마케팅 프로세스 진행.전개 &gt;체감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLICK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>트래픽, 참여</x:t>
+  </x:si>
+  <x:si>
+    <x:t>광고순서</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VEIW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACTION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실적 최대화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOFU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>디스플레이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동영상 조회수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잠재고객</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MILIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">cCPI: </x:t>
+  </x:si>
+  <x:si>
+    <x:t>ex)전화번호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>*CTA 문구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOFU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포털 사이트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진척사항</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOFU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61이상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고객행동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- KPI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유입/첫인상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감성자극</x:t>
+  </x:si>
+  <x:si>
+    <x:t>짧고 강렬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>앱 프로모션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메인 카테고리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구매횟수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11. NPD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8~18만원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) BAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7. RFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구매결정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recency</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 가격 민감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세부 카테고리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 실행전략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-충동구매가능</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전략,기획</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미완성 기억</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Low(1점)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>관심 + 불안</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상세검토</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8. STP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최우선 고객</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14. PLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A/B 테스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무진사:</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18만원 이상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고객생각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>총 구매금액</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-계정 1개당</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13. 4P</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이벤트 세팅</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8만원 이하</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엄브렐러 전략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시각 만족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원웨이 전략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>할인정책 설계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>책임의식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31~60일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 문제정의</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mid(2점)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>홈페이지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>관심 + 피로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이탈/재방문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키워드 분류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D-DAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>탐색/비교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 일관된 컨셉 &amp; 톤앤매너: 컨텐츠 &amp; 메세지 (어떤 시즌, 상황,채널)-&gt; IMC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-가성비 있는 상품을 기준으로 빠른 구매결정 &amp; 검색 비교를 선호하는 성향 고객</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최종카드= WT전략: 약점을 개선해서 시장의 위협요소에 최대한 덜 노출시키겠다는 전략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동영상을 조회한 후 실제 상품 및 브랜드에 관심을 가질 법한 사용자들에게 광고집행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>데이터 세트 &gt; 설정 &gt; 이벤트 설정 &gt; 이벤트 설정도구 열기 &gt; 카페24 링크 넣기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 다양한 플랫폼 대비, 직장인 출근룩을 디테일하게 큐레이션하는 플랫폼, 서비스 부재</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유튜브 내 인스트림 광고 외 외부 제휴채널 내 건너뛰기 기능 없이 출력가능한 광고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실제 동영상광고를 본 후 구매까지 도달할 확률이 높은 소비자를 대상으로 광고 집행</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">동영상을 통해 나의 상품, 브랜드를 광고,홍보해서 해당 요소의 존재감을 인지시킨다. </x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 신규 스타트업 비즈니스 모델 적용X// 이미 비즈니스가 운영되고 있는 경우에 한함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 잠재고객 : 일반 유입 고객대비, 상품 및 서비스 결제확률이 매우 높은 고객</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A/B 테스트 -&gt; 단기간 내 상대적으로 더많은 호감을 받는 컨텐츠 문구를 채택</x:t>
+  </x:si>
+  <x:si>
+    <x:t>건너뛸 수 있거나 없는 인스트림 광고 혹은 범퍼 광고들을 조합해서 스토리텔링 전개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- MD와 협업하여 업종, 상품 가장 많이 판매되는 퍼널 사전 가설,검증, 전략 설계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문제 2: 유입은 발생, 구매전환률이 낮음/ 우리 홈페이지(브랜드) 신뢰도 낮음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 어떠한 서비스, 상품, 플랫폼 출시, 리뉴얼 -&gt; 시장 소비자들에게 선보이겠다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>짧은 동영상을 통해 생각지 못한 나의 결핍과 수요를 문득 창출시켜주고자 하는 목적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>출근룩 고민을 줄이고 당신에게 어울리는 스타일을 추천합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1) Product 전략 (판매요소 = 상품|서비스|플랫폼)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">- 1+1, 덤정책, %할인 =&gt; 큰 방향성 x, 장기적 목적 없이 단발성의 프로모션 실행 -&gt; 부메랑으로 돌아온다 (일관성x, 고객 매우 혼란) </x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+        <x:b val="1"/>
+      </x:rPr>
+      <x:t>1)키워드 수집:</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t xml:space="preserve">  최근 소비자들이 많이 검색하는 키워드 동향-&gt; 그 기반으로 한 콘텐츠 생성 -&gt;Funnel 설계 구조시 첫단계 소비자 획득 유리</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>: 어떤 강점을 어필하고, 어떤 약점을 빠르게 보완할 것이며, 어떤 타이밍에 좋은 기회를 포착할 것인가, 최악의 리스크를 어떻게하면 피할 수 있을까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 플레이스 &gt; 온오프라인을 나누는 것이 아니라, 채널 내 어떤 지점에서 매출발생 &amp; 외부 채널 중 어떤 플랫폼에서 소비자들을 많이 유입시킬 것인가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1) 관리자 권한 부여: 여러관리자가 광고캠페인 관리가 가능 (SNS 채널을 통해서 광고 집행-&gt; 관리자 여러명 / 채널 계정의 소유주만 접속가능)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구글 ai에 예산을 위탁 -&gt;  해당 예산으로 구글이 다양한 채널 대리 집행</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">3) 밀러의 법칙(Miller's Law) : 사람의 단기 기억에는 정보의 한계가 존재(사람은 한번에 최대 5-9개 사이의 정보만을 기억) </x:t>
+  </x:si>
+  <x:si>
+    <x:t>6초 이하의 길이만 허용, 최대한 짧은 시간 내 브랜드를 각인시키고자 집행하는 광고 =&gt; 건너뛰기 없음,  유튜브 영상 앞,끝,중간 모두 가능</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(*Before VS After: 채널별 유입 비중 -&gt; Paid Social  / Organic Search/ Organic Social )</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1) 멘탈모델 (mental model) : 소비자가 이미 자신의 머리속에 가지고 있는 이미지 및 컨셉을 다른 플랫폼, 서비스에서도 기대한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이벤트 관리자 &gt; 데이터 연결 &gt; 새 데이터 소스 연결 &gt; 웹 &gt; 광고계정설정 &gt; (픽셀코드설치) 직접설정 &gt; Meta 픽셀전용 &gt; 코드 복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문제 3: 유입 존재, 구매전환률 보통, 재방문 거의 전무/ 우리 홈페이지(브랜드) 기술적, 시각적,기능적 차별화 포인트 부재</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -74,610 +614,223 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>https://docs.google.com/forms/d/e/1FAIpQLSdXs6_v4ofkPICNDYSSmO6x1yRrk0WiNohaSWJVGXX6soOiBQ/viewform</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 페이지 체류시간 매우 짧음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-충동구매가능</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 가격보다 상품,브랜드 ,플랫폼 이미지 중요</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>8. STP</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>Activation(사용자 경험 및 실행)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>무진사:</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">구조 개선이 필요한 단계 : </x:t>
-  </x:si>
-  <x:si>
-    <x:t>(*Before VS After: 채널별 유입 비중 -&gt; Paid Social  / Organic Search/ Organic Social )</x:t>
-  </x:si>
-  <x:si>
-    <x:t>product = 실물 상품만 의미 X (플랫폼, 서비스, 교육, 컨텐츠 등)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 어느 방향을 향해 나아갈 것인가 = 고객 머리속에 우리는 어떤 이미지로 남고 싶은가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 목적에 따른 특정 아이템 빠르게 검색 후 구매</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-상품 구매후 만족시, 재구매 가능성이 매우 높음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-가격대비 만족도 높아야하는 고객 = 가성비 추구</x:t>
+    <x:t>실제 우리 상푸 및 서비스와 유사한 광고를 보고 상품을 시제 구매한 이력을 가지고 있는 소비자들을 대상으로 광고하고자 할때</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; SNS 등 Owned Media를 통한 유입비중 10% 이상 증가 &amp; 우리 홈페이지(브랜드) 접속시 CTR 3% 이상 기록</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 상품 목록페이지 (PLP= Product List Page) -&gt; 상품 상세페이지 이동할때 발생하는 클릭률 35% 이상 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TPO: Time Place Occasion -&gt;ex) 출근룩/ 데일리룩/ 봄코디/ 오피스룩/ 소개팅룩 /하객룩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 여러가지 업무들이 순차적/ 동시다발적으로 전개되어야하는데, 각 담당자들이 누구이며 마감기한이 언제까지인지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 최초에 특정 브랜드가 런칭했을 때의 상항에서의 4P전락이 시간경과에 따라서 일치하지 않은 확률이 매우 높음</x:t>
   </x:si>
   <x:si>
     <x:t>&gt;CRM (Customer Relationship Management). Email 발송 후클릭률 8% 이상</x:t>
   </x:si>
   <x:si>
+    <x:t>GAds: GA4를 통해 수집된 사용자의 데이터 정보를 받아서 해당 사용자들을 잠재고객이라는 이름으로 관리를 함.</x:t>
+  </x:si>
+  <x:si>
     <x:t>(*CTR 데이터 수집,분석 : page_view 이벤트 / click_purchase_button 이벤트)</x:t>
   </x:si>
   <x:si>
-    <x:t>1순위: Revenue</x:t>
+    <x:t>- 소비성향 : 합리적이고 가성비있는 소비 지향/ 가격대비 활용도 중요/ 브랜드 이름보다는 스타일링 및 코디 관심</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 당연적 요소 컨텐츠: 소비자 입장에서 당연히 있어야 할것으로 기대하는 컨텐츠 
+(ex. 쇼핑몰 - 검색창 )</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카페 24 접속 &gt; 쇼핑몰 설정 &gt; 기본설정 &gt; 검색엔진 최적화(SEO) &gt; 코드 직접 입력 &gt; 코드 붙여넣기</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">앱 다운로드를 유도                                                    </x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 이미지, 카피, CTA -&gt; 해당 3개 요소를 모두 바꿔서 하자!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필터 및 검색기능 강화, 상품정보 큐레이션 UI/UX 개선</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">- 지금 당장 고객들이 원하는 니즈 파악 + 장기적인 방향? </x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 합리적 소비를 위한 상품비교가 익숙한 25-34 직장인 여성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구글 포털사이트 내 키워드 검색시 노출되는 검색광고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1) 유튜브 광고 컨텐츠를 기획. 제작 -&gt; 랜딩페이지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도구 &gt; 계획 &gt; 키워드 플래너 &gt; 새 키워드 찾기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유튜브 채널을 활용한 상품 밑 브랜드 인지도 활성화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. GA4,GTM을 통해서 받은 데이터를 다시 GAds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Paid Media (또 다른 신규 고객 유입 창출)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; 직곽적x : 초반 매출, 영업이익 드리프트 저조</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 구글 트랜드 (글로벌 시장 &gt; 검색 키워드 서칭)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://business.facebook.com/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Earned Media (좋은 피드백 기록, 공유)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4) 데스크탑 &gt; 페이스북 사이트 접속 &gt; 페이지 생성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 개인화 맞춤전략 -&gt; 고객 맞춤형 추천 경험 제공</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 메타(인스타그램, 페이스북), 구글애즈 (유튜브)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 반드시 모든 브랜드,상품은 저마다의 수명주기 존재</x:t>
+  </x:si>
+  <x:si>
+    <x:t>온라인 &gt; 상품 목록페이지 &gt; 띠베너 &gt; 상품구매 유도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타겟:  25-34 직장인 여성(합리적 비교 소비형)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 옷장 앞에서 여러 옷을 걸쳐보면서 고민하던 아침</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스타일 확인, 코디완성, 지금바로 확인하기, 추천받기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메시지를 통해 사용자의 구체적인 행동 유도 (CTA)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 직장인을 위한 전문 데일리룩 AI큐레이션 몰, 무진사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>요즘 직장인들이 선택하는 가성비 데일리룩
+TOP 스타일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5) 인스타그램 프로페셔널 계정 &amp; 페이스북 페이지 연동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>특정 키워드 검색 입력시, 이에 대한 해결관련 컨텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 중형키워드 모두가 다 대형키워드가 된다는 보장 X</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">&gt; 매일 아침 출근룩 선택으로 몇분씩 고민중이신가요? </x:t>
+  </x:si>
+  <x:si>
+    <x:t>가격 부담없이 세련된 스타일을 완성할 수 있습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가성비, 가심비, 활용도, 리뷰좋은, 인기상품, best</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 어떤 컬러, 타이포그래피, 레이아웃으로 무드보드 생성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>꾸준한 컨텐츠 제작 + 컨텐츠의 전문성 + 소비자의 리뷰</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- RFM분석 대상 -&gt; 구매경험 1,050명 대상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 추천 링크를 활용한 구매 발생 비율 10% 이상 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 계속적으로 트랜드한 브랜드, 아이템 추종(유목민)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; SNS 및 포털사이트를 통한 외부유입 15% 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 지난 3개월 시간 무진사 홈페이지(브랜드) 실적 가정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 광고 캠페인을 활용한 유입비중 40% 이상 증가</x:t>
   </x:si>
   <x:si>
     <x:t>3) FGI: Focus Croup Interview</x:t>
   </x:si>
   <x:si>
-    <x:t>- RFM분석 대상 -&gt; 구매경험 1,050명 대상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 광고 캠페인을 활용한 유입비중 40% 이상 증가</x:t>
+    <x:t>-(오픈마켓, 종합몰, 편집샵, 독립목,소셜커머스 등</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA4: 우리 사이트에 방문하는 사용자의 트래픽 수집</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 트랜드 민감, SNS검색 후 비교 및 자기개성 어필</x:t>
   </x:si>
   <x:si>
     <x:t>AI 활용 기술적 업그레이드 -&gt; 맞춤 추천 기술 도입</x:t>
   </x:si>
   <x:si>
+    <x:t>&gt;평균세션(Avg Session) 시간 2분 이상 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">                               </x:t>
+  </x:si>
+  <x:si>
     <x:t>&gt; 참여도 획득 보고서를 통해서 평슌 세션 확인 가능</x:t>
   </x:si>
   <x:si>
-    <x:t>&gt; SNS 및 포털사이트를 통한 외부유입 15% 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 지난 3개월 시간 무진사 홈페이지(브랜드) 실적 가정</x:t>
+    <x:t>-각 비즈니스 포트폴리오별 광고계정(갯수 제한 x)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 직장인을 위한 합리적인 데일리룩 큐레이션 쇼핑몰</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상품 상세페이지 내 리뷰정보 요약 노출, 패션 코디 제안</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 가격 경쟁 치열 - 출혈경쟁으로 인한 사업성 악화</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">-우리 홈페이지(브랜드)를 통해서 매출, 이익이 발생 </x:t>
   </x:si>
   <x:si>
-    <x:t>&gt;평균세션(Avg Session) 시간 2분 이상 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상품 상세페이지 내 리뷰정보 요약 노출, 패션 코디 제안</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 추천 링크를 활용한 구매 발생 비율 10% 이상 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-(오픈마켓, 종합몰, 편집샵, 독립목,소셜커머스 등</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">                               </x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 계속적으로 트랜드한 브랜드, 아이템 추종(유목민)</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t xml:space="preserve">- </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="맑은 고딕"/>
-        <x:sz val="11"/>
-        <x:color rgb="ff000000"/>
-        <x:b val="1"/>
-      </x:rPr>
-      <x:t>명확한 고객행동지표를 기반으로 선정하기 위한 중간절차</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>- 신규 스타트업 비즈니스 모델 적용X// 이미 비즈니스가 운영되고 있는 경우에 한함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문제 2: 유입은 발생, 구매전환률이 낮음/ 우리 홈페이지(브랜드) 신뢰도 낮음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-가성비 있는 상품을 기준으로 빠른 구매결정 &amp; 검색 비교를 선호하는 성향 고객</x:t>
+    <x:t>-특정 브랜드의 충성도보다 본인만의 개성적인 스타일 중요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 트랜드 패션에 관심이 높은 2530 프리랜서 여성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매일 아침 옷장 앞에서 고민했다면 이제 빠르게 선택!
+1000만명이 선택한 리뷰좋은 데일리룩 추천</x:t>
+  </x:si>
+  <x:si>
+    <x:t>광고소재 15~30초/ 최소 6초, 5초 경과 후  -&gt; 과금되는 시점: 30초 이상 영상 시청</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. 유튜브 채널을 통해 우리와 소통중인 고객들에게 우리 사이트의 광고를 우선적으로 노출(효과)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-목표달성: 무신사 홈페이지 목적: 패션상품 큐레이션 (추천) + 사용자 구매유도 → 매출, 이익</x:t>
   </x:si>
   <x:si>
     <x:t>-경쟁사 역시, 위에서 분석한 고객 성향에 따른 차별점= 특징 &amp; 개선할 부분 유츄+ 정보수집</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-목표달성: 무신사 홈페이지 목적: 패션상품 큐레이션 (추천) + 사용자 구매유도 → 매출, 이익</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t xml:space="preserve">&gt; 좋은 상품을 구매하는 것도 좋지만 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="맑은 고딕"/>
-        <x:sz val="11"/>
-        <x:color rgb="ff000000"/>
-        <x:b val="1"/>
-      </x:rPr>
-      <x:t>실패하지 않은 선택을 최우선으로 결정하는 리스크 회피 성향</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>- Objective (미시적 목표) : 사용자가 자발적으로 Earned Media에 가서 상품 및 서비스를 공유, 광고 비율 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 동질집단 분석 보고서(cohort=동질집단). 1월 2주차 프로모션 행사를 통해서 유입된 사용자들의 7일내 재방문율 25% 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문제 3: 유입 존재, 구매전환률 보통, 재방문 거의 전무/ 우리 홈페이지(브랜드) 기술적, 시각적,기능적 차별화 포인트 부재</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; SNS 등 Owned Media를 통한 유입비중 10% 이상 증가 &amp; 우리 홈페이지(브랜드) 접속시 CTR 3% 이상 기록</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 상품 목록페이지 (PLP= Product List Page) -&gt; 상품 상세페이지 이동할때 발생하는 클릭률 35% 이상 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 상세페이지 및 컨텐츠 내 기존 소비자 리뷰만족도를 어필할 수 있는 컨텐츠</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 이전에 온라인으로 출근룩 구매 -&gt; 생각보다 저품질, 소재,주변반응 별로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2) Field Research: 해당 업종 관계자, 전문가 섭외, 인터뷰</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-&gt; 주간 구매 사용자수(Weekly Purchasing Users) 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">- 위에서 발견한 고객 성향에 따른 자사 경쟁력 &amp; 개선할 부분까지 나열 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 스크롤 깊이(Scroll Depth) 50% 이상 도달률 40% 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-&gt; STP전략의 Positioning에서 도출된 방향성과 정체성 반드시 일치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 인구통계학적 질문/ 업계 및 브랜드 관심도/ 구매행동기반 / 컨텐츠 소비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 힉의 법칙 =&gt; 사람은 너무 많은 성택지를 주먼 오히려 선택을 힘들어한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt;GTM활용 10,25,50,75,90  세부적인 스크롤 깊이 단위까지 확인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30일 이내 구매한 한달에 3회 이상 구매한, 총 18만원 이상을 지불한 금액</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 1개의 의류상춤 +화장품+악세사리까지 토탈 코디네이션 &amp; 출근룩 큐레이션</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-구매하기 전까지 많은 정보 수집, 비교 -&gt; 구매가지 걸리는 시간 많음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; UTM url 생성 후 eamil 발송 시, 삽입 -&gt; 해당 url을 통해서 유입한 사용자수 등을 확인</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> -Objective (미시적 목표): 구매 가능성이 높은 기존 구매 사용자의 재방문 효과적으로 유도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 앞에서 수집한 고객정보를 기반으로 최우선 고객집단(그룹)을 정의하는데 있어서 단순 경험, 의견을 바탕으로 결정 X</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> -Objective (미시적 목표): 사용자가 및 방문자가 실제 상품을 구매할 수 있는 직.간접적인 행위의 지표가 상승</x:t>
-  </x:si>
-  <x:si>
-    <x:t>차선고객 = 성장가능 고객</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30일 이내-&gt; High</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3) Competitor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 평균 객단가 22만원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 회원가입:3,200명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 구매자: 1,050명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 사용자가 관심상품으로 선택한 상품을 재조회하는 재조회률 30% 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 포털 사이트 등을 통한 자연 검색 유입 비중 20% 이상 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(*세션-&gt; 30분 시간을 기준으로 사용자의 액션행위 체크 단위)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 상품 목록페이지 기준, 상품 상세페이지 이동 유입경로 분석 보고서</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(*우리 홈페이지에 유입되는 신규사용자 -New Visitor 수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 전자상거래 이벤트 -&gt;purchase conversion rate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문제1: 실제 유입이 저조/ 우리 홈페이지(브랜드 ) 인지도 낮음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1) Desk Research: 오픈 서베이, 메조미디너, 나스미디어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 공유하기 버튼 클릭횟수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3. FUNNEL 구조 설계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-Key Results</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4) Form활용 리서치</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1) 유입 -&gt;  첫인상 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>-&gt;KPI(핵심성과지표)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>개선 (solution)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비교하기 쉽게 보고싶어!</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">290명: L/L/L </x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">280명 : M/L/L </x:t>
-  </x:si>
-  <x:si>
-    <x:t>160명: RFM H/H/H</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-첫 구매 만족도 높음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-할인 시즌만 겨냥해서 구매</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 브랜드 충성도 매우 낮음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8만원 이하 -&gt;Lovw</x:t>
-  </x:si>
-  <x:si>
-    <x:t>90일 이상 -&gt; Low</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5) 이탈 또는 재방문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- KeyResults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5. Journey map</x:t>
-  </x:si>
-  <x:si>
-    <x:t>320명 : H/M/M</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이탈/재방문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 문제정의</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유입/첫인상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상세검토</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고객생각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고객행동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7. RFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구매결정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61이상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>관심 + 불안</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mid(2점)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미완성 기억</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8만원 이하</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8~18만원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31~60일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>관심 + 피로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구매횟수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18만원 이상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>총 구매금액</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최우선 고객</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Low(1점)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- KPI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recency</x:t>
-  </x:si>
-  <x:si>
-    <x:t>탐색/비교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3) Competitior``</x:t>
-  </x:si>
-  <x:si>
-    <x:t>혜택, 신뢰, 시의성, 긴급성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Acquisition (유입단계)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구체적이며 동종업계 -&gt;경쟁사 나열</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RFM Score 기준 테이블</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 채널별 경쟁사, 아이템별 경쟁자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여러상품 클릭, 가격/리뷰 비교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불편한점 (pain point)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설득할 수 있을만한 요소 부족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt;월 신규 방문자 5,000명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4. User Reaserch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지금 구매하는것이 현명한 선택일까?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2회</x:t>
-  </x:si>
-  <x:si>
-    <x:t>`</x:t>
-  </x:si>
-  <x:si>
-    <x:t>,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> </x:t>
-  </x:si>
-  <x:si>
-    <x:t>단계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호기심</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1회</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Segment 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4) 구매의사결정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3회 이상 구매</x:t>
-  </x:si>
-  <x:si>
-    <x:t>재방문할 명문 부족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1) Customer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신뢰할만한 정보 부족</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">&gt; 재방문 세션수 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>2) Company</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Frequency</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 리뷰 작성률 높음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Segment 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Segment 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Recency </x:t>
-  </x:si>
-  <x:si>
-    <x:t>Segment 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1회 -&gt; Low</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2회 -&gt;Mid</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30일 이내 구매</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Monetary</x:t>
-  </x:si>
-  <x:si>
-    <x:t>High (3점)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내 취향에 맞는 사이트인가?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메인배너, 추천상품 스캔</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사용자 맞춤 기준 불명확</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt;앱푸쉬알람 클릭률5% 이상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 구매전환율 2.5% 달성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3) 상세검토 -&gt; 확신형성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정보 구조 미비, 정보 부족</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">2) 탐색 -&gt; 비교 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>60일 이내 -&gt; mid</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 25~34세 직장인 68%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 출근룩 카테고리 구매 비중 높음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>=&gt; 차선고객이 최우선 고객에 비해 너무 많은 경우 그 부분이 FUNNEL구조에서의 개선점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 목록 페이지 내 클릭 이벤트 세팅 (목록페이지 유입대비, 해당버튼 클릭 수 =&gt; 클릴률</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 상품상세페이지 (PDP= Product Detail Page) 조회율 60%이상 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> -Objective (미시적 목표): 실질적인 상품 구매 전활융 향상 및 매출 이익 증대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 브랜드 인지도 : 정석 시간 + 비용 꾸준한 투자 //SNS활용 재치,  개성 콘텐츠</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt;GA4,GTM 등의 트래픽 수집, 분석 툴 데이터 취합 비교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; cart conversion rate(장바구니 전환율)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 자사 경쟁력(상품, 플랫폼, 서비스, 기술 등) 기반 분석</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필터 및 검색기능 강화, 상품정보 큐레이션 UI/UX 개선</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; GA4 &gt; 데이터 스트림 코드를 통해서 삽압 vs 구글</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-트랜디함을 좋아하는 고객들로 추정, 우연하게 브랜드 노출</x:t>
-  </x:si>
-  <x:si>
-    <x:t>찜, 쿠폰, CRM, 리타게팅 마케팅을 통해서 재방문율 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장바구니, 구매 고민</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가장 높은 피로감</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>&gt;</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="맑은 고딕"/>
-        <x:sz val="11"/>
-        <x:color rgb="ff000000"/>
-        <x:b val="1"/>
-      </x:rPr>
-      <x:t>가격민감+ 가치추구 혼합형</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>Revenue(매출향상)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>8~18만원 -&gt; Mid</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18만원 이상 -&gt;High</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3회이상 -&gt; High</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -713,63 +866,29 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>- 전략적으로 타겟(과녁) 고객을 선정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 장바구지-&gt; 구매 전활율 전호나 35%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 리뷰작성빈도 및 작성률 (SQL)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2. NSM 정의: 거시적 목표 =큰목표</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보류 후 종료 또는 재방문 구매 의사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상세페이지, 리뷰, 포토 혹은 동영상 조회</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 두번째 재구매로 이어지는 비중이 약함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 후기 작성률, 기존 대비 10% 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 상품 공유하기 버튼 클릭율 3% 이상 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; Returning User = Visiors</x:t>
-  </x:si>
-  <x:si>
-    <x:t>처음 구매를 하려고 하는데, 실패하지 않을까?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- SNS 광고 통해서 유입한 고객 (대부분)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; Google Form / Naver Form</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-리뷰가 존재x, 할인 비시즌 거의 활동 전무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 우리 홈페이지의 인기상품군들의 구매비중 50%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다시는 마주하고 싶지 않다.
-꼭 다시 오고 싶다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>⇒ 방문을통해서 구매전환까지 매력도(설들력) 약함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 평균 주문 구매금액 7만원 유지(평균객단가)</x:t>
+    <x:t>7) 폰 레스토프 효과 : 이질성의 효과, 강조와 지강조 컨텐츠가 동시에 존재해야 둘다 인식된다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>*우리사이트의 존재를 먼저 인지한 경우, 해당 고객을 주요 잠재고객으로 인식 후 광고 캠페인 집행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 패션성향 : 출근룩, 데일리 캐주얼룩 중심/ 너무 튀는 스타일 부담 &amp; 세련됨 +무난함추구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-구체적인 브랜드 혹은 상품 슬로건(Just do it, nothing is impossible)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 컨텐츠 기획 기본 방향 수립（광고 톤앤매너, 배경컬러, 웹사이트 메인베너, 상세페이지, CRM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우리가 취급하는 상품 및 서비스를 구매할 확률이 높은 소비자들을 대상으로 광고를 노출하고자ᄒᆞᇂ때</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GTM: 우리 사이트에 접속한 사용자 가운데 주요한 이벤트를 클릭한 사람들을 선별하고자 할 때</x:t>
   </x:si>
   <x:si>
     <x:r>
-      <x:t xml:space="preserve">&gt; </x:t>
+      <x:t xml:space="preserve">&gt; 좋은 상품을 구매하는 것도 좋지만 </x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -778,12 +897,63 @@
         <x:color rgb="ff000000"/>
         <x:b val="1"/>
       </x:rPr>
-      <x:t>즉각 결정 보류 + 재방문시 구매결정 성향</x:t>
+      <x:t>실패하지 않은 선택을 최우선으로 결정하는 리스크 회피 성향</x:t>
     </x:r>
   </x:si>
   <x:si>
+    <x:t>4) 힉의 법칙(Hick's Law) : 소비자가 어떤 것을 선택하려고 할 때, 지나치게 옵션이 많으면 결정장애 유발 =&gt; 5개 이하</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-Low Fidelity WireFrame :저품질 와이어 프레임 -&gt; 일체의 채색없이 오롯이 선과 무채색만으로 컨텐츠 프레임 완성</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> -Objective (미시적 목표): 구매 가능성이 높은 기존 구매 사용자의 재방문 효과적으로 유도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비즈니스 자산 &gt; 데이터 세트 생성(픽셀 코드를 생성한 후 픽셀코드를 통해서 수집한 데이터가 저장될 공간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 쇼핑성향 : 월평균 1~2회 온라인 의류쇼핑 진행 / 1회 구매시, 약 7만원/ 3개월 20만원 구매</x:t>
+  </x:si>
+  <x:si>
+    <x:t>*우리 사이트를 먼저 인지한게 아닌, 우리가 운영중인 구글 유튜브 공식 채널 계정을 먼저 인지한 고객들!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; UTM url 생성 후 eamil 발송 시, 삽입 -&gt; 해당 url을 통해서 유입한 사용자수 등을 확인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROI: Return On Investment : 마케팅 외 기타 비용 집행 대비 영업 이익(순이익)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 하이엔드 고가전략, 프리미엄 브랜드 -&gt; 프로모션 전략을 철저하게 계획하에 장기적인 관점에서 실행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3) 스마트폰 : 인스타그램 앱 접속 &gt; 설정 &gt; 계정 설정 변환(일반 -&gt; 프로페셔널 계정 =비즈니스)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 어느 방향을 향해 나아갈 것인가 = 고객 머리속에 우리는 어떤 이미지로 남고 싶은가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소형키워드 : 중소기업, 자본,인력 미비상태 &gt; 마이크로 시장(작은시장)주도하겠다는 의지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5) 제이콥의 법칙: 소비자는 익숙하고 보편적인 UI/UX 패턴을 선호한다는 심리학 이론</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 최근 본 | 구매한 상품 기반, 맞춤 스타일 제공 -&gt; 최근 인기 코디 스타일 피드백</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. 유튜브에 접속한 댓글, 좋아요 등을 한 고객들의 정보를 GAds로 찾아올 필요가 있음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비즈니스 플레이 그라운드 =필드, 앱인경우, 앱 다운로드를 최대한 많이 유도하고자 할때</x:t>
+  </x:si>
+  <x:si>
+    <x:t>=&gt; 차선고객이 최우선 고객에 비해 너무 많은 경우 그 부분이 FUNNEL구조에서의 개선점</x:t>
+  </x:si>
+  <x:si>
     <x:r>
-      <x:t xml:space="preserve">&gt; 어떤 홈페이지에 접속, </x:t>
+      <x:t xml:space="preserve">대형키워드: </x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -792,82 +962,928 @@
         <x:color rgb="ff000000"/>
         <x:b val="1"/>
       </x:rPr>
-      <x:t>탐색 중심소비패턴</x:t>
+      <x:t>자본, 인력구조 확보</x:t>
     </x:r>
-  </x:si>
-  <x:si>
-    <x:t>- 쇼핑성향 : 월평균 1~2회 온라인 의류쇼핑 진행 / 1회 구매시, 약 7만원/ 3개월 20만원 구매</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 4계절 존재 -&gt; 시즌 트랜드가 빠르게 흘러감</x:t>
-  </x:si>
-  <x:si>
     <x:r>
-      <x:t>Retention(재방문)</x:t>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t xml:space="preserve"> 상태 &gt; 단기간 내 상위노출 장악 및 실질적 매출 유도</x:t>
     </x:r>
   </x:si>
   <x:si>
+    <x:t>&gt; 상품상세페이지 (PDP= Product Detail Page) 조회율 60%이상 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) 카노모델 (Kano Model): 소비자에게 영향을 주는 컨텐츠는 크게 3가지의 종류</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> -Objective (미시적 목표): 실질적인 상품 구매 전활융 향상 및 매출 이익 증대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 목록 페이지 내 클릭 이벤트 세팅 (목록페이지 유입대비, 해당버튼 클릭 수 =&gt; 클릴률</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 브랜드 인지도 : 정석 시간 + 비용 꾸준한 투자 //SNS활용 재치,  개성 콘텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Probelm(문제 자각시키기) -&gt; Agitation (동요) -&gt; Solution(해결)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중형키워드: 검색은 일어나고 있지만 아직 확실한 트랜드로 부상하지 않은 키워드 그룹/ 잠재력 존재 &gt; 대형키워드 기준 상대적 적은 자본으로도 선점 //  리스크-&gt; 키워드 성장 후 대형키워드 부상</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">4) 감성제안 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Funnel 구조 설계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>promotion 전략실행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mid of fUnnel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 출근룩 고민 끝!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B 상품스펙을 강조</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 상품 연출 컷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리뷰 별표표시 강조</x:t>
+  </x:si>
+  <x:si>
+    <x:t>굳이 리뷰언급 x</x:t>
+  </x:si>
+  <x:si>
     <x:r>
-      <x:t>Referral (주변추천, 바이럴 단계)</x:t>
+      <x:t>-</x:t>
     </x:r>
-  </x:si>
-  <x:si>
-    <x:t>- 패션성향 : 출근룩, 데일리 캐주얼룩 중심/ 너무 튀는 스타일 부담 &amp; 세련됨 +무난함추구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>* 출근시 착용가능한 출근룩 고민많음</x:t>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+        <x:b val="1"/>
+      </x:rPr>
+      <x:t xml:space="preserve"> 충성도가 높은 전략 -&gt; 1인당 고객 LTV높게 </x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t xml:space="preserve">- </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+        <x:b val="1"/>
+      </x:rPr>
+      <x:t>명확한 고객행동지표를 기반으로 선정하기 위한 중간절차</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1) 메세지 유형 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>디맨드젠 캠페인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>웹사이트 트래픽</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2) 탐색 -&gt; 비교 </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">280명 : M/L/L </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">- 장바구니에 담는 전환률 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>개선 (solution)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8만원 이하 -&gt;Lovw</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1) 유입 -&gt;  첫인상 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>-첫 구매 만족도 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>차선고객 = 성장가능 고객</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메인배너, 추천상품 스캔</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30일 이내-&gt; High</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5) 이탈 또는 재방문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1순위: Revenue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- KeyResults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt;KPI(핵심성과지표)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-Key Results</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18. Wire Frame</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">product 전략 실행 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>4) Form활용 리서치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-할인 시즌만 겨냥해서 구매</x:t>
+  </x:si>
+  <x:si>
+    <x:t>90일 이상 -&gt; Low</x:t>
+  </x:si>
+  <x:si>
+    <x:t>160명: RFM H/H/H</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 공유하기 버튼 클릭횟수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 평균 객단가 22만원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 회원가입:3,200명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 브랜드 충성도 매우 낮음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 직장인 코디네이션 및 큐레이팅 최대한 어필될 수 있는 컨텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; cart conversion rate(장바구니 전환율)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>찜, 쿠폰, CRM, 리타게팅 마케팅을 통해서 재방문율 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 자사 경쟁력(상품, 플랫폼, 서비스, 기술 등) 기반 분석</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사용자의 특정행위에 따른 광고 과금 방식(회원가입,다운로드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 선별된 키워드 활용 -&gt; 광고카피 문안 변환 (채널별)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-트랜디함을 좋아하는 고객들로 추정, 우연하게 브랜드 노출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SO전략: 강점을 활용한 시장의 기회요소를 포착하겠다는 전략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt;GA4,GTM 등의 트래픽 수집, 분석 툴 데이터 취합 비교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리뷰와 데이터를 기반으로 실패없는 데일리 패션을 경험하세요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 공식 인스타계정, 유튜브계정, 공식 블로그 계정,사이트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12. WBS = Work Breakdown Structure</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-Product/ Price / Place / Promtion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; GA4 &gt; 데이터 스트림 코드를 통해서 삽압 vs 구글</x:t>
+  </x:si>
+  <x:si>
+    <x:t>니즈: 출근 시 선택할 수 있는 출근룩 관련 스트레스 감소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- UX/UI 전략(눈에 보이는 시각적인 서비스 개선. 효율성)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; 출혈경쟁 (단가경쟁) -&gt; 원가 절감 성공한 기업만 생존</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 유료의 비용을 지불하고 사용자들의 트래픽을 획득하는 매체</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사용자의 실질적인 참여(댓글등록, 이벤트 영상 )발생되었을</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리크스 관리(해야할 것, 하지말아야할 것, 우선시 해야할 것)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1) Desk Research: 오픈 서베이, 메조미디너, 나스미디어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 상품 목록페이지 기준, 상품 상세페이지 이동 유입경로 분석 보고서</x:t>
+  </x:si>
+  <x:si>
+    <x:t>폼 형식의 광고를 보고 소비자들이 최대한 많이 참여할 수 있도록 할때</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15초까지 무조건 영상을 다 봐야하는 부담 -&gt; 인지도, 각인효과 기대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구글 포털사이트 &gt; 쇼핑 관련 상품명 입력시, 구글 쇼핑 색션 출력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(*세션-&gt; 30분 시간을 기준으로 사용자의 액션행위 체크 단위)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">-어떻게 메세지를 전달, 어ᄄᅠᆫ 컨텐츠로 접근, 가치를 부여? </x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 구글애즈 키워드 플래너: 현실적인 키워드 입찰가를 중심으로 확인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 사용자가 관심상품으로 선택한 상품을 재조회하는 재조회률 30% 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문제1: 실제 유입이 저조/ 우리 홈페이지(브랜드 ) 인지도 낮음</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">&gt; 자사 자산을 스캔, 검색, 조회를 통해 인지 +리뷰 데이터 조회 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 해당 키워드가 우리 업종, 업계, 산업과 연관성을 가질 수록 유리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(*우리 홈페이지에 유입되는 신규사용자 -New Visitor 수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 그래서 무진사는 당신에게 맞는 스타일을 먼저 큐레이션해드립니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대 30초 / 북미 시장 가능, 국내 광고 -&gt; 구글과의 협의 필요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Before(이전) -&gt;After(이후) -&gt; Bridge(단계)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 포털 사이트 등을 통한 자연 검색 유입 비중 20% 이상 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; "합리적"이라는 것의 정의 = 심리적으로 받아들여질 수 있는 가격</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4) Promotion 전략(어떤 메세지로 소비자를 설득할 것인가)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WO전략: 약점의 개선으로 시장의 기회요소를 최대한 활용하겠다는 전략</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+        <x:b val="1"/>
+      </x:rPr>
+      <x:t>&gt; Segmentation A(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t>트랜드 탐색, 검색 선호하는 유형)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>4. GAds는 해당 데이터를 활용하여 잠재고객 설정-&gt; 우선광고 집행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 전자상거래 이벤트 -&gt;purchase conversion rate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNS광고캠페인 문구</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">290명: L/L/L </x:t>
+  </x:si>
+  <x:si>
+    <x:t>18만원 이상 -&gt;High</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3) Positioning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>=&gt; 과소비 X, 합리적o</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마케팅 전략 기획안 발표</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블로그(정보전달 컨텐츠)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- Pain Point:</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 구매자: 1,050명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. FUNNEL 구조 설계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내 취향에 맞는 사이트인가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-패션 관심도 매우 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 니치 마케팅 = 틈새시장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>320명 : H/M/M</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 월소득 :350만원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 1회 구매후 재방문 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상품 상세페이지 기획안 정리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비교하기 쉽게 보고싶어!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5. Journey map</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1) 브랜드 및 상품 정체성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3) Competitor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2순위: Retention</x:t>
+  </x:si>
+  <x:si>
+    <x:t>채널/매체별 메세지 전략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) 장기적인 비전  제시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8~18만원 -&gt; Mid</x:t>
+  </x:si>
+  <x:si>
+    <x:t>* 상품 리뷰 의존도 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사용자 맞춤 기준 불명확</x:t>
+  </x:si>
+  <x:si>
+    <x:t>* 재방문 유입 확률 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월평균 클릭률 1% 마지노선</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Revenue(매출향상)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상품 특장점 인사이트 도출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3회이상 -&gt; High</x:t>
+  </x:si>
+  <x:si>
+    <x:t>*구글 애즈 유튜브 광고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T-Threat (위협)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>60일 이내 -&gt; mid</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정보 구조 미비, 정보 부족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3) 상세검토 -&gt; 확신형성</x:t>
   </x:si>
   <x:si>
     <x:t>- 리뷰/평점 확인 필수</x:t>
   </x:si>
   <x:si>
-    <x:t>-&gt; 확고한 1위 독점적 지위 확보</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; K-패션, 스타일 관심도 증가</x:t>
+    <x:t>-&gt; 생존과 가장 밀접</x:t>
+  </x:si>
+  <x:si>
+    <x:t>광고 캠페인 채널 세팅</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15. 컨텐츠 기획.제작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 충성도가 매우 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt;앱푸쉬알람 클릭률5% 이상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 구매전환율 2.5% 달성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. Earned Media</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) Targeting</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나에게 맞는 룩 확인하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가설기반 덴드시 테스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>shorts광고 (CPM)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 메타 비즈니스 관리자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초개인화 맞춤 매체전략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>W- Weakness(약점)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Retention(재방문)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타겟 유저 = 페르소나 결정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Top Of Funnel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>앱설치 시 광고과금 방식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1회 클릭당 광고 과금방식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>데스크탑 UI/UX기획</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WBS by PM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>객단가 상승 정략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퍼널 이벤트 설계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>place 전략실행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 실행 일정 관리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 나이 : 31세</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">경쟁정도 중간-낮음 </x:t>
   </x:si>
   <x:si>
     <x:r>
-      <x:t>W- Weakness(약점)</x:t>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+        <x:b val="1"/>
+      </x:rPr>
+      <x:t>3)</x:t>
     </x:r>
-  </x:si>
-  <x:si>
-    <x:t>2) 장기적인 비전  제시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-특히 신상품 출시 많은 관심</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 충성도가 매우 높음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-특정 브랜드의 충성도보다 본인만의 개성적인 스타일 중요</x:t>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t xml:space="preserve"> </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+        <x:b val="1"/>
+      </x:rPr>
+      <x:t>스토리텔링</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">price 전략실행 </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">키워드 범주: </x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026.04.28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(유혹,위기=&gt;자본)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 온라인.포으라인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세부 작업내용 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>=&gt; 일관성 흐트러짐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; 2인자의 전략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 성.비수기 존재</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Youtube 구독 및 참여</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">&gt; 이미지, 카피CTA-&gt; </x:t>
+  </x:si>
+  <x:si>
+    <x:t>*서브카피(설득 강화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안내없이 캠페인 만들기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>앱 다운로드 유도를 위함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>광고 캠페인 매체 선정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>첫 직장에 입사한지 3개월</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인피드 광고 (CPC)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키워드 -&gt; 카피 문구 전환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 네이버 데이터랩(이커머스 쇼핑업종 &gt; 연,상하반기 .분기.월 단위 -&gt; 어ᄄᅠᆫ 업종의 어떤 키우ㅝ드가 이슈) : 트랜드 추이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8) 게슈탈트 심리학 :  유사성의 법칙 -&gt;  비슷한 속성값을 가지고 있는 요소들을 비슷한 컬러, 도형으로 만들수록 기억에 오래남음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 단순히 저렴한 금액으로 상품 판매,해당 서비스가 이 가격대에 충분히 합리적이고, 만족스럽다는 느낌을 가질 수 있도로 설계하는 과정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- Objective (미시적 목표) : 사용자가 자발적으로 Earned Media에 가서 상품 및 서비스를 공유, 광고 비율 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 동질집단 분석 보고서(cohort=동질집단). 1월 2주차 프로모션 행사를 통해서 유입된 사용자들의 7일내 재방문율 25% 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지금 스타일 추천받기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16. 무드보드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17. 컨텐츠 제작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EX)한경희 생활과학</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EX) 아모레퍼시픽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카카오 (메신저)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4) 행동 키워드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3회 이상 구매</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스토리 구조 컨텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) 감정 키워드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인기 출근룩 확인하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">-&gt; 충성도 X, </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Segment 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Monetary</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4) 구매의사결정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1) 상황별 키워드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Frequency</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1) Customer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2회 -&gt;Mid</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10. SWOT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Segment 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 리뷰 작성률 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>재방문할 명문 부족</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">&gt; 광고메세지 x </x:t>
+  </x:si>
+  <x:si>
+    <x:t>신뢰할만한 정보 부족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Segment 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">&gt; 재방문 세션수 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>장바구니, 구매 고민</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1) PAS: </x:t>
   </x:si>
   <x:si>
     <x:t>- 브랜드 스토리</x:t>
   </x:si>
   <x:si>
-    <x:t>- 가격 민감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>* 상품 리뷰 의존도 높음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 직업: IT 기업 마케팅 매니저</x:t>
-  </x:si>
-  <x:si>
     <x:t>- 컨텐츠 전략 :</x:t>
   </x:si>
   <x:si>
-    <x:r>
-      <x:t>2) Targeting</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>- 월소득 :350만원</x:t>
+    <x:t>2) Company</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9. Persona</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가장 높은 피로감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Segment 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Recency </x:t>
+  </x:si>
+  <x:si>
+    <x:t>- Solution:</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30일 이내 구매</x:t>
   </x:si>
   <x:si>
     <x:t>- 이름 : 김서연</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1회 -&gt; Low</x:t>
+  </x:si>
+  <x:si>
+    <x:t>High (3점)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동영상 도달범위</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정보 중심 컨텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘의 코디 바로보기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전환을 유도하세요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오디오 도달 범위</x:t>
+  </x:si>
+  <x:si>
+    <x:t>광고 상품 종류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>shorts광고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인지도, 트래픽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범퍼광고(CPM)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잠재고객, 판매</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3) 가치 키워드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ex)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> </x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판매</x:t>
+  </x:si>
+  <x:si>
+    <x:t>참여</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CPE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CPS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>,</x:t>
+  </x:si>
+  <x:si>
+    <x:t>트래픽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CPC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인지도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>앱홍보</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>앱</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쇼핑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호기심</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쇠퇴기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>백종원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성숙기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>단계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>`</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산출물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동영상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2회</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">- </x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>담당자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1회</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성장기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역할</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도입기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검색</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>개인화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인피드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CPA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CPM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김승리</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -889,6 +1905,72 @@
     </x:r>
   </x:si>
   <x:si>
+    <x:t>&gt; 국내 소비자 트랜드 &amp; 대중심리 민감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 후기 작성률, 기존 대비 10% 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">매일 옷태문에 스트레스를 받던 그녀느 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Referral (주변추천, 바이럴 단계)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- Low End: 저가전략(가성비)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상세페이지, 리뷰, 포토 혹은 동영상 조회</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 모든 비지니스 업무 마감기한 존재</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 리뷰작성빈도 및 작성률 (SQL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 출근준비시간이 10분 줄었습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 전략적으로 타겟(과녁) 고객을 선정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. NSM 정의: 거시적 목표 =큰목표</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브랜드가 제공하고자 하는 혜택 관련 컨텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>youtube 도달범위, 조회수,참여도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>* 출근시 착용가능한 출근룩 고민많음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보류 후 종료 또는 재방문 구매 의사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 두번째 재구매로 이어지는 비중이 약함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Activation(사용자 경험 및 실행)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 위 전략을 통해 기대하는 KPI 지표:</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빠르게 선택하는 직장인 데일리룩 플랫폼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 시간은 없고 스타일은 포기하기 싫다면</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 장바구지-&gt; 구매 전활율 전호나 35%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>건너뛸 수 있는 인스트림 광고(CPV)</x:t>
+  </x:si>
+  <x:si>
     <x:r>
       <x:rPr>
         <x:rFont val="맑은 고딕"/>
@@ -908,66 +1990,167 @@
     </x:r>
   </x:si>
   <x:si>
+    <x:t>예쁘다? -&gt; 감성적 설득, 마케팅 설득</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 중국산 값싼 브랜드,플랫폼의 국내 진출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실제 상품이 1건 판매되었을 대 발생</x:t>
+  </x:si>
+  <x:si>
+    <x:t>편안한, 세련된, 단정한, 고민끝, 자신감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 가성비 : 원가 절감 // 대량생산</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026.03.30~2026.04.08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026.03.30~2026.04.15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owned Media( 지속적 재방문)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>출근 준비를 가볍게 만드는 스타일 쇼핑</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">브랜드가 전달하고자하는 깊이있는 메세지 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>건너뛸 수 없는 인스트림광고(CPM)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 컨텐츠 만족에 따른 구매전환율 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 메세지: 고급화된 메세지의 일관된 소통</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고민없는 스타일 선택, 리뷰로 증명된 쇼핑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 맘카페, 디시인사이드, 웃긴대학 등</x:t>
+  </x:si>
+  <x:si>
+    <x:t>건너뛸 수 있는 인스트림 광고 (CPV)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문제 해결 관련 키워드 중심의 컨텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">오늘도 옷 때문에 늦을까봐 걱정했다면 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제는 스타일 고민없이 하루를 시작하세요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>핵심 타겟 상품 특장점 도출(TPO타겐)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owned Media( 지속적 관계 관리)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유튜브 내 오디오 팟캐스트 관련 광고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B 문제해결형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A 감성형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>product = 실물 상품만 의미 X (플랫폼, 서비스, 교육, 컨텐츠 등)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 유튜브 동영상 컨텐츠 노출 &gt; 브랜드/상품의 존재 먼저 인지한 경우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실제 광고를 보고 우리의 사이트(랜딩 페이지)에 최대한 많이 유입시키고자 할때</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; STP전략의 Positioning에서 도출된 방향성과 정체성 반드시 일치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) Field Research: 해당 업종 관계자, 전문가 섭외, 인터뷰</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 직장인 데일리룩 구매, 큐레이션 효과적으로 추천 -&gt; 고객 만족도 경험</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 1개의 의류상춤 +화장품+악세사리까지 토탈 코디네이션 &amp; 출근룩 큐레이션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 상세페이지 및 컨텐츠 내 기존 소비자 리뷰만족도를 어필할 수 있는 컨텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 힉의 법칙 =&gt; 사람은 너무 많은 성택지를 주먼 오히려 선택을 힘들어한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 인구통계학적 질문/ 업계 및 브랜드 관심도/ 구매행동기반 / 컨텐츠 소비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30일 이내 구매한 한달에 3회 이상 구매한, 총 18만원 이상을 지불한 금액</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoAS: Return On Ads Spend: 마케팅 비용대비 ,매출액</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-구매하기 전까지 많은 정보 수집, 비교 -&gt; 구매가지 걸리는 시간 많음</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">-High Fidelity WireFrame: 고품질 와이어 프레임 -&gt; </x:t>
+  </x:si>
+  <x:si>
+    <x:t>=&gt; 예쁘기 때문에, 더 비싸도 살거야! =&gt; 가격의 합리적이게 다가오것</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) Price 전략 (해당 브랜드, 상품은 어떤 가격대에 포지셔닝 인식)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유튜브 내 쇼츠 카테고리 노출되는 광고. 60ch 이하. 세로 형태 타입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3) Place 전략(어디에서 어ᄄᅠᇂ게 소비자의 경험을 제공할 것인가)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 경쟁업체의 현 판매가를 가장 높은 비중으로 반영하여 Price전략 구축</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; 주간 구매 사용자수(Weekly Purchasing Users) 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 이전에 온라인으로 출근룩 구매 -&gt; 생각보다 저품질, 소재,주변반응 별로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>출근룩 고민때문에 아침시간이 부족했다면 
+지금바로 스타일 추천 받아보세요</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">- 위에서 발견한 고객 성향에 따른 자사 경쟁력 &amp; 개선할 부분까지 나열 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt;GTM활용 10,25,50,75,90  세부적인 스크롤 깊이 단위까지 확인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 스크롤 깊이(Scroll Depth) 50% 이상 도달률 40% 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리뉴얼 전략 &gt; 기존브랜드 리뉴얼 vs 자매 브랜드런칭(-&gt;엄브렐러 전략)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1) 메세지 유형 (키워드 분류) 다르게 A/B</x:t>
+  </x:si>
+  <x:si>
     <x:r>
       <x:rPr>
         <x:rFont val="맑은 고딕"/>
         <x:sz val="11"/>
-        <x:color rgb="ff000000"/>
+        <x:color rgb="ffff0000"/>
         <x:b val="1"/>
       </x:rPr>
-      <x:t>&gt; Segmentation A(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="맑은 고딕"/>
-        <x:sz val="11"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>트랜드 탐색, 검색 선호하는 유형)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>- 소비성향 : 합리적이고 가성비있는 소비 지향/ 가격대비 활용도 중요/ 브랜드 이름보다는 스타일링 및 코디 관심</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> &gt;Primary Target</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 나이 : 31세</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9. Persona</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- Pain Point:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>* 가성비(가격 민감성) &amp; 품질 어느정도 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-          <x:rPr hs:extension="1">
-            <x:rFont val="맑은 고딕"/>
-            <x:sz val="11"/>
-            <x:color rgb="ffff0000"/>
-            <x:b val="1"/>
-            <hs:size val="100"/>
-            <hs:ratio val="100"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:rPr>
-        </mc:Choice>
-        <mc:Fallback>
-          <x:rPr>
-            <x:rFont val="맑은 고딕"/>
-            <x:sz val="11"/>
-            <x:color rgb="ffff0000"/>
-            <x:b val="1"/>
-          </x:rPr>
-        </mc:Fallback>
-      </mc:AlternateContent>
       <x:t xml:space="preserve">&gt; Segment B </x:t>
     </x:r>
     <x:r>
@@ -995,135 +2178,231 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>- 컨텐츠 만족에 따른 구매전환율 높음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- Solution:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 합리적 소비를 위한 상품비교가 익숙한 25-34 직장인 여성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; SKU 부족: 상품 다양성 부족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최종카드= WT전략: 약점을 개선해서 시장의 위협요소에 최대한 덜 노출시키겠다는 전략</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 다양한 플랫폼 대비, 직장인 출근룩을 디테일하게 큐레이션하는 플랫폼, 서비스 부재</x:t>
-  </x:si>
-  <x:si>
-    <x:t>* 재방문 유입 확률 높음</x:t>
+    <x:t>&gt; 단순 상품을 판매하는 것이 아닌 경험을 판매</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-비즈니스 포트폴리오 최대 2개까지 생성 가능</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다시는 마주하고 싶지 않다.
+꼭 다시 오고 싶다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>처음 구매를 하려고 하는데, 실패하지 않을까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>⇒ 방문을통해서 구매전환까지 매력도(설들력) 약함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- SNS 광고 통해서 유입한 고객 (대부분)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 우리 홈페이지의 인기상품군들의 구매비중 50%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-상품 구매후 만족시, 재구매 가능성이 매우 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 목적에 따른 특정 아이템 빠르게 검색 후 구매</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 평균 주문 구매금액 7만원 유지(평균객단가)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; Google Form / Naver Form</x:t>
+  </x:si>
+  <x:si>
+    <x:t>현실적인 주제, 실현가능한 프로젝트인지 파악</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 상품 공유하기 버튼 클릭율 3% 이상 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Objective: 실질적 상품 구매전환률 향상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>* 가성비(가격 민감성) &amp; 품질 어느정도 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-리뷰가 존재x, 할인 비시즌 거의 활동 전무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 4계절 존재 -&gt; 시즌 트랜드가 빠르게 흘러감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; Returning User = Visiors</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">- 핀터레스트, 인스타그램, 구글링, 해외사이트 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; New Product Development</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 가격보다 상품,브랜드 ,플랫폼 이미지 중요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ST전략: 강점을 활용한 시장의 위협요소 방어전략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-가격대비 만족도 높아야하는 고객 = 가성비 추구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; User id &gt; Avg order value</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; 감성설득 -&gt; 죽어도 이 브랜드 상품 선텍</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자체적인 유튜브 채널 &gt; 구독자수 증가를 위함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 유입경로 채널: 인스타그램, 틱톡, 유트브</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 상품 조회하는데 소요하는 시간 = 체류시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. Owned media =&gt; 브랜드 인지도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-단순히 광고소재를 여러개 만들어서 지밴한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. GTM을 통해서 사용자 방문 트래픽 수집</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. GTM운 해당 수집 데이터를 GA4에 전달</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ex) 왼쪽 상단:로고/ 우측상단: 로그인 버튼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>*브랜드 헤드라인 사전 정의(브랜드 정체성 강조)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 브랜드 및 기업이 직접 소유, 관리하는 매체</x:t>
+  </x:si>
+  <x:si>
+    <x:t>모든 것을 내가 직접 맞춤으로 광고캠페인 세팅</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-전혀 관리가 불가능한 제3의 커뮤니티 영역</x:t>
+  </x:si>
+  <x:si>
+    <x:t>랜딩페이지 유입.접속 증대를 위한 광고 캠페인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) 자체적인 유튜브 공식 채널 계정 운영관리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. Paid Media =&gt; 대중과의 접점 용이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동영상 등의 동적 컨텐츠를 조회할깨 과듬방식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구글 외 구글 제휴 사이트 내 광고 캠페인 집행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Paid Media (최초 신규 고객 유입)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">- 앞 단계에서 도출된 사용자 정보를 기반으로 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; 직관적: 매출 영업이익 결과 바로 도출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소비자들에게 최대한 많이 광고를 노출하고자 할때</x:t>
+  </x:si>
+  <x:si>
+    <x:t>건너뛸 수 없는 30초 인스트림 광고 (CPM)</x:t>
   </x:si>
   <x:si>
     <x:r>
-      <x:t>&gt;Secondary Target</x:t>
+      <x:t xml:space="preserve">&gt; 어떤 홈페이지에 접속, </x:t>
     </x:r>
-  </x:si>
-  <x:si>
-    <x:t>- 트랜드 패션에 관심이 높은 2530 프리랜서 여성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 트랜드 민감, SNS검색 후 비교 및 자기개성 어필</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-구체적인 브랜드 혹은 상품 슬로건(Just do it, nothing is impossible)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 컨텐츠 기획 기본 방향 수립（광고 톤앤매너, 배경컬러, 웹사이트 메인베너, 상세페이지, CRM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11. NPD</x:t>
-  </x:si>
-  <x:si>
     <x:r>
-      <x:t>T-Threat (위협)</x:t>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+        <x:b val="1"/>
+      </x:rPr>
+      <x:t>탐색 중심소비패턴</x:t>
     </x:r>
   </x:si>
   <x:si>
-    <x:t>&gt; 직장인을 위한 합리적인 데일리룩 큐레이션 쇼핑몰</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2순위: Retention</x:t>
-  </x:si>
-  <x:si>
     <x:r>
-      <x:t>10. SWOT</x:t>
+      <x:t xml:space="preserve">&gt; </x:t>
     </x:r>
-  </x:si>
-  <x:si>
     <x:r>
-      <x:t>O-Opportunity (기회)</x:t>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+        <x:b val="1"/>
+      </x:rPr>
+      <x:t>즉각 결정 보류 + 재방문시 구매결정 성향</x:t>
     </x:r>
   </x:si>
   <x:si>
-    <x:t>&gt; 직장인 코디네이션 및 큐레이팅 최대한 어필될 수 있는 컨텐츠</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 성.비수기 존재</x:t>
-  </x:si>
-  <x:si>
-    <x:t>: 어떤 강점을 어필하고, 어떤 약점을 빠르게 보완할 것이며, 어떤 타이밍에 좋은 기회를 포착할 것인가, 최악의 리스크를 어떻게하면 피할 수 있을까?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-&gt; 생존과 가장 밀접</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">&gt; 자사 자산을 스캔, 검색, 조회를 통해 인지 +리뷰 데이터 조회 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 기술력, 가격, 가성비, 컨텐츠</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-&gt; 2인자의 전략</x:t>
-  </x:si>
-  <x:si>
     <x:r>
-      <x:t>S- Strength (강점)</x:t>
+      <x:t>&gt;</x:t>
     </x:r>
-  </x:si>
-  <x:si>
-    <x:t>ST전략: 강점을 활용한 시장의 위협요소 방어전략</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; New Product Development</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 가성비 : 원가 절감 // 대량생산</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 가격 경쟁 치열 - 출혈경쟁으로 인한 사업성 악화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SO전략: 강점을 활용한 시장의 기회요소를 포착하겠다는 전략</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 중국산 값싼 브랜드,플랫폼의 국내 진출</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-&gt; 약점대비 현재 업종의 활황기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Objective: 실질적 상품 구매전환률 향상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 국내 소비자 트랜드 &amp; 대중심리 민감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WO전략: 약점의 개선으로 시장의 기회요소를 최대한 활용하겠다는 전략</x:t>
-  </x:si>
-  <x:si>
-    <x:t>*각 전략마다 3-5개 정도 수립</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">- 지금 당장 고객들이 원하는 니즈 파악 + 장기적인 방향? </x:t>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+        <x:b val="1"/>
+      </x:rPr>
+      <x:t>가격민감+ 가치추구 혼합형</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 출근 준비 시간을 줄이는 스타일 추천!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A/B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>=-CTA=Call To Action=사용자로 하여금 무언가의 액션을 불러일으키게 하는 요소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"지금 스타일 확인하기"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3) 리뷰 강조 A/B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4) CTA 문구 테스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"AI 스타일 추천받기"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 일상에서의 출근 상황</x:t>
+  </x:si>
+  <x:si>
+    <x:t>=-가설기반 반드시 테스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A 일상에서의 라이프스타일 연상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) 이미지 스타일 다르게 A/B</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="19">
+  <x:fonts count="20">
     <x:font>
       <x:name val="맑은 고딕"/>
       <x:sz val="11"/>
@@ -1176,26 +2455,11 @@
       <x:sz val="12"/>
       <x:color rgb="ff000000"/>
     </x:font>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Arial"/>
-          <x:sz val="18"/>
-          <x:color rgb="ff000000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Arial"/>
-          <x:sz val="18"/>
-          <x:color rgb="ff000000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
+    <x:font>
+      <x:name val="Arial"/>
+      <x:sz val="18"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:font hs:extension="1">
@@ -1213,28 +2477,6 @@
           <x:name val="맑은 고딕"/>
           <x:sz val="14"/>
           <x:color rgb="ffff0000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="맑은 고딕"/>
-          <x:sz val="11"/>
-          <x:color rgb="ffff0000"/>
-          <x:b val="1"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="맑은 고딕"/>
-          <x:sz val="11"/>
-          <x:color rgb="ffff0000"/>
-          <x:b val="1"/>
         </x:font>
       </mc:Fallback>
     </mc:AlternateContent>
@@ -1369,13 +2611,79 @@
         </x:font>
       </mc:Fallback>
     </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="맑은 고딕"/>
+          <x:sz val="13"/>
+          <x:color rgb="ff000000"/>
+          <x:b val="1"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="맑은 고딕"/>
+          <x:sz val="13"/>
+          <x:color rgb="ff000000"/>
+          <x:b val="1"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Arial"/>
+          <x:sz val="10"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Arial"/>
+          <x:sz val="10"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
   </x:fonts>
-  <x:fills count="2">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="ffe7e6e6"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="ffffff00"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="fffaf3db"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="ffffb689"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
     </x:fill>
   </x:fills>
   <x:borders count="2">
@@ -1416,7 +2724,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="44">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -1522,6 +2830,91 @@
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="1" applyFill="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="1" applyFill="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="1" applyFill="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" hs:applyExtension="1">
@@ -1535,44 +2928,14 @@
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <x:alignment horizontal="general" vertical="center"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <x:alignment horizontal="general" vertical="center"/>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <x:alignment horizontal="general" vertical="center"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -1981,6 +3344,49 @@
 </x:styleSheet>
 </file>
 
+<file path=xl/drawings/drawing0.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic macro="" fPublished="0">
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2743200" y="5867400"/>
+          <a:ext cx="2638425" cy="1990725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="1" fPrintsWithSheet="1"/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office 테마">
   <a:themeElements>
@@ -2243,36 +3649,36 @@
   <x:sheetData>
     <x:row r="8" spans="3:3">
       <x:c r="C8" t="s">
-        <x:v>104</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="3:3">
       <x:c r="C9" t="s">
-        <x:v>45</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:3">
       <x:c r="C11" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>353</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="3:3">
       <x:c r="C12" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="3:3">
       <x:c r="C13" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="3:3">
       <x:c r="C14" s="3" t="s">
-        <x:v>215</x:v>
+        <x:v>641</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69972223043441772461" right="0.69972223043441772461" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
@@ -2284,170 +3690,170 @@
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
   <x:sheetData>
     <x:row r="6" spans="3:3" ht="22.05000000000000071054">
-      <x:c r="C6" s="28" t="s">
-        <x:v>267</x:v>
+      <x:c r="C6" s="27" t="s">
+        <x:v>475</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="3:3">
       <x:c r="C7" t="s">
-        <x:v>271</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="3:3">
-      <x:c r="C9" s="16" t="s">
-        <x:v>276</x:v>
+      <x:c r="C9" s="15" t="s">
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:3">
       <x:c r="C10" t="s">
-        <x:v>274</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:3">
       <x:c r="C11" t="s">
-        <x:v>273</x:v>
+        <x:v>354</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="15:17">
-      <x:c r="O12" s="19"/>
-      <x:c r="P12" s="19"/>
-      <x:c r="Q12" s="19"/>
+      <x:c r="O12" s="18"/>
+      <x:c r="P12" s="18"/>
+      <x:c r="Q12" s="18"/>
     </x:row>
     <x:row r="13" spans="3:17">
-      <x:c r="C13" s="16" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="O13" s="19"/>
-      <x:c r="P13" s="19"/>
-      <x:c r="Q13" s="19"/>
+      <x:c r="C13" s="15" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="O13" s="18"/>
+      <x:c r="P13" s="18"/>
+      <x:c r="Q13" s="18"/>
     </x:row>
     <x:row r="14" spans="3:17">
       <x:c r="C14" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="O14" s="19"/>
-      <x:c r="P14" s="19"/>
-      <x:c r="Q14" s="19"/>
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="O14" s="18"/>
+      <x:c r="P14" s="18"/>
+      <x:c r="Q14" s="18"/>
     </x:row>
     <x:row r="15" spans="3:17">
       <x:c r="C15" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="O15" s="19"/>
-      <x:c r="P15" s="19"/>
-      <x:c r="Q15" s="19"/>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="O15" s="18"/>
+      <x:c r="P15" s="18"/>
+      <x:c r="Q15" s="18"/>
     </x:row>
     <x:row r="16" spans="3:17">
       <x:c r="C16" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="O16" s="19"/>
-      <x:c r="P16" s="19"/>
-      <x:c r="Q16" s="19"/>
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="O16" s="18"/>
+      <x:c r="P16" s="18"/>
+      <x:c r="Q16" s="18"/>
     </x:row>
     <x:row r="17" spans="15:17">
-      <x:c r="O17" s="19"/>
-      <x:c r="P17" s="19"/>
-      <x:c r="Q17" s="19"/>
+      <x:c r="O17" s="18"/>
+      <x:c r="P17" s="18"/>
+      <x:c r="Q17" s="18"/>
     </x:row>
     <x:row r="18" spans="3:17">
-      <x:c r="C18" s="16" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="O18" s="19"/>
-      <x:c r="P18" s="19"/>
-      <x:c r="Q18" s="19"/>
+      <x:c r="C18" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="O18" s="18"/>
+      <x:c r="P18" s="18"/>
+      <x:c r="Q18" s="18"/>
     </x:row>
     <x:row r="19" spans="3:17">
       <x:c r="C19" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="O19" s="19"/>
-      <x:c r="P19" s="19"/>
-      <x:c r="Q19" s="19"/>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="O19" s="18"/>
+      <x:c r="P19" s="18"/>
+      <x:c r="Q19" s="18"/>
     </x:row>
     <x:row r="20" spans="3:17">
       <x:c r="C20" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="O20" s="19"/>
-      <x:c r="P20" s="19"/>
-      <x:c r="Q20" s="19"/>
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="O20" s="18"/>
+      <x:c r="P20" s="18"/>
+      <x:c r="Q20" s="18"/>
     </x:row>
     <x:row r="21" spans="15:17">
-      <x:c r="O21" s="19"/>
-      <x:c r="P21" s="19"/>
-      <x:c r="Q21" s="19"/>
+      <x:c r="O21" s="18"/>
+      <x:c r="P21" s="18"/>
+      <x:c r="Q21" s="18"/>
     </x:row>
     <x:row r="22" spans="3:3">
-      <x:c r="C22" s="16" t="s">
-        <x:v>264</x:v>
+      <x:c r="C22" s="15" t="s">
+        <x:v>400</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="3:3">
       <x:c r="C23" t="s">
-        <x:v>282</x:v>
+        <x:v>586</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="3:3">
       <x:c r="C24" t="s">
-        <x:v>280</x:v>
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="3:3">
       <x:c r="C25" t="s">
-        <x:v>285</x:v>
+        <x:v>562</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="3:3">
       <x:c r="C26" t="s">
-        <x:v>220</x:v>
+        <x:v>653</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="3:3">
       <x:c r="C27" t="s">
-        <x:v>270</x:v>
+        <x:v>441</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="3:3">
       <x:c r="C30" t="s">
-        <x:v>287</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="3:12">
       <x:c r="C31" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="L31" s="21" t="s">
-        <x:v>226</x:v>
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="L31" s="20" t="s">
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="3:12">
       <x:c r="C32" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="L32" s="21" t="s">
-        <x:v>275</x:v>
+        <x:v>658</x:v>
+      </x:c>
+      <x:c r="L32" s="20" t="s">
+        <x:v>440</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="3:12">
       <x:c r="C33" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="L33" s="21" t="s">
-        <x:v>283</x:v>
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="L33" s="20" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="3:12">
       <x:c r="C34" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="L34" s="21" t="s">
-        <x:v>272</x:v>
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="L34" s="20" t="s">
+        <x:v>405</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
@@ -2459,42 +3865,1392 @@
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
   <x:sheetData>
     <x:row r="3" spans="3:3" ht="22.05000000000000071054">
-      <x:c r="C3" s="28" t="s">
-        <x:v>263</x:v>
+      <x:c r="C3" s="27" t="s">
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="3:3">
       <x:c r="C4" t="s">
-        <x:v>278</x:v>
+        <x:v>656</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="3:3">
       <x:c r="C5" t="s">
-        <x:v>18</x:v>
+        <x:v>609</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="3:3">
       <x:c r="C7" t="s">
-        <x:v>5</x:v>
+        <x:v>386</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="3:3">
-      <x:c r="C8" s="21" t="s">
-        <x:v>58</x:v>
+      <x:c r="C8" s="20" t="s">
+        <x:v>612</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:3">
       <x:c r="C10" t="s">
-        <x:v>229</x:v>
+        <x:v>390</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:3">
-      <x:c r="C11" s="21" t="s">
-        <x:v>288</x:v>
+      <x:c r="C11" s="20" t="s">
+        <x:v>194</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69972223043441772461" right="0.69972223043441772461" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet12"/>
+  <x:dimension ref="C4:L38"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
+  <x:cols>
+    <x:col min="3" max="3" width="15.75" customWidth="1"/>
+    <x:col min="4" max="4" width="29.23046875" bestFit="1" customWidth="1"/>
+    <x:col min="5" max="5" width="20.12109375" bestFit="1" customWidth="1"/>
+    <x:col min="6" max="6" width="28.8515625" bestFit="1" customWidth="1"/>
+    <x:col min="8" max="8" width="20.12109375" bestFit="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="4" spans="3:3">
+      <x:c r="C4" t="s">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="3:3">
+      <x:c r="C5" s="20" t="s">
+        <x:v>429</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="3:3">
+      <x:c r="C6" s="20" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="3:3">
+      <x:c r="C7" s="20" t="s">
+        <x:v>568</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="3:3">
+      <x:c r="C8" s="20" t="s">
+        <x:v>162</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="3:3">
+      <x:c r="C12" s="18" t="s">
+        <x:v>425</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="3:12">
+      <x:c r="C14" s="28" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D14" s="28" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="E14" s="28" t="s">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="F14" s="28" t="s">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="G14" s="28" t="s">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="H14" s="28" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="I14" s="28"/>
+      <x:c r="J14" s="29" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="K14" s="29" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="L14" s="29" t="s">
+        <x:v>538</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="3:10">
+      <x:c r="C15" s="18" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="E15" s="18" t="s">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="F15" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G15" s="18" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="H15" s="18" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="I15" s="18" t="s">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="J15" t="s">
+        <x:v>560</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="3:9">
+      <x:c r="C16" s="18"/>
+      <x:c r="D16" s="18" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E16" s="18" t="s">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="F16" s="18"/>
+      <x:c r="G16" s="18"/>
+      <x:c r="H16" s="18" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="I16" s="18" t="s">
+        <x:v>534</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="3:9">
+      <x:c r="C17" s="18"/>
+      <x:c r="D17" s="18" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="E17" s="18"/>
+      <x:c r="F17" s="18"/>
+      <x:c r="G17" s="18"/>
+      <x:c r="H17" s="18" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="I17" s="18" t="s">
+        <x:v>559</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="3:9">
+      <x:c r="C18" s="18" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E18" s="18"/>
+      <x:c r="F18" s="18"/>
+      <x:c r="G18" s="18"/>
+      <x:c r="H18" s="18"/>
+      <x:c r="I18" s="18"/>
+    </x:row>
+    <x:row r="19" spans="3:9">
+      <x:c r="C19" s="18"/>
+      <x:c r="D19" s="18" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="E19" s="18"/>
+      <x:c r="F19" s="18"/>
+      <x:c r="G19" s="18"/>
+      <x:c r="H19" s="18"/>
+      <x:c r="I19" s="18"/>
+    </x:row>
+    <x:row r="20" spans="3:9">
+      <x:c r="C20" s="18"/>
+      <x:c r="D20" s="18" t="s">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="E20" s="18"/>
+      <x:c r="F20" s="18"/>
+      <x:c r="G20" s="18"/>
+      <x:c r="H20" s="18"/>
+      <x:c r="I20" s="18"/>
+    </x:row>
+    <x:row r="21" spans="3:9">
+      <x:c r="C21" s="18" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="D21" s="18" t="s">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="E21" s="18"/>
+      <x:c r="F21" s="18"/>
+      <x:c r="G21" s="18"/>
+      <x:c r="H21" s="18"/>
+      <x:c r="I21" s="18"/>
+    </x:row>
+    <x:row r="22" spans="3:9">
+      <x:c r="C22" s="18"/>
+      <x:c r="D22" s="18" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="E22" s="18"/>
+      <x:c r="F22" s="18"/>
+      <x:c r="G22" s="18"/>
+      <x:c r="H22" s="18"/>
+      <x:c r="I22" s="18"/>
+    </x:row>
+    <x:row r="23" spans="3:9">
+      <x:c r="C23" s="18"/>
+      <x:c r="D23" s="18" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E23" s="18"/>
+      <x:c r="F23" s="18"/>
+      <x:c r="G23" s="18"/>
+      <x:c r="H23" s="18"/>
+      <x:c r="I23" s="18"/>
+    </x:row>
+    <x:row r="24" spans="3:9">
+      <x:c r="C24" s="18" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="D24" s="18" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="E24" s="18"/>
+      <x:c r="F24" s="18"/>
+      <x:c r="G24" s="18"/>
+      <x:c r="H24" s="18"/>
+      <x:c r="I24" s="18"/>
+    </x:row>
+    <x:row r="25" spans="3:9">
+      <x:c r="C25" s="18"/>
+      <x:c r="D25" s="18" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E25" s="18"/>
+      <x:c r="F25" s="18"/>
+      <x:c r="G25" s="18"/>
+      <x:c r="H25" s="18"/>
+      <x:c r="I25" s="18"/>
+    </x:row>
+    <x:row r="26" spans="3:9">
+      <x:c r="C26" s="18"/>
+      <x:c r="D26" s="18" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="E26" s="18"/>
+      <x:c r="F26" s="18"/>
+      <x:c r="G26" s="18"/>
+      <x:c r="H26" s="18"/>
+      <x:c r="I26" s="18"/>
+    </x:row>
+    <x:row r="27" spans="3:9">
+      <x:c r="C27" s="18"/>
+      <x:c r="D27" s="18" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="E27" s="18"/>
+      <x:c r="F27" s="18"/>
+      <x:c r="G27" s="18"/>
+      <x:c r="H27" s="18"/>
+      <x:c r="I27" s="18"/>
+    </x:row>
+    <x:row r="28" spans="3:9">
+      <x:c r="C28" s="18"/>
+      <x:c r="D28" s="18" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="E28" s="18"/>
+      <x:c r="F28" s="18"/>
+      <x:c r="G28" s="18"/>
+      <x:c r="H28" s="18"/>
+      <x:c r="I28" s="18"/>
+    </x:row>
+    <x:row r="31" spans="3:9">
+      <x:c r="C31" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="H31" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="I31" t="s">
+        <x:v>145</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="3:3">
+      <x:c r="C35" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="3:3">
+      <x:c r="C36" t="s">
+        <x:v>648</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="3:3">
+      <x:c r="C37" t="s">
+        <x:v>343</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="3:3">
+      <x:c r="C38" t="s">
+        <x:v>137</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet13"/>
+  <x:dimension ref="C4:G52"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
+  <x:sheetData>
+    <x:row r="4" spans="3:3">
+      <x:c r="C4" t="s">
+        <x:v>130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="3:3">
+      <x:c r="C5" s="20" t="s">
+        <x:v>336</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="3:3">
+      <x:c r="C7" t="s">
+        <x:v>165</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="3:3">
+      <x:c r="C8" s="20" t="s">
+        <x:v>637</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="3:3">
+      <x:c r="C9" s="20" t="s">
+        <x:v>114</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="3:3">
+      <x:c r="C10" s="20" t="s">
+        <x:v>614</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="3:3">
+      <x:c r="C11" s="20" t="s">
+        <x:v>339</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="3:3">
+      <x:c r="C12" s="20" t="s">
+        <x:v>207</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="4:4">
+      <x:c r="D13" s="21" t="s">
+        <x:v>273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="4:4">
+      <x:c r="D14" s="20" t="s">
+        <x:v>579</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="5:5">
+      <x:c r="E15" s="20" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="5:5">
+      <x:c r="E16" s="20" t="s">
+        <x:v>301</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="5:5">
+      <x:c r="E17" s="20" t="s">
+        <x:v>664</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="5:5">
+      <x:c r="E18" s="20" t="s">
+        <x:v>382</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="3:3">
+      <x:c r="C20" t="s">
+        <x:v>624</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="3:3">
+      <x:c r="C21" s="20" t="s">
+        <x:v>453</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="3:3">
+      <x:c r="C22" s="20" t="s">
+        <x:v>627</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="4:4">
+      <x:c r="D23" s="20" t="s">
+        <x:v>340</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="4:4">
+      <x:c r="D24" s="20" t="s">
+        <x:v>361</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="5:5">
+      <x:c r="E25" s="20" t="s">
+        <x:v>623</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="5:5">
+      <x:c r="E26" t="s">
+        <x:v>585</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="3:3">
+      <x:c r="C27" s="20" t="s">
+        <x:v>350</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="3:3">
+      <x:c r="C28" s="20" t="s">
+        <x:v>371</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="3:3">
+      <x:c r="C29" s="20" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="3:3">
+      <x:c r="C30" s="20" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="3:3">
+      <x:c r="C31" s="20" t="s">
+        <x:v>661</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="3:3">
+      <x:c r="C32" s="20" t="s">
+        <x:v>294</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="3:7">
+      <x:c r="C33" s="21" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="D33" s="18"/>
+      <x:c r="E33" s="18"/>
+      <x:c r="F33" s="18"/>
+      <x:c r="G33" s="18"/>
+    </x:row>
+    <x:row r="34" spans="3:7">
+      <x:c r="C34" s="18" t="s">
+        <x:v>532</x:v>
+      </x:c>
+      <x:c r="D34" s="21" t="s">
+        <x:v>681</x:v>
+      </x:c>
+      <x:c r="E34" s="18"/>
+      <x:c r="F34" s="18"/>
+      <x:c r="G34" s="18"/>
+    </x:row>
+    <x:row r="35" spans="3:7">
+      <x:c r="C35" s="18"/>
+      <x:c r="D35" s="21" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="E35" s="18"/>
+      <x:c r="F35" s="18"/>
+      <x:c r="G35" s="18"/>
+    </x:row>
+    <x:row r="37" spans="3:3">
+      <x:c r="C37" t="s">
+        <x:v>626</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="3:3">
+      <x:c r="C38" s="20" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="3:3">
+      <x:c r="C39" s="20" t="s">
+        <x:v>437</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="3:3">
+      <x:c r="C40" t="s">
+        <x:v>210</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="3:3">
+      <x:c r="C41" s="20" t="s">
+        <x:v>160</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="3:3">
+      <x:c r="C42" s="20" t="s">
+        <x:v>663</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="3:3">
+      <x:c r="C43" s="20" t="s">
+        <x:v>169</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="3:3">
+      <x:c r="C44" s="20"/>
+    </x:row>
+    <x:row r="45" spans="3:3">
+      <x:c r="C45" s="20"/>
+    </x:row>
+    <x:row r="47" spans="3:3">
+      <x:c r="C47" t="s">
+        <x:v>362</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="3:3">
+      <x:c r="C48" s="20" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="3:3">
+      <x:c r="C49" s="20" t="s">
+        <x:v>597</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="3:3">
+      <x:c r="C50" s="20" t="s">
+        <x:v>147</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="4:4">
+      <x:c r="D51" s="20" t="s">
+        <x:v>166</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="4:4">
+      <x:c r="D52" s="20" t="s">
+        <x:v>268</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet14"/>
+  <x:dimension ref="C4:D19"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
+  <x:cols>
+    <x:col min="3" max="3" width="16.125" customWidth="1"/>
+    <x:col min="4" max="4" width="17.25" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="4" spans="3:3">
+      <x:c r="C4" t="s">
+        <x:v>123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="3:3">
+      <x:c r="C5" s="20" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="3:3">
+      <x:c r="C6" s="20" t="s">
+        <x:v>209</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="3:3">
+      <x:c r="C7" s="20" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="3:3">
+      <x:c r="C8" s="20" t="s">
+        <x:v>436</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="3:3">
+      <x:c r="C9" s="20" t="s">
+        <x:v>439</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="3:3">
+      <x:c r="C12" s="30" t="s">
+        <x:v>547</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="3:3">
+      <x:c r="C13" s="30" t="s">
+        <x:v>544</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="3:3">
+      <x:c r="C14" s="30" t="s">
+        <x:v>529</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="3:3">
+      <x:c r="C15" s="30" t="s">
+        <x:v>527</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="3:3">
+      <x:c r="C16" t="s">
+        <x:v>634</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="3:4">
+      <x:c r="C17" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D17" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="3:4">
+      <x:c r="C18" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="D18" t="s">
+        <x:v>459</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="4:4">
+      <x:c r="D19" t="s">
+        <x:v>528</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet15"/>
+  <x:dimension ref="C4:M95"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
+  <x:cols>
+    <x:col min="3" max="3" width="16.75" customWidth="1"/>
+    <x:col min="8" max="8" width="42.21484375" bestFit="1" customWidth="1"/>
+    <x:col min="10" max="10" width="54.6875" bestFit="1" customWidth="1"/>
+    <x:col min="12" max="12" width="21.49609375" bestFit="1" customWidth="1"/>
+    <x:col min="13" max="13" width="45.75" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="4" spans="3:3" ht="22.05000000000000071054">
+      <x:c r="C4" s="27" t="s">
+        <x:v>407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="3:3">
+      <x:c r="C5" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="3:3">
+      <x:c r="C6" s="20" t="s">
+        <x:v>355</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="4:4">
+      <x:c r="D7" s="18" t="s">
+        <x:v>203</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="4:4">
+      <x:c r="D8" s="18" t="s">
+        <x:v>351</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="4:4">
+      <x:c r="D9" s="18" t="s">
+        <x:v>451</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="4:4">
+      <x:c r="D10" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="3:3">
+      <x:c r="C12" s="31" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="3:3">
+      <x:c r="C13" t="s">
+        <x:v>277</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="3:3">
+      <x:c r="C14" t="s">
+        <x:v>284</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="4:4">
+      <x:c r="D15" s="20" t="s">
+        <x:v>219</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="3:3">
+      <x:c r="C16" t="s">
+        <x:v>271</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="4:4">
+      <x:c r="D17" t="s">
+        <x:v>379</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="3:3">
+      <x:c r="C20" t="s">
+        <x:v>395</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="3:3">
+      <x:c r="C21" t="s">
+        <x:v>431</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="3:3">
+      <x:c r="C22" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="4:4">
+      <x:c r="D23" t="s">
+        <x:v>620</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="4:4">
+      <x:c r="D24" t="s">
+        <x:v>267</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="3:3" ht="19.25">
+      <x:c r="C26" s="32" t="s">
+        <x:v>144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="3:5">
+      <x:c r="C27" t="s">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="E27" t="s">
+        <x:v>182</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="3:5">
+      <x:c r="C28" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="E28" t="s">
+        <x:v>588</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="3:5">
+      <x:c r="C29" t="s">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="E29" t="s">
+        <x:v>222</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="3:5">
+      <x:c r="C30" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="E30" t="s">
+        <x:v>213</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="3:3" ht="19.25">
+      <x:c r="C32" s="32" t="s">
+        <x:v>450</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="3:3">
+      <x:c r="C33" s="23" t="s">
+        <x:v>484</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="3:3">
+      <x:c r="C34" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="3:3">
+      <x:c r="C35" t="s">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="3:3">
+      <x:c r="C36" t="s">
+        <x:v>581</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="3:3">
+      <x:c r="C37" t="s">
+        <x:v>357</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="3:3">
+      <x:c r="C39" s="31" t="s">
+        <x:v>108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="3:3">
+      <x:c r="C40" t="s">
+        <x:v>359</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="3:3">
+      <x:c r="C41" t="s">
+        <x:v>212</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="3:3">
+      <x:c r="C42" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="3:3">
+      <x:c r="C43" t="s">
+        <x:v>215</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="3:3">
+      <x:c r="C45" t="s">
+        <x:v>432</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="3:3">
+      <x:c r="C46" t="s">
+        <x:v>448</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="3:3">
+      <x:c r="C47" t="s">
+        <x:v>564</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="3:3">
+      <x:c r="C48" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="3:3">
+      <x:c r="C49" t="s">
+        <x:v>570</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="3:3">
+      <x:c r="C51" t="s">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="3:3">
+      <x:c r="C52" t="s">
+        <x:v>602</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="3:3">
+      <x:c r="C53" t="s">
+        <x:v>603</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="3:3">
+      <x:c r="C56" s="23" t="s">
+        <x:v>389</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="3:3">
+      <x:c r="C58" s="18" t="s">
+        <x:v>541</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="3:3">
+      <x:c r="C59" s="18" t="s">
+        <x:v>102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="3:3">
+      <x:c r="C60" s="18" t="s">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="3:3">
+      <x:c r="C61" s="18" t="s">
+        <x:v>134</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="3:4">
+      <x:c r="C62" s="18" t="s">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="D62" s="18" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="3:3">
+      <x:c r="C64" t="s">
+        <x:v>373</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="3:3">
+      <x:c r="C65" t="s">
+        <x:v>498</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="3:3">
+      <x:c r="C66" t="s">
+        <x:v>464</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="3:3">
+      <x:c r="C67" t="s">
+        <x:v>224</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="3:3">
+      <x:c r="C69" t="s">
+        <x:v>461</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="3:3">
+      <x:c r="C70" t="s">
+        <x:v>550</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="3:3">
+      <x:c r="C71" t="s">
+        <x:v>214</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="3:3">
+      <x:c r="C73" t="s">
+        <x:v>141</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="3:3">
+      <x:c r="C74" t="s">
+        <x:v>594</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="3:3">
+      <x:c r="C75" t="s">
+        <x:v>573</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="3:3">
+      <x:c r="C77" t="s">
+        <x:v>94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="3:3">
+      <x:c r="C78" t="s">
+        <x:v>601</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="3:3">
+      <x:c r="C79" t="s">
+        <x:v>218</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="3:13">
+      <x:c r="C84" s="18" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="H84" s="29" t="s">
+        <x:v>670</x:v>
+      </x:c>
+      <x:c r="I84" s="29"/>
+      <x:c r="J84" s="28" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="K84" s="29"/>
+      <x:c r="L84" s="28" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="M84" s="29" t="s">
+        <x:v>367</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="3:13" ht="31.5" customHeight="1">
+      <x:c r="C85" s="18" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="H85" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="J85" s="18" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="L85" s="18" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="M85" s="33" t="s">
+        <x:v>246</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="3:13" ht="32.75">
+      <x:c r="C86" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="H86" t="s">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="J86" s="18" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="L86" s="18" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="M86" s="33" t="s">
+        <x:v>630</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="3:13" ht="32.75">
+      <x:c r="C87" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="H87" t="s">
+        <x:v>598</x:v>
+      </x:c>
+      <x:c r="J87" s="18" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="L87" s="18" t="s">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="M87" s="33" t="s">
+        <x:v>216</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="3:12">
+      <x:c r="C88" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="L88" s="18" t="s">
+        <x:v>413</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="3:3">
+      <x:c r="C89" t="s">
+        <x:v>434</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="3:3">
+      <x:c r="C90" t="s">
+        <x:v>73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="3:3">
+      <x:c r="C91" t="s">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="3:3">
+      <x:c r="C92" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="3:3">
+      <x:c r="C93" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="3:3">
+      <x:c r="C95" t="s">
+        <x:v>158</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet16"/>
+  <x:dimension ref="C5:C9"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
+  <x:sheetData>
+    <x:row r="5" spans="3:3" ht="22.05000000000000071054">
+      <x:c r="C5" s="27" t="s">
+        <x:v>457</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="3:3">
+      <x:c r="C6" s="20" t="s">
+        <x:v>680</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="3:3">
+      <x:c r="C7" s="20" t="s">
+        <x:v>329</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="3:3">
+      <x:c r="C8" s="20" t="s">
+        <x:v>223</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="3:3">
+      <x:c r="C9" s="20" t="s">
+        <x:v>655</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet18"/>
+  <x:dimension ref="C6:C8"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
+  <x:sheetData>
+    <x:row r="6" spans="3:3">
+      <x:c r="C6" t="s">
+        <x:v>314</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="3:3">
+      <x:c r="C8" s="20" t="s">
+        <x:v>261</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet17"/>
+  <x:dimension ref="C4:D20"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
+  <x:cols>
+    <x:col min="4" max="4" width="72.125" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="4" spans="3:3">
+      <x:c r="C4" t="s">
+        <x:v>458</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="3:3">
+      <x:c r="C6" t="s">
+        <x:v>175</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="3:3">
+      <x:c r="C7" t="s">
+        <x:v>279</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="4:4" ht="32.75">
+      <x:c r="D8" s="34" t="s">
+        <x:v>189</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="3:4" ht="32.75">
+      <x:c r="C9" s="20" t="s">
+        <x:v>622</x:v>
+      </x:c>
+      <x:c r="D9" s="34" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="4:4">
+      <x:c r="D10" s="20" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="3:3">
+      <x:c r="C12" s="18" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="4:4">
+      <x:c r="D13" t="s">
+        <x:v>91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="3:3">
+      <x:c r="C15" s="18" t="s">
+        <x:v>260</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="3:3">
+      <x:c r="C16" s="18" t="s">
+        <x:v>272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="4:4">
+      <x:c r="D17" t="s">
+        <x:v>669</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="3:3">
+      <x:c r="C18" s="18" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="3:3">
+      <x:c r="C19" s="18" t="s">
+        <x:v>252</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="3:3">
+      <x:c r="C20" s="18" t="s">
+        <x:v>452</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet20"/>
+  <x:dimension ref="D6:E29"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
+  <x:cols>
+    <x:col min="4" max="4" width="16.0703125" bestFit="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="6" spans="4:4">
+      <x:c r="D6" t="s">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="4:4">
+      <x:c r="D8" t="s">
+        <x:v>676</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="4:4">
+      <x:c r="D9" s="20" t="s">
+        <x:v>341</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="4:4">
+      <x:c r="D10" t="s">
+        <x:v>208</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="4:4">
+      <x:c r="D12" s="18" t="s">
+        <x:v>665</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="4:4">
+      <x:c r="D13" s="21" t="s">
+        <x:v>671</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="4:4">
+      <x:c r="D14" t="s">
+        <x:v>334</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="4:4">
+      <x:c r="D16" s="18" t="s">
+        <x:v>411</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="4:4">
+      <x:c r="D17" s="20" t="s">
+        <x:v>673</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="4:4">
+      <x:c r="D18" t="s">
+        <x:v>599</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="4:4">
+      <x:c r="D20" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="4:5">
+      <x:c r="D21" t="s">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="E21" s="18" t="s">
+        <x:v>679</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="5:5">
+      <x:c r="E22" s="18"/>
+    </x:row>
+    <x:row r="23" spans="4:5">
+      <x:c r="D23" t="s">
+        <x:v>508</x:v>
+      </x:c>
+      <x:c r="E23" s="18" t="s">
+        <x:v>605</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="5:5">
+      <x:c r="E24" s="18"/>
+    </x:row>
+    <x:row r="25" spans="4:5">
+      <x:c r="D25" t="s">
+        <x:v>546</x:v>
+      </x:c>
+      <x:c r="E25" s="18" t="s">
+        <x:v>205</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="5:5">
+      <x:c r="E26" s="18"/>
+    </x:row>
+    <x:row r="27" spans="4:5">
+      <x:c r="D27" t="s">
+        <x:v>549</x:v>
+      </x:c>
+      <x:c r="E27" s="18" t="s">
+        <x:v>592</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="5:5">
+      <x:c r="E28" s="18"/>
+    </x:row>
+    <x:row r="29" spans="4:5">
+      <x:c r="D29" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="E29" s="18" t="s">
+        <x:v>201</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
@@ -2507,17 +5263,17 @@
   <x:sheetData>
     <x:row r="8" spans="3:3">
       <x:c r="C8" t="s">
-        <x:v>202</x:v>
+        <x:v>572</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="3:3">
       <x:c r="C9" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:3">
       <x:c r="C10" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>628</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:3">
@@ -2530,8 +5286,806 @@
       <x:c r="C13" s="1"/>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69972223043441772461" right="0.69972223043441772461" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet19"/>
+  <x:dimension ref="D5:F28"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
+  <x:cols>
+    <x:col min="4" max="4" width="9.00390625" bestFit="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="5" spans="4:4">
+      <x:c r="D5" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="4:4">
+      <x:c r="D7" t="s">
+        <x:v>416</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="5:5">
+      <x:c r="E8" s="18"/>
+    </x:row>
+    <x:row r="9" spans="5:5">
+      <x:c r="E9" s="18" t="s">
+        <x:v>170</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="5:5">
+      <x:c r="E10" s="18" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="5:5">
+      <x:c r="E11" t="s">
+        <x:v>269</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="5:5">
+      <x:c r="E12" t="s">
+        <x:v>206</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="5:5">
+      <x:c r="E13" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="5:5">
+      <x:c r="E15" s="23" t="s">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="6:6">
+      <x:c r="F16" s="21" t="s">
+        <x:v>129</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="6:6">
+      <x:c r="F17" s="21" t="s">
+        <x:v>638</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="6:6">
+      <x:c r="F18" s="21" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="6:6">
+      <x:c r="F19" s="18" t="s">
+        <x:v>263</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="6:6">
+      <x:c r="F21" s="35" t="s">
+        <x:v>204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="5:5" ht="16.5" customHeight="1">
+      <x:c r="E23" s="18" t="s">
+        <x:v>176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="5:5">
+      <x:c r="E25" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="5:5">
+      <x:c r="E27" t="s">
+        <x:v>131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="5:5">
+      <x:c r="E28" t="s">
+        <x:v>151</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:hyperlinks>
+    <x:hyperlink ref="F21:F21" r:id="rId1"/>
+  </x:hyperlinks>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
+  <x:drawing r:id="rId2"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet21"/>
+  <x:dimension ref="D5:G23"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
+  <x:sheetData>
+    <x:row r="5" spans="4:4">
+      <x:c r="D5" t="s">
+        <x:v>502</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="4:5">
+      <x:c r="D6" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="E6" t="s">
+        <x:v>682</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="4:5">
+      <x:c r="D7" t="s">
+        <x:v>518</x:v>
+      </x:c>
+      <x:c r="E7" t="s">
+        <x:v>611</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="4:5">
+      <x:c r="D8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="E8" t="s">
+        <x:v>346</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="4:5">
+      <x:c r="D9" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E9" t="s">
+        <x:v>257</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="4:5">
+      <x:c r="D10" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="E10" t="s">
+        <x:v>275</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="4:5">
+      <x:c r="D11" t="s">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="E11" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="4:4">
+      <x:c r="D14" t="s">
+        <x:v>286</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="4:4">
+      <x:c r="D15" t="s">
+        <x:v>509</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="4:4">
+      <x:c r="D16" t="s">
+        <x:v>509</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="4:4">
+      <x:c r="D17" t="s">
+        <x:v>553</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="4:4">
+      <x:c r="D18" t="s">
+        <x:v>553</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="4:4">
+      <x:c r="D19" t="s">
+        <x:v>553</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="4:4">
+      <x:c r="D20" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="4:7">
+      <x:c r="D21" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E21" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="G21" t="s">
+        <x:v>504</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="4:7">
+      <x:c r="D22" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="E22" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="G22" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="4:7">
+      <x:c r="D23" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="E23" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G23" t="s">
+        <x:v>506</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet22"/>
+  <x:dimension ref="C6:C48"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
+  <x:cols>
+    <x:col min="3" max="3" width="77.96484375" bestFit="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="6" spans="3:3">
+      <x:c r="C6" t="s">
+        <x:v>509</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="3:3">
+      <x:c r="C7" s="20" t="s">
+        <x:v>666</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="3:3">
+      <x:c r="C8" t="s">
+        <x:v>414</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="3:3">
+      <x:c r="C9" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="3:3">
+      <x:c r="C10" t="s">
+        <x:v>443</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="3:3">
+      <x:c r="C12" t="s">
+        <x:v>296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C19" s="41" t="s">
+        <x:v>688</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C20" s="41" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C21" s="43" t="s">
+        <x:v>696</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C22" s="41" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C23" s="41" t="s">
+        <x:v>192</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="3:3">
+      <x:c r="C24" s="42"/>
+    </x:row>
+    <x:row r="25" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C25" s="41" t="s">
+        <x:v>635</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="3:3" ht="53.39999999999999857891">
+      <x:c r="C26" s="41" t="s">
+        <x:v>608</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C27" s="41" t="s">
+        <x:v>289</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C28" s="41" t="s">
+        <x:v>607</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C29" s="41" t="s">
+        <x:v>687</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="3:3">
+      <x:c r="C30" s="42"/>
+    </x:row>
+    <x:row r="31" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C31" s="41" t="s">
+        <x:v>698</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C32" s="41" t="s">
+        <x:v>697</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C33" s="41" t="s">
+        <x:v>695</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C34" s="41" t="s">
+        <x:v>290</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C35" s="41" t="s">
+        <x:v>291</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="3:3">
+      <x:c r="C36" s="42"/>
+    </x:row>
+    <x:row r="37" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C37" s="41" t="s">
+        <x:v>692</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C38" s="41" t="s">
+        <x:v>509</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C39" s="41" t="s">
+        <x:v>292</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C40" s="41" t="s">
+        <x:v>689</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C41" s="41" t="s">
+        <x:v>293</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="3:3">
+      <x:c r="C42" s="42"/>
+    </x:row>
+    <x:row r="43" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C43" s="41" t="s">
+        <x:v>693</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="3:3" ht="53.39999999999999857891">
+      <x:c r="C44" s="43" t="s">
+        <x:v>690</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C45" s="41" t="s">
+        <x:v>509</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C46" s="41" t="s">
+        <x:v>691</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C47" s="41" t="s">
+        <x:v>689</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C48" s="41" t="s">
+        <x:v>694</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet23"/>
+  <x:dimension ref="A5:D48"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
+  <x:cols>
+    <x:col min="2" max="2" width="14.9296875" bestFit="1" customWidth="1"/>
+    <x:col min="3" max="3" width="41.25390625" bestFit="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="5" spans="3:3">
+      <x:c r="C5" t="s">
+        <x:v>399</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="3:3">
+      <x:c r="C6" s="18" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="3:3">
+      <x:c r="C7" s="18" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="3:4">
+      <x:c r="C9" t="s">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="D9" t="s">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="3:4">
+      <x:c r="C10" t="s">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="D10" t="s">
+        <x:v>77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="3:4">
+      <x:c r="C11" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="s">
+        <x:v>674</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="3:4">
+      <x:c r="C12" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D12" t="s">
+        <x:v>446</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="3:4">
+      <x:c r="C13" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="D13" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="3:4">
+      <x:c r="C14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="3:4">
+      <x:c r="C15" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="D15" t="s">
+        <x:v>672</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="3:4">
+      <x:c r="C17" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D17" t="s">
+        <x:v>171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="3:4">
+      <x:c r="C18" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="D18" t="s">
+        <x:v>196</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="3:4">
+      <x:c r="C19" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="D19" t="s">
+        <x:v>163</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="3:4">
+      <x:c r="C20" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D20" t="s">
+        <x:v>678</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="3:4">
+      <x:c r="C21" t="s">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="D21" t="s">
+        <x:v>348</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="3:4">
+      <x:c r="C22" s="18" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="D22" s="18" t="s">
+        <x:v>191</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="2:3">
+      <x:c r="B24" s="31" t="s">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="C24" s="31" t="s">
+        <x:v>155</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="3:4">
+      <x:c r="C25" s="36" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D25" t="s">
+        <x:v>150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="3:4">
+      <x:c r="C26" s="36" t="s">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="D26" t="s">
+        <x:v>247</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="3:4">
+      <x:c r="C27" s="36" t="s">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="D27" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="3:4">
+      <x:c r="C28" s="36" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="D28" t="s">
+        <x:v>625</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:3">
+      <x:c r="A31" s="18"/>
+      <x:c r="B31" s="18" t="s">
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="C31" s="18" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="3:4">
+      <x:c r="C32" s="37" t="s">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="D32" t="s">
+        <x:v>173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="3:4">
+      <x:c r="C33" s="37" t="s">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="D33" t="s">
+        <x:v>247</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="3:4">
+      <x:c r="C34" s="37" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="D34" t="s">
+        <x:v>347</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="3:4">
+      <x:c r="C35" s="38" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D35" t="s">
+        <x:v>153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="3:4">
+      <x:c r="C36" s="37" t="s">
+        <x:v>683</x:v>
+      </x:c>
+      <x:c r="D36" t="s">
+        <x:v>358</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="3:4">
+      <x:c r="C37" s="38" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="D37" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="3:4">
+      <x:c r="C38" s="38" t="s">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="D38" t="s">
+        <x:v>625</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="3:4">
+      <x:c r="C40" s="39" t="s">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="D40" t="s">
+        <x:v>154</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="3:4">
+      <x:c r="C41" s="39" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D41" t="s">
+        <x:v>159</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="3:4">
+      <x:c r="C42" s="39" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="D42" t="s">
+        <x:v>606</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="3:4">
+      <x:c r="C43" s="39" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="D43" t="s">
+        <x:v>662</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="3:3">
+      <x:c r="C46" t="s">
+        <x:v>197</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="3:3">
+      <x:c r="C47" t="s">
+        <x:v>675</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="3:3">
+      <x:c r="C48" s="20" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet24"/>
+  <x:dimension ref="B3:C21"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
+  <x:sheetData>
+    <x:row r="3" spans="2:2">
+      <x:c r="B3" t="s">
+        <x:v>258</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="2:3">
+      <x:c r="B7" s="18" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C7" s="18"/>
+    </x:row>
+    <x:row r="8" spans="2:3">
+      <x:c r="B8" s="18" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="C8" s="18"/>
+    </x:row>
+    <x:row r="9" spans="2:3">
+      <x:c r="B9" s="18" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="C9" s="18"/>
+    </x:row>
+    <x:row r="10" spans="2:3">
+      <x:c r="B10" s="18"/>
+      <x:c r="C10" s="18"/>
+    </x:row>
+    <x:row r="12" spans="2:2">
+      <x:c r="B12" t="s">
+        <x:v>253</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="2:2">
+      <x:c r="B13" t="s">
+        <x:v>667</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="2:2">
+      <x:c r="B14" t="s">
+        <x:v>668</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="2:2">
+      <x:c r="B15" t="s">
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="2:2">
+      <x:c r="B16" t="s">
+        <x:v>365</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="2:2">
+      <x:c r="B18" t="s">
+        <x:v>265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="2:2">
+      <x:c r="B19" t="s">
+        <x:v>610</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="2:2">
+      <x:c r="B20" t="s">
+        <x:v>248</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="2:2">
+      <x:c r="B21" t="s">
+        <x:v>274</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
 
@@ -2543,333 +6097,333 @@
   <x:sheetData>
     <x:row r="7" spans="4:4">
       <x:c r="D7" t="s">
-        <x:v>84</x:v>
+        <x:v>376</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="4:4">
       <x:c r="D9" s="3" t="s">
-        <x:v>129</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:4">
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:4">
       <x:c r="C11" s="2"/>
       <x:c r="D11" s="4" t="s">
-        <x:v>85</x:v>
+        <x:v>313</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="3:5">
       <x:c r="C12" s="1"/>
       <x:c r="E12" t="s">
-        <x:v>136</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="3:5">
       <x:c r="C13" s="1"/>
       <x:c r="E13" t="s">
-        <x:v>28</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="3:5">
       <x:c r="C14" s="1"/>
       <x:c r="E14" t="s">
-        <x:v>76</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="5:5">
       <x:c r="E15" t="s">
-        <x:v>50</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="6:6">
       <x:c r="F16" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="6:6">
       <x:c r="F17" t="s">
-        <x:v>184</x:v>
+        <x:v>332</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="6:6">
       <x:c r="F18" t="s">
-        <x:v>79</x:v>
+        <x:v>356</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="6:6">
       <x:c r="F19" t="s">
-        <x:v>77</x:v>
+        <x:v>349</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="6:6">
       <x:c r="F20" t="s">
-        <x:v>17</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="6:6">
       <x:c r="F21" t="s">
-        <x:v>24</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="4:4">
-      <x:c r="D23" s="16" t="s">
-        <x:v>14</x:v>
+      <x:c r="D23" s="15" t="s">
+        <x:v>578</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="4:4">
       <x:c r="D24" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="4:4">
       <x:c r="D25" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>313</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="4:4">
       <x:c r="D26" t="s">
-        <x:v>181</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="4:4">
       <x:c r="D27" t="s">
-        <x:v>34</x:v>
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="4:4">
       <x:c r="D28" t="s">
-        <x:v>51</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="4:16">
       <x:c r="D29" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="P29" s="19" t="s">
-        <x:v>15</x:v>
+        <x:v>633</x:v>
+      </x:c>
+      <x:c r="P29" s="18" t="s">
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="5:16">
       <x:c r="E30" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="P30" t="s">
-        <x:v>16</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="5:16">
       <x:c r="E31" t="s">
-        <x:v>78</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="P31" t="s">
-        <x:v>25</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="5:16">
       <x:c r="E32" t="s">
-        <x:v>30</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="P32" t="s">
-        <x:v>284</x:v>
+        <x:v>650</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="5:17">
       <x:c r="E33" t="s">
-        <x:v>180</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="P33" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="Q33" s="21" t="s">
-        <x:v>3</x:v>
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="Q33" s="20" t="s">
+        <x:v>540</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="5:5">
       <x:c r="E34" t="s">
-        <x:v>61</x:v>
+        <x:v>632</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="4:4">
-      <x:c r="D36" s="16" t="s">
-        <x:v>221</x:v>
+      <x:c r="D36" s="15" t="s">
+        <x:v>419</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="4:4">
       <x:c r="D37" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="4:16">
       <x:c r="D38" s="2" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="P38" s="19" t="s">
-        <x:v>266</x:v>
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="P38" s="18" t="s">
+        <x:v>388</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="4:4">
       <x:c r="D39" t="s">
-        <x:v>48</x:v>
+        <x:v>455</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="4:4">
       <x:c r="D40" t="s">
-        <x:v>23</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="4:4">
       <x:c r="D41" t="s">
-        <x:v>171</x:v>
+        <x:v>409</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="4:4">
       <x:c r="D42" t="s">
-        <x:v>75</x:v>
+        <x:v>352</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="4:5">
       <x:c r="D43" t="s">
-        <x:v>140</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="E43" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="5:5">
       <x:c r="E44" t="s">
-        <x:v>208</x:v>
+        <x:v>654</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="5:5">
       <x:c r="E45" t="s">
-        <x:v>155</x:v>
+        <x:v>482</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="5:5">
       <x:c r="E46" t="s">
-        <x:v>65</x:v>
+        <x:v>266</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="5:5">
       <x:c r="E47" t="s">
-        <x:v>188</x:v>
+        <x:v>337</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="4:4">
-      <x:c r="D49" s="16" t="s">
-        <x:v>194</x:v>
+      <x:c r="D49" s="15" t="s">
+        <x:v>396</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="4:4">
       <x:c r="D50" s="2" t="s">
-        <x:v>182</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="4:4">
       <x:c r="D51" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>313</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="4:4">
       <x:c r="D52" t="s">
-        <x:v>172</x:v>
+        <x:v>410</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="4:4">
       <x:c r="D53" t="s">
-        <x:v>200</x:v>
+        <x:v>582</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="4:4">
       <x:c r="D54" t="s">
-        <x:v>216</x:v>
+        <x:v>646</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="4:4">
       <x:c r="D55" t="s">
-        <x:v>213</x:v>
+        <x:v>643</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="5:5">
       <x:c r="E56" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="5:5">
       <x:c r="E57" t="s">
-        <x:v>80</x:v>
+        <x:v>366</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="5:5">
       <x:c r="E58" t="s">
-        <x:v>185</x:v>
+        <x:v>325</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="5:5">
       <x:c r="E59" t="s">
-        <x:v>4</x:v>
+        <x:v>660</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="4:4" ht="17.14999999999999857891">
-      <x:c r="D61" s="17" t="s">
-        <x:v>222</x:v>
+      <x:c r="D61" s="16" t="s">
+        <x:v>565</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="4:4" ht="17.14999999999999857891">
       <x:c r="D62" s="6" t="s">
-        <x:v>47</x:v>
+        <x:v>454</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="5:5" ht="17.14999999999999857891">
       <x:c r="E63" s="6" t="s">
-        <x:v>100</x:v>
+        <x:v>311</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="5:5" ht="17.14999999999999857891">
       <x:c r="E64" s="6" t="s">
-        <x:v>207</x:v>
+        <x:v>649</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="5:5" ht="17.14999999999999857891">
       <x:c r="E65" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="5:5" ht="17.14999999999999857891">
       <x:c r="E66" s="6" t="s">
-        <x:v>206</x:v>
+        <x:v>563</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="5:5" ht="17.14999999999999857891">
       <x:c r="E67" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="5:6" ht="18.55000000000000071054">
       <x:c r="E68" s="7"/>
       <x:c r="F68" s="5" t="s">
-        <x:v>124</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="5:6" ht="18.55000000000000071054">
       <x:c r="E69" s="7"/>
       <x:c r="F69" s="6" t="s">
-        <x:v>83</x:v>
+        <x:v>320</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="5:6" ht="18.55000000000000071054">
       <x:c r="E70" s="7"/>
       <x:c r="F70" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>569</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69972223043441772461" right="0.69972223043441772461" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
@@ -2882,54 +6436,54 @@
   <x:sheetData>
     <x:row r="5" spans="5:5">
       <x:c r="E5" t="s">
-        <x:v>137</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="5:5">
       <x:c r="E6" t="s">
-        <x:v>82</x:v>
+        <x:v>344</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="5:5">
       <x:c r="E7" t="s">
-        <x:v>54</x:v>
+        <x:v>613</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="5:5">
       <x:c r="E8" t="s">
-        <x:v>26</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="4:5">
       <x:c r="D9" s="3"/>
       <x:c r="E9" t="s">
-        <x:v>86</x:v>
+        <x:v>316</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:5">
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
       <x:c r="E10" t="s">
-        <x:v>211</x:v>
+        <x:v>647</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:5">
       <x:c r="C11" s="2"/>
       <x:c r="D11" s="4"/>
       <x:c r="E11" t="s">
-        <x:v>59</x:v>
+        <x:v>618</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="3:5">
       <x:c r="C12" s="1"/>
       <x:c r="E12" t="s">
-        <x:v>60</x:v>
+        <x:v>617</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="3:5">
       <x:c r="C13" s="1"/>
-      <x:c r="E13" s="18" t="s">
-        <x:v>9</x:v>
+      <x:c r="E13" s="17" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="3:3">
@@ -2975,7 +6529,7 @@
   <x:hyperlinks>
     <x:hyperlink ref="E13:E13" r:id="rId1"/>
   </x:hyperlinks>
-  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69972223043441772461" right="0.69972223043441772461" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
@@ -2996,35 +6550,35 @@
   <x:sheetData>
     <x:row r="5" spans="5:5">
       <x:c r="E5" t="s">
-        <x:v>101</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="5:5">
       <x:c r="E6" t="s">
-        <x:v>87</x:v>
+        <x:v>304</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="5:5">
       <x:c r="E7" t="s">
-        <x:v>175</x:v>
+        <x:v>299</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="5:5">
       <x:c r="E8" t="s">
-        <x:v>173</x:v>
+        <x:v>403</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="4:5">
       <x:c r="D9" s="3"/>
       <x:c r="E9" t="s">
-        <x:v>150</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:5">
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
       <x:c r="E10" t="s">
-        <x:v>99</x:v>
+        <x:v>309</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:4">
@@ -3040,122 +6594,122 @@
     <x:row r="14" spans="3:10" ht="27.10000000000000142109">
       <x:c r="C14" s="1"/>
       <x:c r="E14" s="8" t="s">
+        <x:v>531</x:v>
+      </x:c>
+      <x:c r="F14" s="8" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G14" s="8" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H14" s="8" t="s">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="I14" s="8" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J14" s="8" t="s">
+        <x:v>302</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="5:10" ht="27.10000000000000142109">
+      <x:c r="E15" s="8" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F15" s="8" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="G15" s="8" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="H15" s="8" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="I15" s="8" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="J15" s="8" t="s">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="5:10" ht="27.10000000000000142109">
+      <x:c r="E16" s="8" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="F14" s="8" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="G14" s="8" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="H14" s="8" t="s">
+      <x:c r="F16" s="8" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G16" s="8" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="H16" s="8" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="I14" s="8" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="J14" s="8" t="s">
-        <x:v>89</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="5:10" ht="53.39999999999999857891">
-      <x:c r="E15" s="8" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="F15" s="8" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="G15" s="8" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="H15" s="8" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="I15" s="8" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="J15" s="8" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="5:10" ht="53.39999999999999857891">
-      <x:c r="E16" s="8" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="F16" s="8" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="G16" s="8" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H16" s="8" t="s">
-        <x:v>118</x:v>
-      </x:c>
       <x:c r="I16" s="8" t="s">
-        <x:v>174</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="J16" s="8" t="s">
-        <x:v>187</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="5:10" ht="79.70000000000000284217">
+        <x:v>193</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="5:10" ht="27.10000000000000142109">
       <x:c r="E17" s="8" t="s">
-        <x:v>106</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F17" s="8" t="s">
-        <x:v>204</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="G17" s="8" t="s">
-        <x:v>209</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="H17" s="8" t="s">
-        <x:v>112</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="I17" s="8" t="s">
-        <x:v>154</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="J17" s="9" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="5:10" ht="79.70000000000000284217">
+        <x:v>241</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="5:10" ht="27.10000000000000142109">
       <x:c r="E18" s="8" t="s">
         <x:v>110</x:v>
       </x:c>
       <x:c r="F18" s="8" t="s">
-        <x:v>191</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="G18" s="8" t="s">
-        <x:v>138</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H18" s="8" t="s">
-        <x:v>192</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="I18" s="8" t="s">
-        <x:v>135</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J18" s="8" t="s">
-        <x:v>128</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="5:10" ht="79.70000000000000284217">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="5:10" ht="53.39999999999999857891">
       <x:c r="E19" s="8" t="s">
-        <x:v>103</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F19" s="8" t="s">
-        <x:v>203</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="G19" s="8" t="s">
-        <x:v>214</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="H19" s="8" t="s">
-        <x:v>114</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="I19" s="8" t="s">
-        <x:v>152</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="J19" s="9" t="s">
-        <x:v>190</x:v>
+        <x:v>326</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="4:4">
@@ -3170,8 +6724,16 @@
     <x:row r="37" spans="4:4">
       <x:c r="D37" s="2"/>
     </x:row>
-    <x:row r="38" spans="4:4">
+    <x:row r="38" spans="4:6">
       <x:c r="D38" s="2"/>
+      <x:c r="F38" t="s">
+        <x:v>511</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="6:6">
+      <x:c r="F39" t="s">
+        <x:v>511</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" spans="5:5">
       <x:c r="E43" s="4"/>
@@ -3192,7 +6754,7 @@
       <x:c r="D63" s="2"/>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69972223043441772461" right="0.69972223043441772461" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
@@ -3200,97 +6762,92 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet6"/>
-  <x:dimension ref="C11:I35"/>
+  <x:dimension ref="C11:I27"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
   <x:sheetData>
     <x:row r="11" spans="4:4">
       <x:c r="D11" t="s">
-        <x:v>143</x:v>
+        <x:v>536</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="4:4">
       <x:c r="D12" t="s">
-        <x:v>153</x:v>
+        <x:v>473</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="4:4">
       <x:c r="D13" t="s">
-        <x:v>218</x:v>
+        <x:v>684</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="3:4">
       <x:c r="C14" t="s">
-        <x:v>141</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D14" t="s">
-        <x:v>46</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="4:4">
       <x:c r="D15" t="s">
-        <x:v>193</x:v>
+        <x:v>686</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="4:4">
       <x:c r="D16" t="s">
-        <x:v>217</x:v>
+        <x:v>685</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="4:4">
       <x:c r="D17" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="4:4">
       <x:c r="D19" t="s">
-        <x:v>156</x:v>
+        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="4:4">
       <x:c r="D20" s="2" t="s">
-        <x:v>186</x:v>
+        <x:v>327</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="4:4">
       <x:c r="D21" s="2" t="s">
-        <x:v>56</x:v>
+        <x:v>631</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="4:4">
       <x:c r="D23" t="s">
-        <x:v>71</x:v>
+        <x:v>387</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="4:4">
       <x:c r="D24" t="s">
-        <x:v>130</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="4:4">
       <x:c r="D25" s="2" t="s">
-        <x:v>132</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="4:9">
       <x:c r="D26" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="I26" t="s">
-        <x:v>145</x:v>
+        <x:v>511</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="4:4">
       <x:c r="D27" s="2" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="4:4">
-      <x:c r="D35" t="s">
-        <x:v>127</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69972223043441772461" right="0.69972223043441772461" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
@@ -3313,122 +6870,122 @@
     </x:row>
     <x:row r="10" spans="3:3">
       <x:c r="C10" s="2" t="s">
-        <x:v>67</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:3">
       <x:c r="C11" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>295</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="3:3">
       <x:c r="C12" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="3:3">
       <x:c r="C14" t="s">
-        <x:v>32</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="3:3">
       <x:c r="C15" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="3:3">
       <x:c r="C16" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>322</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="3:3">
       <x:c r="C17" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>375</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="3:3">
       <x:c r="C18" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="3:3">
       <x:c r="C20" s="11" t="s">
-        <x:v>161</x:v>
+        <x:v>491</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="3:3">
       <x:c r="C21" t="s">
-        <x:v>70</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="3:3">
       <x:c r="C22" t="s">
-        <x:v>176</x:v>
+        <x:v>401</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="3:3">
       <x:c r="C23" t="s">
-        <x:v>98</x:v>
+        <x:v>318</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="3:3">
       <x:c r="C26" s="11" t="s">
-        <x:v>157</x:v>
+        <x:v>472</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="3:3">
       <x:c r="C27" t="s">
-        <x:v>119</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="3:3">
       <x:c r="C28" t="s">
-        <x:v>197</x:v>
+        <x:v>398</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="3:3">
       <x:c r="C29" t="s">
-        <x:v>164</x:v>
+        <x:v>474</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="3:3">
       <x:c r="C30" t="s">
-        <x:v>163</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="3:3">
       <x:c r="C33" s="11" t="s">
-        <x:v>166</x:v>
+        <x:v>469</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="3:3">
       <x:c r="C34" t="s">
-        <x:v>121</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="3:3">
       <x:c r="C35" t="s">
-        <x:v>196</x:v>
+        <x:v>369</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="3:3">
       <x:c r="C36" t="s">
-        <x:v>195</x:v>
+        <x:v>391</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="3:3">
       <x:c r="C37" t="s">
-        <x:v>97</x:v>
+        <x:v>303</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="3:3">
       <x:c r="C39" t="s">
-        <x:v>62</x:v>
+        <x:v>619</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="3:3">
       <x:c r="C42" s="11" t="s">
-        <x:v>159</x:v>
+        <x:v>481</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="3:3">
@@ -3438,176 +6995,176 @@
     </x:row>
     <x:row r="44" spans="3:3">
       <x:c r="C44" t="s">
-        <x:v>93</x:v>
+        <x:v>319</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="3:3">
       <x:c r="C45" t="s">
-        <x:v>177</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="3:3">
       <x:c r="C46" t="s">
-        <x:v>178</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="3:3">
       <x:c r="C47" t="s">
-        <x:v>158</x:v>
+        <x:v>477</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="3:3">
       <x:c r="C48" t="s">
-        <x:v>72</x:v>
+        <x:v>321</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="3:3">
       <x:c r="C50" s="11" t="s">
-        <x:v>160</x:v>
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="3:3">
       <x:c r="C51" t="s">
-        <x:v>69</x:v>
+        <x:v>306</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="3:8">
       <x:c r="C52" t="s">
-        <x:v>102</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="H52" s="2" t="s">
-        <x:v>179</x:v>
+        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="3:3">
       <x:c r="C53" s="2" t="s">
-        <x:v>94</x:v>
+        <x:v>305</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="3:3">
       <x:c r="C54" s="2" t="s">
-        <x:v>205</x:v>
+        <x:v>577</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="3:3">
       <x:c r="C57" s="11" t="s">
-        <x:v>162</x:v>
+        <x:v>476</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="3:3">
       <x:c r="C58" t="s">
-        <x:v>92</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="3:3">
       <x:c r="C59" s="2" t="s">
-        <x:v>210</x:v>
+        <x:v>642</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="3:3">
       <x:c r="C60" s="2" t="s">
-        <x:v>189</x:v>
+        <x:v>330</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="3:3">
       <x:c r="C61" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="3:3">
       <x:c r="C64" s="11" t="s">
-        <x:v>149</x:v>
+        <x:v>468</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="3:3">
       <x:c r="C65" t="s">
-        <x:v>91</x:v>
+        <x:v>368</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="3:3">
       <x:c r="C66" s="2" t="s">
-        <x:v>95</x:v>
+        <x:v>317</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="3:3">
       <x:c r="C67" s="2" t="s">
-        <x:v>212</x:v>
+        <x:v>652</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="3:3">
       <x:c r="C68" s="2" t="s">
-        <x:v>96</x:v>
+        <x:v>323</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="3:6">
-      <x:c r="C72" s="15" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="D72" s="15"/>
+      <x:c r="C72" s="40" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D72" s="40"/>
       <x:c r="E72" s="12"/>
       <x:c r="F72" s="12"/>
     </x:row>
     <x:row r="73" spans="3:6">
       <x:c r="C73" s="14" t="s">
-        <x:v>144</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D73" s="13" t="s">
-        <x:v>167</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="E73" s="13" t="s">
-        <x:v>113</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F73" s="13" t="s">
-        <x:v>123</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="3:6">
       <x:c r="C74" s="14" t="s">
-        <x:v>125</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D74" s="12" t="s">
-        <x:v>165</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="E74" s="12" t="s">
-        <x:v>117</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F74" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="3:6">
       <x:c r="C75" s="14" t="s">
-        <x:v>157</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="D75" s="12" t="s">
-        <x:v>151</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="E75" s="12" t="s">
-        <x:v>139</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="F75" s="12" t="s">
-        <x:v>148</x:v>
+        <x:v>543</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="3:6">
       <x:c r="C76" s="14" t="s">
-        <x:v>166</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="D76" s="12" t="s">
-        <x:v>120</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E76" s="12" t="s">
-        <x:v>116</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F76" s="12" t="s">
-        <x:v>115</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells count="1">
     <x:mergeCell ref="C72:D72"/>
   </x:mergeCells>
-  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69972223043441772461" right="0.69972223043441772461" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
@@ -3626,170 +7183,170 @@
   </x:cols>
   <x:sheetData>
     <x:row r="3" spans="3:3" ht="20.64999999999999857891">
-      <x:c r="C3" s="20" t="s">
-        <x:v>13</x:v>
+      <x:c r="C3" s="19" t="s">
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="3:3" ht="22.05000000000000071054">
       <x:c r="C6" t="s">
-        <x:v>198</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="3:9">
       <x:c r="C7" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="E7" s="23" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="G7" s="19" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="I7" s="19" t="s">
-        <x:v>242</x:v>
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="E7" s="22" t="s">
+        <x:v>636</x:v>
+      </x:c>
+      <x:c r="G7" s="18" t="s">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="I7" s="18" t="s">
+        <x:v>584</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="3:9">
-      <x:c r="C8" s="21" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E8" s="22" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="G8" s="22" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I8" s="22" t="s">
-        <x:v>233</x:v>
+      <x:c r="C8" s="20" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E8" s="21" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="G8" s="21" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I8" s="21" t="s">
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="3:9">
-      <x:c r="C9" s="21" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="E9" s="22" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G9" s="22" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I9" s="22" t="s">
-        <x:v>12</x:v>
+      <x:c r="C9" s="20" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E9" s="21" t="s">
+        <x:v>659</x:v>
+      </x:c>
+      <x:c r="G9" s="21" t="s">
+        <x:v>645</x:v>
+      </x:c>
+      <x:c r="I9" s="21" t="s">
+        <x:v>657</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:9">
-      <x:c r="C10" s="21" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E10" s="22" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G10" s="22" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I10" s="22" t="s">
-        <x:v>231</x:v>
+      <x:c r="C10" s="20" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E10" s="21" t="s">
+        <x:v>621</x:v>
+      </x:c>
+      <x:c r="G10" s="21" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="I10" s="21" t="s">
+        <x:v>408</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:9">
-      <x:c r="C11" s="21" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E11" s="22" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G11" s="22" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="I11" s="19"/>
+      <x:c r="C11" s="20" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E11" s="21" t="s">
+        <x:v>644</x:v>
+      </x:c>
+      <x:c r="G11" s="21" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="I11" s="18"/>
     </x:row>
     <x:row r="12" spans="3:7">
-      <x:c r="C12" s="21" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="G12" s="22" t="s">
-        <x:v>234</x:v>
+      <x:c r="C12" s="20" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="G12" s="21" t="s">
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="3:3" ht="22.05000000000000071054">
-      <x:c r="C15" s="25" t="s">
-        <x:v>238</x:v>
+      <x:c r="C15" s="24" t="s">
+        <x:v>412</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="3:3">
-      <x:c r="C16" s="22" t="s">
-        <x:v>199</x:v>
+      <x:c r="C16" s="21" t="s">
+        <x:v>571</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="3:5">
       <x:c r="C17" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E17" s="23" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="3:5">
+      <x:c r="C18" s="20" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E18" s="20" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="E17" s="24" t="s">
-        <x:v>258</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="3:5">
-      <x:c r="C18" s="21" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="E18" s="21" t="s">
-        <x:v>259</x:v>
-      </x:c>
     </x:row>
     <x:row r="19" spans="3:5">
-      <x:c r="C19" s="21" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="E19" s="21" t="s">
-        <x:v>260</x:v>
+      <x:c r="C19" s="20" t="s">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="E19" s="20" t="s">
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="3:5">
-      <x:c r="C20" s="21" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="E20" s="21" t="s">
-        <x:v>251</x:v>
+      <x:c r="C20" s="20" t="s">
+        <x:v>651</x:v>
+      </x:c>
+      <x:c r="E20" s="20" t="s">
+        <x:v>596</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="3:3">
-      <x:c r="C21" s="21" t="s">
-        <x:v>235</x:v>
+      <x:c r="C21" s="20" t="s">
+        <x:v>392</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="3:3">
-      <x:c r="C22" s="21" t="s">
-        <x:v>257</x:v>
+      <x:c r="C22" s="20" t="s">
+        <x:v>394</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="3:3" ht="22.05000000000000071054">
-      <x:c r="C26" s="26" t="s">
-        <x:v>0</x:v>
+      <x:c r="C26" s="25" t="s">
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="3:3">
-      <x:c r="C27" s="21" t="s">
-        <x:v>19</x:v>
+      <x:c r="C27" s="20" t="s">
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="3:3">
-      <x:c r="C28" s="21" t="s">
-        <x:v>261</x:v>
+      <x:c r="C28" s="20" t="s">
+        <x:v>255</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="3:3">
-      <x:c r="C30" s="19" t="s">
-        <x:v>265</x:v>
+      <x:c r="C30" s="18" t="s">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="3:3">
       <x:c r="C31" t="s">
-        <x:v>262</x:v>
+        <x:v>256</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69972223043441772461" right="0.69972223043441772461" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
@@ -3797,89 +7354,171 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet9"/>
-  <x:dimension ref="U4:V20"/>
+  <x:dimension ref="U4:W33"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="21" max="21" width="12.74609375" bestFit="1" customWidth="1"/>
+    <x:col min="22" max="22" width="68.00390625" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="4" spans="21:21" ht="22.05000000000000071054">
-      <x:c r="U4" s="27" t="s">
-        <x:v>247</x:v>
+      <x:c r="U4" s="26" t="s">
+        <x:v>488</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="21:21">
-      <x:c r="U6" s="21" t="s">
-        <x:v>240</x:v>
+      <x:c r="U6" s="20" t="s">
+        <x:v>494</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="21:21">
-      <x:c r="U7" s="21" t="s">
-        <x:v>246</x:v>
+      <x:c r="U7" s="20" t="s">
+        <x:v>430</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="21:21">
-      <x:c r="U8" s="21" t="s">
-        <x:v>236</x:v>
+      <x:c r="U8" s="20" t="s">
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="21:21">
-      <x:c r="U9" s="21" t="s">
-        <x:v>239</x:v>
+      <x:c r="U9" s="20" t="s">
+        <x:v>381</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="21:21">
-      <x:c r="U10" s="21" t="s">
-        <x:v>244</x:v>
+      <x:c r="U10" s="20" t="s">
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="21:21">
-      <x:c r="U11" s="21" t="s">
-        <x:v>223</x:v>
+      <x:c r="U11" s="20" t="s">
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="21:21">
-      <x:c r="U12" s="21" t="s">
-        <x:v>219</x:v>
+      <x:c r="U12" s="20" t="s">
+        <x:v>264</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="21:21">
-      <x:c r="U14" s="22" t="s">
-        <x:v>237</x:v>
+      <x:c r="U14" s="21" t="s">
+        <x:v>486</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="22:22">
       <x:c r="V15" t="s">
-        <x:v>269</x:v>
+        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="22:22">
       <x:c r="V16" t="s">
-        <x:v>52</x:v>
+        <x:v>616</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="21:21">
-      <x:c r="U17" s="22" t="s">
-        <x:v>248</x:v>
+      <x:c r="U17" s="21" t="s">
+        <x:v>374</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="22:22">
       <x:c r="V18" t="s">
-        <x:v>53</x:v>
+        <x:v>629</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="21:21">
-      <x:c r="U19" s="21" t="s">
-        <x:v>252</x:v>
+      <x:c r="U19" s="20" t="s">
+        <x:v>492</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="22:22">
       <x:c r="V20" t="s">
-        <x:v>63</x:v>
+        <x:v>615</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="21:21">
+      <x:c r="U23" s="20" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="21:23">
+      <x:c r="U26" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="V26" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="W26" t="s">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="21:23">
+      <x:c r="U27" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="V27" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="W27" t="s">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="21:23">
+      <x:c r="U28" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="V28" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="W28" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="21:23">
+      <x:c r="U29" t="s">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="V29" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="W29" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="21:22">
+      <x:c r="U30" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="V30" t="s">
+        <x:v>65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="21:22">
+      <x:c r="U31" t="s">
+        <x:v>516</x:v>
+      </x:c>
+      <x:c r="V31" t="s">
+        <x:v>587</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="21:22">
+      <x:c r="U32" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="V32" t="s">
+        <x:v>422</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="21:22">
+      <x:c r="U33" t="s">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="V33" t="s">
+        <x:v>342</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69972223043441772461" right="0.69972223043441772461" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
--- a/marketing/무진사 데이터 컨텐츠마케팅 프로세스_260317.xlsx
+++ b/marketing/무진사 데이터 컨텐츠마케팅 프로세스_260317.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="14115" windowHeight="11430" tabRatio="599" firstSheet="5" activeTab="21"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11460" tabRatio="599" firstSheet="5" activeTab="29"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="1. 문제정의" sheetId="1" r:id="rId4"/>
@@ -36,511 +36,48 @@
     <x:sheet name="Sheet1" sheetId="22" r:id="rId25"/>
     <x:sheet name="23.구글 애즈 유튜브 광고" sheetId="23" r:id="rId26"/>
     <x:sheet name="24. 구글 애즈 &amp;유튜브 광고" sheetId="24" r:id="rId27"/>
+    <x:sheet name="Sheet4" sheetId="25" r:id="rId28"/>
+    <x:sheet name="25.구글애즈 광고캠페인 세팅" sheetId="26" r:id="rId29"/>
+    <x:sheet name="26. 구글애즈 유튜브 광고캠페인 썸네일 " sheetId="27" r:id="rId30"/>
+    <x:sheet name="27. 상품 상세페이지 기획, 제작" sheetId="28" r:id="rId31"/>
+    <x:sheet name="28. SEO,SEM,SERP" sheetId="29" r:id="rId32"/>
+    <x:sheet name="29. notion" sheetId="30" r:id="rId33"/>
   </x:sheets>
   <x:calcPr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" mc:Ignorable="hs" hs:hclCalcId="904"/>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="699">
-  <x:si>
-    <x:t>자사 브랜드 및 상품의 인지도를 최대한 많이 효과적으로 높이거나 알리고자 할때</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">유튜브 내 특정 키워드 검색시, 검색바 우측 상단 |하단 값과 함께 노출되는 광고 (썸네일이미지+ 텍스트 방식) -&gt; 썸네일 클릭시 요금 부과                                                                                                                                 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>광고메세지는 굉장히 감성 0 -&gt; 우리 타겟고객에게는 잘 와닿지않는 메세지x</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-타겟 중요성: 너무 좁혀놓고 모집단(모수)너무 적은 상황 -&gt; 예산 소진 x</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 테스트 진행 시, 변수는 1개 원칙 (실무적으로 최소화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 단순히 광고소재를 여러개 만들어서 집행 -&gt; A/B x</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; GA4: 사용자들이 우리 사이트 유입,방문 &gt; 어ᄄᅠᆫ 페이지,얼만큼 시간 체류 이탈&gt; 이벤트 활용 /전환/재방문 =&gt; 세션전환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://docs.google.com/forms/d/e/1FAIpQLSdXs6_v4ofkPICNDYSSmO6x1yRrk0WiNohaSWJVGXX6soOiBQ/viewform</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 똑같은 매체에서 상품,서비스를 판매하더라도 메인,서브, 상세페이지, 상푸 ㅁ목로페이지 등 다양한 채널에서 각각 높은 비율을 차지하고 있는 페이지를 선별-&gt; 극대화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6) 피츠의 법칙 : 클수록, 화려할수록 클릭을 하고 싶은 욕구가 커진다 (로그인, 회원가입, 구매하기, 신청하기)-&gt; 엑센트 컬러 강조, 일반 버튼 사이즈보다 키워줌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 매력적 요소 컨텐츠 : 전혀 기대안했는데, 있음으로써 매우 큰 감동을 느끼는 컨텐츠 (AI기반 추천 시스템 기능)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 앞에서 수집한 고객정보를 기반으로 최우선 고객집단(그룹)을 정의하는데 있어서 단순 경험, 의견을 바탕으로 결정 X</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 일원적 요소 컨텐츠: 있으면 있을수록 만족하지만, 없으면 없을수록 불편한 컨텐츠
-(ex) 쇼핑몰 - 상세 필터기능)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2) 픽셀 추적 코드 : 이벤트 설정 -&gt; 사용자의 액션행위 수집 -&gt; 기반 리타겟팅 광고 캠페인(*광고 효율성 극대화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> -Objective (미시적 목표): 사용자가 및 방문자가 실제 상품을 구매할 수 있는 직.간접적인 행위의 지표가 상승</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 출근룩 카테고리 구매 비중 높음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 25~34세 직장인 68%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>텍스트 신쟁 시, 변수는 1개 원칙</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> &gt;Primary Target</x:t>
-  </x:si>
-  <x:si>
-    <x:t>행동-&gt; 추천받기 /지금 보기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>광고 컨텐츠 소재 기획, 제작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불편한점 (pain point)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>핵심 상품 특장점 소개 전략 문서</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20. Ads Campaign</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-특히 신상품 출시 많은 관심</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설득할 수 있을만한 요소 부족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-SNS컨텐츠 소비를 많이하는 고객</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4. User Reaserch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 채널별 경쟁사, 아이템별 경쟁자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Media 활용 순서 및 흐름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지금 구매하는것이 현명한 선택일까?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; SKU 부족: 상품 다양성 부족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 페이지 체류시간 매우 짧음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여러상품 클릭, 가격/리뷰 비교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>리뷰좋은 데일리룩 추천을 발견</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-&gt; 확고한 1위 독점적 지위 확보</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키워드 경쟁력: RoAS, ROI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>O-Opportunity (기회)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 상품 상세페이지 진입률 상승</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt;Secondary Target</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-Product Life Cycle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키워드 예산// 검색정도//클릭률</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRM 채널 설계 및 프로세스 구축</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; K-패션, 스타일 관심도 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 직업: IT 기업 마케팅 매니저</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 기술력, 가격, 가성비, 컨텐츠</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RFM Score 기준 테이블</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt;월 신규 방문자 5,000명</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">구조 개선이 필요한 단계 : </x:t>
-  </x:si>
-  <x:si>
-    <x:t>상품 판매.할인가 포지셔닝 정의</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Acquisition (유입단계)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>혜택, 신뢰, 시의성, 긴급성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 출근 준비가 훨씬 가벼워진 하루</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 필요에 의해서 단발성 구매</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S- Strength (강점)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상품 기본정보 서비스 요약정리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 컨텐츠: 가치 추구형 컨텐츠</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 네이버 광고 센터 - 연관키워드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구체적이며 동종업계 -&gt;경쟁사 나열</x:t>
-  </x:si>
-  <x:si>
-    <x:t>*각 전략마다 3-5개 정도 수립</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-&gt; 약점대비 현재 업종의 활황기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-&gt; High End :고가전략</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가치-&gt; 리뷰좋은 /가성비/인기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직접 오프라인 방문 유도를 위함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-조회,구독 높아지는 경향:자극적</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잠재고객의 어ᄄᅠᆫ 행위가 발생</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bottom of Funneel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감정 -&gt; 고민끝/ 자신감/ 편안함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상품 판매효과 극대화 광고탬페인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>건너뛸 수 없는 일반 광고(CPM)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19. 3P Media Mix</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오프라인 매장 방문 및 프로모션</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가치: 리뷰기반 가성비 스타일 추구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상황-&gt; 출근룩/ 데일리룩/오피스룩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 키워드 확인 &amp; 예산 결정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6) 메타 비즈니스 관리자 접속</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1000회 노출당 광고 과금 방식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사용자의 참여유도를 위한 광고캠페인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마케팅 프로세스 진행.전개 &gt;체감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLICK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>트래픽, 참여</x:t>
-  </x:si>
-  <x:si>
-    <x:t>광고순서</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VEIW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACTION</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실적 최대화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOFU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>디스플레이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>동영상 조회수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잠재고객</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MILIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">cCPI: </x:t>
-  </x:si>
-  <x:si>
-    <x:t>ex)전화번호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>*CTA 문구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOFU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포털 사이트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진척사항</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOFU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61이상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고객행동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- KPI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유입/첫인상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감성자극</x:t>
-  </x:si>
-  <x:si>
-    <x:t>짧고 강렬</x:t>
-  </x:si>
-  <x:si>
-    <x:t>앱 프로모션</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메인 카테고리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구매횟수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11. NPD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8~18만원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2) BAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7. RFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구매결정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recency</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 가격 민감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세부 카테고리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 실행전략</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-충동구매가능</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전략,기획</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미완성 기억</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Low(1점)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>관심 + 불안</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상세검토</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8. STP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최우선 고객</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14. PLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A/B 테스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무진사:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18만원 이상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고객생각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>총 구매금액</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-계정 1개당</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13. 4P</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이벤트 세팅</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8만원 이하</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엄브렐러 전략</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시각 만족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>원웨이 전략</x:t>
-  </x:si>
-  <x:si>
-    <x:t>할인정책 설계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>책임의식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31~60일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 문제정의</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mid(2점)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>홈페이지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>관심 + 피로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이탈/재방문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키워드 분류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D-DAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>탐색/비교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 일관된 컨셉 &amp; 톤앤매너: 컨텐츠 &amp; 메세지 (어떤 시즌, 상황,채널)-&gt; IMC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-가성비 있는 상품을 기준으로 빠른 구매결정 &amp; 검색 비교를 선호하는 성향 고객</x:t>
-  </x:si>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="766">
   <x:si>
     <x:t>최종카드= WT전략: 약점을 개선해서 시장의 위협요소에 최대한 덜 노출시키겠다는 전략</x:t>
   </x:si>
   <x:si>
-    <x:t>동영상을 조회한 후 실제 상품 및 브랜드에 관심을 가질 법한 사용자들에게 광고집행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>데이터 세트 &gt; 설정 &gt; 이벤트 설정 &gt; 이벤트 설정도구 열기 &gt; 카페24 링크 넣기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 다양한 플랫폼 대비, 직장인 출근룩을 디테일하게 큐레이션하는 플랫폼, 서비스 부재</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유튜브 내 인스트림 광고 외 외부 제휴채널 내 건너뛰기 기능 없이 출력가능한 광고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실제 동영상광고를 본 후 구매까지 도달할 확률이 높은 소비자를 대상으로 광고 집행</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">동영상을 통해 나의 상품, 브랜드를 광고,홍보해서 해당 요소의 존재감을 인지시킨다. </x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 신규 스타트업 비즈니스 모델 적용X// 이미 비즈니스가 운영되고 있는 경우에 한함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 잠재고객 : 일반 유입 고객대비, 상품 및 서비스 결제확률이 매우 높은 고객</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A/B 테스트 -&gt; 단기간 내 상대적으로 더많은 호감을 받는 컨텐츠 문구를 채택</x:t>
-  </x:si>
-  <x:si>
-    <x:t>건너뛸 수 있거나 없는 인스트림 광고 혹은 범퍼 광고들을 조합해서 스토리텔링 전개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- MD와 협업하여 업종, 상품 가장 많이 판매되는 퍼널 사전 가설,검증, 전략 설계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문제 2: 유입은 발생, 구매전환률이 낮음/ 우리 홈페이지(브랜드) 신뢰도 낮음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 어떠한 서비스, 상품, 플랫폼 출시, 리뉴얼 -&gt; 시장 소비자들에게 선보이겠다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>짧은 동영상을 통해 생각지 못한 나의 결핍과 수요를 문득 창출시켜주고자 하는 목적</x:t>
-  </x:si>
-  <x:si>
-    <x:t>출근룩 고민을 줄이고 당신에게 어울리는 스타일을 추천합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1) Product 전략 (판매요소 = 상품|서비스|플랫폼)</x:t>
+    <x:t>-MCP,Figma,Slack,GCP,GMP...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-최초의 WBS 스케쥴/페이지 Notion개설</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. SEO: Search Engine Optimization</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAds: GA4를 통해 수집된 사용자의 데이터 정보를 받아서 해당 사용자들을 잠재고객이라는 이름으로 관리를 함.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 최초에 특정 브랜드가 런칭했을 때의 상항에서의 4P전락이 시간경과에 따라서 일치하지 않은 확률이 매우 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt;CRM (Customer Relationship Management). Email 발송 후클릭률 8% 이상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1) 관리자 권한 부여: 여러관리자가 광고캠페인 관리가 가능 (SNS 채널을 통해서 광고 집행-&gt; 관리자 여러명 / 채널 계정의 소유주만 접속가능)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 여러가지 업무들이 순차적/ 동시다발적으로 전개되어야하는데, 각 담당자들이 누구이며 마감기한이 언제까지인지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TPO: Time Place Occasion -&gt;ex) 출근룩/ 데일리룩/ 봄코디/ 오피스룩/ 소개팅룩 /하객룩</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">- 1+1, 덤정책, %할인 =&gt; 큰 방향성 x, 장기적 목적 없이 단발성의 프로모션 실행 -&gt; 부메랑으로 돌아온다 (일관성x, 고객 매우 혼란) </x:t>
@@ -571,28 +108,792 @@
     <x:t>- 플레이스 &gt; 온오프라인을 나누는 것이 아니라, 채널 내 어떤 지점에서 매출발생 &amp; 외부 채널 중 어떤 플랫폼에서 소비자들을 많이 유입시킬 것인가?</x:t>
   </x:si>
   <x:si>
-    <x:t>1) 관리자 권한 부여: 여러관리자가 광고캠페인 관리가 가능 (SNS 채널을 통해서 광고 집행-&gt; 관리자 여러명 / 채널 계정의 소유주만 접속가능)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구글 ai에 예산을 위탁 -&gt;  해당 예산으로 구글이 다양한 채널 대리 집행</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">3) 밀러의 법칙(Miller's Law) : 사람의 단기 기억에는 정보의 한계가 존재(사람은 한번에 최대 5-9개 사이의 정보만을 기억) </x:t>
-  </x:si>
-  <x:si>
-    <x:t>6초 이하의 길이만 허용, 최대한 짧은 시간 내 브랜드를 각인시키고자 집행하는 광고 =&gt; 건너뛰기 없음,  유튜브 영상 앞,끝,중간 모두 가능</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(*Before VS After: 채널별 유입 비중 -&gt; Paid Social  / Organic Search/ Organic Social )</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1) 멘탈모델 (mental model) : 소비자가 이미 자신의 머리속에 가지고 있는 이미지 및 컨셉을 다른 플랫폼, 서비스에서도 기대한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이벤트 관리자 &gt; 데이터 연결 &gt; 새 데이터 소스 연결 &gt; 웹 &gt; 광고계정설정 &gt; (픽셀코드설치) 직접설정 &gt; Meta 픽셀전용 &gt; 코드 복사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문제 3: 유입 존재, 구매전환률 보통, 재방문 거의 전무/ 우리 홈페이지(브랜드) 기술적, 시각적,기능적 차별화 포인트 부재</x:t>
+    <x:t>-장점:별도의 비용x / 단점: 경쟁이 치열하고, 상위노출까지 시간이 많이 걸림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. 컨텐츠 상단: HOOK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1080 x 1920 = 9:16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>*예산세팅 : ROI, RoAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 평점, 별점, 리뷰, 사용자수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1920 x 1080 = 16:9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 8mm 테입 / 방송국용 카메라</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0~3초 : attention = hook</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 2억</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키네마스터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영상편집실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7~11초 : 신뢰</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 영상소스, 이미지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 오늘뭐입지? -&gt; 우리 서비스 내 큐레이션 기능활용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 컨텐츠 저장 공간 &gt; 네이버, 티스토리 블로그 (작성자만이 권한) -&gt; 외부관계자가 함께 참여 x</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t xml:space="preserve">- </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+        <x:b val="1"/>
+      </x:rPr>
+      <x:t xml:space="preserve">생성형 AI를 통해서 특정 키워드 및 질문 </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t>시, 답변으로 채택가능한 컨텐츠가 될 수 있도록 기획, 제작</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 일반 사용자들이 주로 검색하는 키워드를 기반으로 제목생성, 클릭하고 싶은 마음이 들 수 있도록 유도문장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중형키워드: 검색은 일어나고 있지만 아직 확실한 트랜드로 부상하지 않은 키워드 그룹/ 잠재력 존재 &gt; 대형키워드 기준 상대적 적은 자본으로도 선점 //  리스크-&gt; 키워드 성장 후 대형키워드 부상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6) 피츠의 법칙 : 클수록, 화려할수록 클릭을 하고 싶은 욕구가 커진다 (로그인, 회원가입, 구매하기, 신청하기)-&gt; 엑센트 컬러 강조, 일반 버튼 사이즈보다 키워줌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 똑같은 매체에서 상품,서비스를 판매하더라도 메인,서브, 상세페이지, 상푸 ㅁ목로페이지 등 다양한 채널에서 각각 높은 비율을 차지하고 있는 페이지를 선별-&gt; 극대화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 스타트업, 초기창업, 중소기업 -&gt; 미래가치를 먼저 가져다 사용하는 경우 (레버리지), 현실에 입각해서 직접 발로 뛰는 마케팅</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-SaaS 플랫폼(구독형 서비스 플랫폼/API)+외부 프로그램 연동 원활</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 매출유입이 안정적인 대기업 : 전년 매출액 기준 13~22% 예산</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 일관된 컨셉 &amp; 톤앤매너: 컨텐츠 &amp; 메세지 (어떤 시즌, 상황,채널)-&gt; IMC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-가성비 있는 상품을 기준으로 빠른 구매결정 &amp; 검색 비교를 선호하는 성향 고객</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 구글애즈 키워드 플래너: 현실적인 키워드 입찰가를 중심으로 확인</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+        <x:b val="1"/>
+      </x:rPr>
+      <x:t>&gt; Segmentation A(</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t>트랜드 탐색, 검색 선호하는 유형)</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>- 해당 키워드가 우리 업종, 업계, 산업과 연관성을 가질 수록 유리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 전자상거래 이벤트 -&gt;purchase conversion rate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 이미지, 카피, CTA -&gt; 해당 3개 요소를 모두 바꿔서 하자!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>폼 형식의 광고를 보고 소비자들이 최대한 많이 참여할 수 있도록 할때</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(*세션-&gt; 30분 시간을 기준으로 사용자의 액션행위 체크 단위)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">-어떻게 메세지를 전달, 어ᄄᅠᆫ 컨텐츠로 접근, 가치를 부여? </x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 그래서 무진사는 당신에게 맞는 스타일을 먼저 큐레이션해드립니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문제1: 실제 유입이 저조/ 우리 홈페이지(브랜드 ) 인지도 낮음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대 30초 / 북미 시장 가능, 국내 광고 -&gt; 구글과의 협의 필요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Before(이전) -&gt;After(이후) -&gt; Bridge(단계)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15초까지 무조건 영상을 다 봐야하는 부담 -&gt; 인지도, 각인효과 기대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 포털 사이트 등을 통한 자연 검색 유입 비중 20% 이상 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; "합리적"이라는 것의 정의 = 심리적으로 받아들여질 수 있는 가격</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 사용자가 관심상품으로 선택한 상품을 재조회하는 재조회률 30% 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4) Promotion 전략(어떤 메세지로 소비자를 설득할 것인가)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 상품 목록페이지 기준, 상품 상세페이지 이동 유입경로 분석 보고서</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구글 포털사이트 &gt; 쇼핑 관련 상품명 입력시, 구글 쇼핑 색션 출력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1) Desk Research: 오픈 서베이, 메조미디너, 나스미디어</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">&gt; 자사 자산을 스캔, 검색, 조회를 통해 인지 +리뷰 데이터 조회 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>(*우리 홈페이지에 유입되는 신규사용자 -New Visitor 수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WO전략: 약점의 개선으로 시장의 기회요소를 최대한 활용하겠다는 전략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4. GAds는 해당 데이터를 활용하여 잠재고객 설정-&gt; 우선광고 집행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인지도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>,</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> </x:t>
+  </x:si>
+  <x:si>
+    <x:t>참여</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ex)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CPS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판매</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>트래픽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CPE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CPC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성장기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>단계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인피드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호기심</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>개인화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도입기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쇼핑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검색</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1회</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역할</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>`</x:t>
+  </x:si>
+  <x:si>
+    <x:t>앱</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성숙기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>앱홍보</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>담당자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쇠퇴기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2회</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산출물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동영상</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">- </x:t>
+  </x:si>
+  <x:si>
+    <x:t>백종원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CPA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CPM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김승리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A/B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt;Secondary Target</x:t>
+  </x:si>
+  <x:si>
+    <x:t>광고 컨텐츠 소재 기획, 제작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 출근룩 카테고리 구매 비중 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> &gt;Primary Target</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여러상품 클릭, 가격/리뷰 비교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>핵심 상품 특장점 소개 전략 문서</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 페이지 체류시간 매우 짧음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 25~34세 직장인 68%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>텍스트 신쟁 시, 변수는 1개 원칙</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지금 구매하는것이 현명한 선택일까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 상품 상세페이지 진입률 상승</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리뷰좋은 데일리룩 추천을 발견</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불편한점 (pain point)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; SKU 부족: 상품 다양성 부족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키워드 경쟁력: RoAS, ROI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20. Ads Campaign</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; 확고한 1위 독점적 지위 확보</x:t>
+  </x:si>
+  <x:si>
+    <x:t>O-Opportunity (기회)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>행동-&gt; 추천받기 /지금 보기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-특히 신상품 출시 많은 관심</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Media 활용 순서 및 흐름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-SNS컨텐츠 소비를 많이하는 고객</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 채널별 경쟁사, 아이템별 경쟁자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설득할 수 있을만한 요소 부족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4. User Reaserch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-Product Life Cycle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>혜택, 신뢰, 시의성, 긴급성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 컨텐츠: 가치 추구형 컨텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RFM Score 기준 테이블</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 네이버 광고 센터 - 연관키워드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; High End :고가전략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 필요에 의해서 단발성 구매</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상품 기본정보 서비스 요약정리</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">구조 개선이 필요한 단계 : </x:t>
+  </x:si>
+  <x:si>
+    <x:t>S- Strength (강점)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>*각 전략마다 3-5개 정도 수립</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Acquisition (유입단계)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 직업: IT 기업 마케팅 매니저</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가치-&gt; 리뷰좋은 /가성비/인기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 출근 준비가 훨씬 가벼워진 하루</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직접 오프라인 방문 유도를 위함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-조회,구독 높아지는 경향:자극적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키워드 예산// 검색정도//클릭률</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구체적이며 동종업계 -&gt;경쟁사 나열</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잠재고객의 어ᄄᅠᆫ 행위가 발생</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bottom of Funneel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감정 -&gt; 고민끝/ 자신감/ 편안함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상품 판매효과 극대화 광고탬페인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>건너뛸 수 없는 일반 광고(CPM)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt;월 신규 방문자 5,000명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19. 3P Media Mix</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오프라인 매장 방문 및 프로모션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; K-패션, 스타일 관심도 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 기술력, 가격, 가성비, 컨텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상품 판매.할인가 포지셔닝 정의</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; 약점대비 현재 업종의 활황기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRM 채널 설계 및 프로세스 구축</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마케팅 프로세스 진행.전개 &gt;체감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 키워드 확인 &amp; 예산 결정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6) 메타 비즈니스 관리자 접속</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A 일상에서의 라이프스타일 연상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가치: 리뷰기반 가성비 스타일 추구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상황-&gt; 출근룩/ 데일리룩/오피스룩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1000회 노출당 광고 과금 방식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사용자의 참여유도를 위한 광고캠페인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) 이미지 스타일 다르게 A/B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLICK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>트래픽, 참여</x:t>
+  </x:si>
+  <x:si>
+    <x:t>광고순서</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOFU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VEIW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACTION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실적 최대화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>디스플레이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동영상 조회수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- KPI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잠재고객</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진척사항</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고객행동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포털 사이트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유입/첫인상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감성자극</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">cCPI: </x:t>
+  </x:si>
+  <x:si>
+    <x:t>*CTA 문구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61이상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ex)전화번호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MILIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOFU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOFU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구매횟수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>앱 프로모션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>짧고 강렬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메인 카테고리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11. NPD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구매결정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전략,기획</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상세검토</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세부 카테고리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) BAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8. STP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-충동구매가능</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7. RFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recency</x:t>
+  </x:si>
+  <x:si>
+    <x:t>관심 + 불안</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최우선 고객</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8~18만원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 가격 민감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 실행전략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미완성 기억</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Low(1점)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이벤트 세팅</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-계정 1개당</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13. 4P</x:t>
+  </x:si>
+  <x:si>
+    <x:t>홈페이지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>관심 + 피로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이탈/재방문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8만원 이하</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엄브렐러 전략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키워드 분류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D-DAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A/B 테스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>할인정책 설계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시각 만족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무진사:</x:t>
+  </x:si>
+  <x:si>
+    <x:t>책임의식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>총 구매금액</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mid(2점)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고객생각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14. PLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18만원 이상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원웨이 전략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31~60일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 문제정의</x:t>
+  </x:si>
+  <x:si>
+    <x:t>탐색/비교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A 감성형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B 문제해결형</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">유튜브 내 특정 키워드 검색시, 검색바 우측 상단 |하단 값과 함께 노출되는 광고 (썸네일이미지+ 텍스트 방식) -&gt; 썸네일 클릭시 요금 부과                                                                                                                                 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://docs.google.com/forms/d/e/1FAIpQLSdXs6_v4ofkPICNDYSSmO6x1yRrk0WiNohaSWJVGXX6soOiBQ/viewform</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-Low Fidelity WireFrame :저품질 와이어 프레임 -&gt; 일체의 채색없이 오롯이 선과 무채색만으로 컨텐츠 프레임 완성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; GA4: 사용자들이 우리 사이트 유입,방문 &gt; 어ᄄᅠᆫ 페이지,얼만큼 시간 체류 이탈&gt; 이벤트 활용 /전환/재방문 =&gt; 세션전환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 동질집단 분석 보고서(cohort=동질집단). 1월 2주차 프로모션 행사를 통해서 유입된 사용자들의 7일내 재방문율 25% 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 단순히 저렴한 금액으로 상품 판매,해당 서비스가 이 가격대에 충분히 합리적이고, 만족스럽다는 느낌을 가질 수 있도로 설계하는 과정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4) 힉의 법칙(Hick's Law) : 소비자가 어떤 것을 선택하려고 할 때, 지나치게 옵션이 많으면 결정장애 유발 =&gt; 5개 이하</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8) 게슈탈트 심리학 :  유사성의 법칙 -&gt;  비슷한 속성값을 가지고 있는 요소들을 비슷한 컬러, 도형으로 만들수록 기억에 오래남음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 네이버 데이터랩(이커머스 쇼핑업종 &gt; 연,상하반기 .분기.월 단위 -&gt; 어ᄄᅠᆫ 업종의 어떤 키우ㅝ드가 이슈) : 트랜드 추이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- Objective (미시적 목표) : 사용자가 자발적으로 Earned Media에 가서 상품 및 서비스를 공유, 광고 비율 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; SNS 등 Owned Media를 통한 유입비중 10% 이상 증가 &amp; 우리 홈페이지(브랜드) 접속시 CTR 3% 이상 기록</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -614,113 +915,305 @@
     </x:r>
   </x:si>
   <x:si>
+    <x:t>문제 3: 유입 존재, 구매전환률 보통, 재방문 거의 전무/ 우리 홈페이지(브랜드) 기술적, 시각적,기능적 차별화 포인트 부재</x:t>
+  </x:si>
+  <x:si>
     <x:t>실제 우리 상푸 및 서비스와 유사한 광고를 보고 상품을 시제 구매한 이력을 가지고 있는 소비자들을 대상으로 광고하고자 할때</x:t>
   </x:si>
   <x:si>
-    <x:t>&gt; SNS 등 Owned Media를 통한 유입비중 10% 이상 증가 &amp; 우리 홈페이지(브랜드) 접속시 CTR 3% 이상 기록</x:t>
-  </x:si>
-  <x:si>
     <x:t>&gt; 상품 목록페이지 (PLP= Product List Page) -&gt; 상품 상세페이지 이동할때 발생하는 클릭률 35% 이상 증가</x:t>
   </x:si>
   <x:si>
-    <x:t>TPO: Time Place Occasion -&gt;ex) 출근룩/ 데일리룩/ 봄코디/ 오피스룩/ 소개팅룩 /하객룩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 여러가지 업무들이 순차적/ 동시다발적으로 전개되어야하는데, 각 담당자들이 누구이며 마감기한이 언제까지인지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 최초에 특정 브랜드가 런칭했을 때의 상항에서의 4P전락이 시간경과에 따라서 일치하지 않은 확률이 매우 높음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt;CRM (Customer Relationship Management). Email 발송 후클릭률 8% 이상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAds: GA4를 통해 수집된 사용자의 데이터 정보를 받아서 해당 사용자들을 잠재고객이라는 이름으로 관리를 함.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(*CTR 데이터 수집,분석 : page_view 이벤트 / click_purchase_button 이벤트)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 소비성향 : 합리적이고 가성비있는 소비 지향/ 가격대비 활용도 중요/ 브랜드 이름보다는 스타일링 및 코디 관심</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 당연적 요소 컨텐츠: 소비자 입장에서 당연히 있어야 할것으로 기대하는 컨텐츠 
-(ex. 쇼핑몰 - 검색창 )</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카페 24 접속 &gt; 쇼핑몰 설정 &gt; 기본설정 &gt; 검색엔진 최적화(SEO) &gt; 코드 직접 입력 &gt; 코드 붙여넣기</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">앱 다운로드를 유도                                                    </x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 이미지, 카피, CTA -&gt; 해당 3개 요소를 모두 바꿔서 하자!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필터 및 검색기능 강화, 상품정보 큐레이션 UI/UX 개선</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">- 지금 당장 고객들이 원하는 니즈 파악 + 장기적인 방향? </x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 합리적 소비를 위한 상품비교가 익숙한 25-34 직장인 여성</x:t>
+    <x:t>1) 비선형편집 (넌리니어 편집) : 선이 연결되지 않는 장비를 가지고 편집 -&gt; 윈도우 : 프리미어, 애프터이펙트, 베가스 / 파이널컷프로</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t xml:space="preserve">- </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+        <x:b val="1"/>
+      </x:rPr>
+      <x:t>포털 사이트 내 사용자가 키워드 검색</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t>시,  AI가 키워드 및 질문에 대한 답변으로 우리의 컨텐츠가 채택될 수 있도록 컨테츠 기획.제작</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>-블로그 등 텍스트 기반의 컨텐츠를 활용해서 포털사이트 내 사용자가 특정 키워드 검색 시, 자사 켄텐츠가 상위노출 되도록 하는 전략 방법</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 6mm 테입 / 이동형 vj 카메라 (pd150, 170, z1000)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; Figma &amp; Slack &amp; Notion + Braze / Zapier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>광고메세지는 굉장히 감성 0 -&gt; 우리 타겟고객에게는 잘 와닿지않는 메세지x</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구글 ai에 예산을 위탁 -&gt;  해당 예산으로 구글이 다양한 채널 대리 집행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>product = 실물 상품만 의미 X (플랫폼, 서비스, 교육, 컨텐츠 등)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 유튜브 동영상 컨텐츠 노출 &gt; 브랜드/상품의 존재 먼저 인지한 경우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; STP전략의 Positioning에서 도출된 방향성과 정체성 반드시 일치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자사 브랜드 및 상품의 인지도를 최대한 많이 효과적으로 높이거나 알리고자 할때</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-타겟 중요성: 너무 좁혀놓고 모집단(모수)너무 적은 상황 -&gt; 예산 소진 x</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실제 광고를 보고 우리의 사이트(랜딩 페이지)에 최대한 많이 유입시키고자 할때</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) Field Research: 해당 업종 관계자, 전문가 섭외, 인터뷰</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 직장인 데일리룩 구매, 큐레이션 효과적으로 추천 -&gt; 고객 만족도 경험</x:t>
+  </x:si>
+  <x:si>
+    <x:t>=&gt; 예쁘기 때문에, 더 비싸도 살거야! =&gt; 가격의 합리적이게 다가오것</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) Price 전략 (해당 브랜드, 상품은 어떤 가격대에 포지셔닝 인식)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3) Place 전략(어디에서 어ᄄᅠᇂ게 소비자의 경험을 제공할 것인가)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>출근룩 고민때문에 아침시간이 부족했다면 
+지금바로 스타일 추천 받아보세요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; 주간 구매 사용자수(Weekly Purchasing Users) 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoAS: Return On Ads Spend: 마케팅 비용대비 ,매출액</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 경쟁업체의 현 판매가를 가장 높은 비중으로 반영하여 Price전략 구축</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">- 위에서 발견한 고객 성향에 따른 자사 경쟁력 &amp; 개선할 부분까지 나열 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 이전에 온라인으로 출근룩 구매 -&gt; 생각보다 저품질, 소재,주변반응 별로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt;GTM활용 10,25,50,75,90  세부적인 스크롤 깊이 단위까지 확인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 인구통계학적 질문/ 업계 및 브랜드 관심도/ 구매행동기반 / 컨텐츠 소비</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">-High Fidelity WireFrame: 고품질 와이어 프레임 -&gt; </x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 상세페이지 및 컨텐츠 내 기존 소비자 리뷰만족도를 어필할 수 있는 컨텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 힉의 법칙 =&gt; 사람은 너무 많은 성택지를 주먼 오히려 선택을 힘들어한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30일 이내 구매한 한달에 3회 이상 구매한, 총 18만원 이상을 지불한 금액</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 1개의 의류상춤 +화장품+악세사리까지 토탈 코디네이션 &amp; 출근룩 큐레이션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-구매하기 전까지 많은 정보 수집, 비교 -&gt; 구매가지 걸리는 시간 많음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유튜브 내 쇼츠 카테고리 노출되는 광고. 60ch 이하. 세로 형태 타입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 스크롤 깊이(Scroll Depth) 50% 이상 도달률 40% 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리뉴얼 전략 &gt; 기존브랜드 리뉴얼 vs 자매 브랜드런칭(-&gt;엄브렐러 전략)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>애프터이펙트 : 모션 그래픽 프로그램 (캐릭터 움직임 생동감있게) + C4D</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 고구마, 커피, 나이키 &gt; 사이트 내 검색 결과 페이지 순서 상이함.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. 유튜브에 접속한 댓글, 좋아요 등을 한 고객들의 정보를 GAds로 찾아올 필요가 있음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>=&gt; 차선고객이 최우선 고객에 비해 너무 많은 경우 그 부분이 FUNNEL구조에서의 개선점</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> -Objective (미시적 목표): 실질적인 상품 구매 전활융 향상 및 매출 이익 증대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Probelm(문제 자각시키기) -&gt; Agitation (동요) -&gt; Solution(해결)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 목록 페이지 내 클릭 이벤트 세팅 (목록페이지 유입대비, 해당버튼 클릭 수 =&gt; 클릴률</x:t>
+  </x:si>
+  <x:si>
+    <x:t>=-CTA=Call To Action=사용자로 하여금 무언가의 액션을 불러일으키게 하는 요소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 최근 본 | 구매한 상품 기반, 맞춤 스타일 제공 -&gt; 최근 인기 코디 스타일 피드백</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5) 제이콥의 법칙: 소비자는 익숙하고 보편적인 UI/UX 패턴을 선호한다는 심리학 이론</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t xml:space="preserve">대형키워드: </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+        <x:b val="1"/>
+      </x:rPr>
+      <x:t>자본, 인력구조 확보</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t xml:space="preserve"> 상태 &gt; 단기간 내 상위노출 장악 및 실질적 매출 유도</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>- 어느 방향을 향해 나아갈 것인가 = 고객 머리속에 우리는 어떤 이미지로 남고 싶은가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 상품상세페이지 (PDP= Product Detail Page) 조회율 60%이상 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소형키워드 : 중소기업, 자본,인력 미비상태 &gt; 마이크로 시장(작은시장)주도하겠다는 의지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비즈니스 플레이 그라운드 =필드, 앱인경우, 앱 다운로드를 최대한 많이 유도하고자 할때</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 브랜드 인지도 : 정석 시간 + 비용 꾸준한 투자 //SNS활용 재치,  개성 콘텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) 카노모델 (Kano Model): 소비자에게 영향을 주는 컨텐츠는 크게 3가지의 종류</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">3) 밀러의 법칙(Miller's Law) : 사람의 단기 기억에는 정보의 한계가 존재(사람은 한번에 최대 5-9개 사이의 정보만을 기억) </x:t>
+  </x:si>
+  <x:si>
+    <x:t>(*Before VS After: 채널별 유입 비중 -&gt; Paid Social  / Organic Search/ Organic Social )</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1) 멘탈모델 (mental model) : 소비자가 이미 자신의 머리속에 가지고 있는 이미지 및 컨셉을 다른 플랫폼, 서비스에서도 기대한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이벤트 관리자 &gt; 데이터 연결 &gt; 새 데이터 소스 연결 &gt; 웹 &gt; 광고계정설정 &gt; (픽셀코드설치) 직접설정 &gt; Meta 픽셀전용 &gt; 코드 복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6초 이하의 길이만 허용, 최대한 짧은 시간 내 브랜드를 각인시키고자 집행하는 광고 =&gt; 건너뛰기 없음,  유튜브 영상 앞,끝,중간 모두 가능</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 매력적 요소 컨텐츠 : 전혀 기대안했는데, 있음으로써 매우 큰 감동을 느끼는 컨텐츠 (AI기반 추천 시스템 기능)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 일원적 요소 컨텐츠: 있으면 있을수록 만족하지만, 없으면 없을수록 불편한 컨텐츠
+(ex) 쇼핑몰 - 상세 필터기능)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> -Objective (미시적 목표): 사용자가 및 방문자가 실제 상품을 구매할 수 있는 직.간접적인 행위의 지표가 상승</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) 픽셀 추적 코드 : 이벤트 설정 -&gt; 사용자의 액션행위 수집 -&gt; 기반 리타겟팅 광고 캠페인(*광고 효율성 극대화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 앞에서 수집한 고객정보를 기반으로 최우선 고객집단(그룹)을 정의하는데 있어서 단순 경험, 의견을 바탕으로 결정 X</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도구 &gt; 계획 &gt; 키워드 플래너 &gt; 새 키워드 찾기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Paid Media (또 다른 신규 고객 유입 창출)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Earned Media (좋은 피드백 기록, 공유)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 메타(인스타그램, 페이스북), 구글애즈 (유튜브)</x:t>
   </x:si>
   <x:si>
     <x:t>구글 포털사이트 내 키워드 검색시 노출되는 검색광고</x:t>
   </x:si>
   <x:si>
+    <x:t>3. GA4,GTM을 통해서 받은 데이터를 다시 GAds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; 직곽적x : 초반 매출, 영업이익 드리프트 저조</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 구글 트랜드 (글로벌 시장 &gt; 검색 키워드 서칭)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://business.facebook.com/</x:t>
+  </x:si>
+  <x:si>
     <x:t>1) 유튜브 광고 컨텐츠를 기획. 제작 -&gt; 랜딩페이지</x:t>
   </x:si>
   <x:si>
-    <x:t>도구 &gt; 계획 &gt; 키워드 플래너 &gt; 새 키워드 찾기</x:t>
-  </x:si>
-  <x:si>
     <x:t>유튜브 채널을 활용한 상품 밑 브랜드 인지도 활성화</x:t>
   </x:si>
   <x:si>
-    <x:t>3. GA4,GTM을 통해서 받은 데이터를 다시 GAds</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Paid Media (또 다른 신규 고객 유입 창출)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-&gt; 직곽적x : 초반 매출, 영업이익 드리프트 저조</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 구글 트랜드 (글로벌 시장 &gt; 검색 키워드 서칭)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://business.facebook.com/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Earned Media (좋은 피드백 기록, 공유)</x:t>
-  </x:si>
-  <x:si>
     <x:t>4) 데스크탑 &gt; 페이스북 사이트 접속 &gt; 페이지 생성</x:t>
   </x:si>
   <x:si>
     <x:t>- 개인화 맞춤전략 -&gt; 고객 맞춤형 추천 경험 제공</x:t>
   </x:si>
   <x:si>
-    <x:t>&gt; 메타(인스타그램, 페이스북), 구글애즈 (유튜브)</x:t>
+    <x:t>온라인 &gt; 상품 목록페이지 &gt; 띠베너 &gt; 상품구매 유도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>꾸준한 컨텐츠 제작 + 컨텐츠의 전문성 + 소비자의 리뷰</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 옷장 앞에서 여러 옷을 걸쳐보면서 고민하던 아침</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 중형키워드 모두가 다 대형키워드가 된다는 보장 X</x:t>
+  </x:si>
+  <x:si>
+    <x:t>특정 키워드 검색 입력시, 이에 대한 해결관련 컨텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">&gt; 매일 아침 출근룩 선택으로 몇분씩 고민중이신가요? </x:t>
   </x:si>
   <x:si>
     <x:t>- 반드시 모든 브랜드,상품은 저마다의 수명주기 존재</x:t>
   </x:si>
   <x:si>
-    <x:t>온라인 &gt; 상품 목록페이지 &gt; 띠베너 &gt; 상품구매 유도</x:t>
-  </x:si>
-  <x:si>
     <x:t>타겟:  25-34 직장인 여성(합리적 비교 소비형)</x:t>
   </x:si>
   <x:si>
-    <x:t>&gt; 옷장 앞에서 여러 옷을 걸쳐보면서 고민하던 아침</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스타일 확인, 코디완성, 지금바로 확인하기, 추천받기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메시지를 통해 사용자의 구체적인 행동 유도 (CTA)</x:t>
+    <x:t>가성비, 가심비, 활용도, 리뷰좋은, 인기상품, best</x:t>
   </x:si>
   <x:si>
     <x:t>&gt; 직장인을 위한 전문 데일리룩 AI큐레이션 몰, 무진사</x:t>
@@ -730,37 +1223,58 @@
 TOP 스타일</x:t>
   </x:si>
   <x:si>
+    <x:t>스타일 확인, 코디완성, 지금바로 확인하기, 추천받기</x:t>
+  </x:si>
+  <x:si>
     <x:t>5) 인스타그램 프로페셔널 계정 &amp; 페이스북 페이지 연동</x:t>
   </x:si>
   <x:si>
-    <x:t>특정 키워드 검색 입력시, 이에 대한 해결관련 컨텐츠</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 중형키워드 모두가 다 대형키워드가 된다는 보장 X</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">&gt; 매일 아침 출근룩 선택으로 몇분씩 고민중이신가요? </x:t>
+    <x:t>메시지를 통해 사용자의 구체적인 행동 유도 (CTA)</x:t>
   </x:si>
   <x:si>
     <x:t>가격 부담없이 세련된 스타일을 완성할 수 있습니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>가성비, 가심비, 활용도, 리뷰좋은, 인기상품, best</x:t>
-  </x:si>
-  <x:si>
     <x:t>- 어떤 컬러, 타이포그래피, 레이아웃으로 무드보드 생성</x:t>
   </x:si>
   <x:si>
-    <x:t>꾸준한 컨텐츠 제작 + 컨텐츠의 전문성 + 소비자의 리뷰</x:t>
+    <x:t>AI 활용 기술적 업그레이드 -&gt; 맞춤 추천 기술 도입</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">                               </x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 참여도 획득 보고서를 통해서 평슌 세션 확인 가능</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-각 비즈니스 포트폴리오별 광고계정(갯수 제한 x)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 직장인을 위한 합리적인 데일리룩 큐레이션 쇼핑몰</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 계속적으로 트랜드한 브랜드, 아이템 추종(유목민)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 광고 캠페인을 활용한 유입비중 40% 이상 증가</x:t>
   </x:si>
   <x:si>
     <x:t>- RFM분석 대상 -&gt; 구매경험 1,050명 대상</x:t>
   </x:si>
   <x:si>
+    <x:t>3) FGI: Focus Croup Interview</x:t>
+  </x:si>
+  <x:si>
     <x:t>&gt; 추천 링크를 활용한 구매 발생 비율 10% 이상 증가</x:t>
   </x:si>
   <x:si>
-    <x:t>- 계속적으로 트랜드한 브랜드, 아이템 추종(유목민)</x:t>
+    <x:t>- 트랜드 민감, SNS검색 후 비교 및 자기개성 어필</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt;평균세션(Avg Session) 시간 2분 이상 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA4: 우리 사이트에 방문하는 사용자의 트래픽 수집</x:t>
   </x:si>
   <x:si>
     <x:t>&gt; SNS 및 포털사이트를 통한 외부유입 15% 증가</x:t>
@@ -769,68 +1283,53 @@
     <x:t>&gt; 지난 3개월 시간 무진사 홈페이지(브랜드) 실적 가정</x:t>
   </x:si>
   <x:si>
-    <x:t>&gt; 광고 캠페인을 활용한 유입비중 40% 이상 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3) FGI: Focus Croup Interview</x:t>
-  </x:si>
-  <x:si>
     <x:t>-(오픈마켓, 종합몰, 편집샵, 독립목,소셜커머스 등</x:t>
   </x:si>
   <x:si>
-    <x:t>GA4: 우리 사이트에 방문하는 사용자의 트래픽 수집</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 트랜드 민감, SNS검색 후 비교 및 자기개성 어필</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AI 활용 기술적 업그레이드 -&gt; 맞춤 추천 기술 도입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt;평균세션(Avg Session) 시간 2분 이상 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">                               </x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 참여도 획득 보고서를 통해서 평슌 세션 확인 가능</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-각 비즈니스 포트폴리오별 광고계정(갯수 제한 x)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 직장인을 위한 합리적인 데일리룩 큐레이션 쇼핑몰</x:t>
-  </x:si>
-  <x:si>
     <x:t>상품 상세페이지 내 리뷰정보 요약 노출, 패션 코디 제안</x:t>
   </x:si>
   <x:si>
     <x:t>&gt; 가격 경쟁 치열 - 출혈경쟁으로 인한 사업성 악화</x:t>
   </x:si>
   <x:si>
+    <x:t>-특정 브랜드의 충성도보다 본인만의 개성적인 스타일 중요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 트랜드 패션에 관심이 높은 2530 프리랜서 여성</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">-우리 홈페이지(브랜드)를 통해서 매출, 이익이 발생 </x:t>
   </x:si>
   <x:si>
-    <x:t>-특정 브랜드의 충성도보다 본인만의 개성적인 스타일 중요</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 트랜드 패션에 관심이 높은 2530 프리랜서 여성</x:t>
+    <x:t>- 패션성향 : 출근룩, 데일리 캐주얼룩 중심/ 너무 튀는 스타일 부담 &amp; 세련됨 +무난함추구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GTM: 우리 사이트에 접속한 사용자 가운데 주요한 이벤트를 클릭한 사람들을 선별하고자 할 때</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. 유튜브 채널을 통해 우리와 소통중인 고객들에게 우리 사이트의 광고를 우선적으로 노출(효과)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>광고소재 15~30초/ 최소 6초, 5초 경과 후  -&gt; 과금되는 시점: 30초 이상 영상 시청</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-구체적인 브랜드 혹은 상품 슬로건(Just do it, nothing is impossible)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>*우리사이트의 존재를 먼저 인지한 경우, 해당 고객을 주요 잠재고객으로 인식 후 광고 캠페인 집행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-목표달성: 무신사 홈페이지 목적: 패션상품 큐레이션 (추천) + 사용자 구매유도 → 매출, 이익</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-경쟁사 역시, 위에서 분석한 고객 성향에 따른 차별점= 특징 &amp; 개선할 부분 유츄+ 정보수집</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7) 폰 레스토프 효과 : 이질성의 효과, 강조와 지강조 컨텐츠가 동시에 존재해야 둘다 인식된다</x:t>
   </x:si>
   <x:si>
     <x:t>매일 아침 옷장 앞에서 고민했다면 이제 빠르게 선택!
 1000만명이 선택한 리뷰좋은 데일리룩 추천</x:t>
-  </x:si>
-  <x:si>
-    <x:t>광고소재 15~30초/ 최소 6초, 5초 경과 후  -&gt; 과금되는 시점: 30초 이상 영상 시청</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2. 유튜브 채널을 통해 우리와 소통중인 고객들에게 우리 사이트의 광고를 우선적으로 노출(효과)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-목표달성: 무신사 홈페이지 목적: 패션상품 큐레이션 (추천) + 사용자 구매유도 → 매출, 이익</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-경쟁사 역시, 위에서 분석한 고객 성향에 따른 차별점= 특징 &amp; 개선할 부분 유츄+ 정보수집</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -866,25 +1365,10 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>7) 폰 레스토프 효과 : 이질성의 효과, 강조와 지강조 컨텐츠가 동시에 존재해야 둘다 인식된다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>*우리사이트의 존재를 먼저 인지한 경우, 해당 고객을 주요 잠재고객으로 인식 후 광고 캠페인 집행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 패션성향 : 출근룩, 데일리 캐주얼룩 중심/ 너무 튀는 스타일 부담 &amp; 세련됨 +무난함추구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-구체적인 브랜드 혹은 상품 슬로건(Just do it, nothing is impossible)</x:t>
-  </x:si>
-  <x:si>
     <x:t>&gt; 컨텐츠 기획 기본 방향 수립（광고 톤앤매너, 배경컬러, 웹사이트 메인베너, 상세페이지, CRM</x:t>
   </x:si>
   <x:si>
     <x:t>우리가 취급하는 상품 및 서비스를 구매할 확률이 높은 소비자들을 대상으로 광고를 노출하고자ᄒᆞᇂ때</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GTM: 우리 사이트에 접속한 사용자 가운데 주요한 이벤트를 클릭한 사람들을 선별하고자 할 때</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -901,577 +1385,70 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>4) 힉의 법칙(Hick's Law) : 소비자가 어떤 것을 선택하려고 할 때, 지나치게 옵션이 많으면 결정장애 유발 =&gt; 5개 이하</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-Low Fidelity WireFrame :저품질 와이어 프레임 -&gt; 일체의 채색없이 오롯이 선과 무채색만으로 컨텐츠 프레임 완성</x:t>
+    <x:t>- 쇼핑성향 : 월평균 1~2회 온라인 의류쇼핑 진행 / 1회 구매시, 약 7만원/ 3개월 20만원 구매</x:t>
+  </x:si>
+  <x:si>
+    <x:t>*우리 사이트를 먼저 인지한게 아닌, 우리가 운영중인 구글 유튜브 공식 채널 계정을 먼저 인지한 고객들!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비즈니스 자산 &gt; 데이터 세트 생성(픽셀 코드를 생성한 후 픽셀코드를 통해서 수집한 데이터가 저장될 공간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; UTM url 생성 후 eamil 발송 시, 삽입 -&gt; 해당 url을 통해서 유입한 사용자수 등을 확인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROI: Return On Investment : 마케팅 외 기타 비용 집행 대비 영업 이익(순이익)</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve"> -Objective (미시적 목표): 구매 가능성이 높은 기존 구매 사용자의 재방문 효과적으로 유도</x:t>
   </x:si>
   <x:si>
-    <x:t>비즈니스 자산 &gt; 데이터 세트 생성(픽셀 코드를 생성한 후 픽셀코드를 통해서 수집한 데이터가 저장될 공간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 쇼핑성향 : 월평균 1~2회 온라인 의류쇼핑 진행 / 1회 구매시, 약 7만원/ 3개월 20만원 구매</x:t>
-  </x:si>
-  <x:si>
-    <x:t>*우리 사이트를 먼저 인지한게 아닌, 우리가 운영중인 구글 유튜브 공식 채널 계정을 먼저 인지한 고객들!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; UTM url 생성 후 eamil 발송 시, 삽입 -&gt; 해당 url을 통해서 유입한 사용자수 등을 확인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROI: Return On Investment : 마케팅 외 기타 비용 집행 대비 영업 이익(순이익)</x:t>
-  </x:si>
-  <x:si>
     <x:t>- 하이엔드 고가전략, 프리미엄 브랜드 -&gt; 프로모션 전략을 철저하게 계획하에 장기적인 관점에서 실행</x:t>
   </x:si>
   <x:si>
     <x:t>3) 스마트폰 : 인스타그램 앱 접속 &gt; 설정 &gt; 계정 설정 변환(일반 -&gt; 프로페셔널 계정 =비즈니스)</x:t>
   </x:si>
   <x:si>
-    <x:t>- 어느 방향을 향해 나아갈 것인가 = 고객 머리속에 우리는 어떤 이미지로 남고 싶은가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소형키워드 : 중소기업, 자본,인력 미비상태 &gt; 마이크로 시장(작은시장)주도하겠다는 의지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5) 제이콥의 법칙: 소비자는 익숙하고 보편적인 UI/UX 패턴을 선호한다는 심리학 이론</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 최근 본 | 구매한 상품 기반, 맞춤 스타일 제공 -&gt; 최근 인기 코디 스타일 피드백</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3. 유튜브에 접속한 댓글, 좋아요 등을 한 고객들의 정보를 GAds로 찾아올 필요가 있음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비즈니스 플레이 그라운드 =필드, 앱인경우, 앱 다운로드를 최대한 많이 유도하고자 할때</x:t>
-  </x:si>
-  <x:si>
-    <x:t>=&gt; 차선고객이 최우선 고객에 비해 너무 많은 경우 그 부분이 FUNNEL구조에서의 개선점</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t xml:space="preserve">대형키워드: </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="맑은 고딕"/>
-        <x:sz val="11"/>
-        <x:color rgb="ff000000"/>
-        <x:b val="1"/>
-      </x:rPr>
-      <x:t>자본, 인력구조 확보</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="맑은 고딕"/>
-        <x:sz val="11"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t xml:space="preserve"> 상태 &gt; 단기간 내 상위노출 장악 및 실질적 매출 유도</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 상품상세페이지 (PDP= Product Detail Page) 조회율 60%이상 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2) 카노모델 (Kano Model): 소비자에게 영향을 주는 컨텐츠는 크게 3가지의 종류</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> -Objective (미시적 목표): 실질적인 상품 구매 전활융 향상 및 매출 이익 증대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 목록 페이지 내 클릭 이벤트 세팅 (목록페이지 유입대비, 해당버튼 클릭 수 =&gt; 클릴률</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 브랜드 인지도 : 정석 시간 + 비용 꾸준한 투자 //SNS활용 재치,  개성 콘텐츠</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Probelm(문제 자각시키기) -&gt; Agitation (동요) -&gt; Solution(해결)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중형키워드: 검색은 일어나고 있지만 아직 확실한 트랜드로 부상하지 않은 키워드 그룹/ 잠재력 존재 &gt; 대형키워드 기준 상대적 적은 자본으로도 선점 //  리스크-&gt; 키워드 성장 후 대형키워드 부상</x:t>
+    <x:t>&gt; 상품 연출 컷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>디맨드젠 캠페인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>굳이 리뷰언급 x</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">4) 감성제안 </x:t>
   </x:si>
   <x:si>
-    <x:t>Funnel 구조 설계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>promotion 전략실행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mid of fUnnel</x:t>
+    <x:t>B 상품스펙을 강조</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1) 메세지 유형 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>리뷰 별표표시 강조</x:t>
+  </x:si>
+  <x:si>
+    <x:t>웹사이트 트래픽</x:t>
   </x:si>
   <x:si>
     <x:t>&gt; 출근룩 고민 끝!</x:t>
   </x:si>
   <x:si>
-    <x:t>B 상품스펙을 강조</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 상품 연출 컷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>리뷰 별표표시 강조</x:t>
-  </x:si>
-  <x:si>
-    <x:t>굳이 리뷰언급 x</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>-</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="맑은 고딕"/>
-        <x:sz val="11"/>
-        <x:color rgb="ff000000"/>
-        <x:b val="1"/>
-      </x:rPr>
-      <x:t xml:space="preserve"> 충성도가 높은 전략 -&gt; 1인당 고객 LTV높게 </x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t xml:space="preserve">- </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="맑은 고딕"/>
-        <x:sz val="11"/>
-        <x:color rgb="ff000000"/>
-        <x:b val="1"/>
-      </x:rPr>
-      <x:t>명확한 고객행동지표를 기반으로 선정하기 위한 중간절차</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1) 메세지 유형 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>디맨드젠 캠페인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>웹사이트 트래픽</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">2) 탐색 -&gt; 비교 </x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">280명 : M/L/L </x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">- 장바구니에 담는 전환률 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>개선 (solution)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8만원 이하 -&gt;Lovw</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1) 유입 -&gt;  첫인상 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>-첫 구매 만족도 높음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>차선고객 = 성장가능 고객</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메인배너, 추천상품 스캔</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30일 이내-&gt; High</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5) 이탈 또는 재방문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1순위: Revenue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- KeyResults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-&gt;KPI(핵심성과지표)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-Key Results</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18. Wire Frame</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">product 전략 실행 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>4) Form활용 리서치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-할인 시즌만 겨냥해서 구매</x:t>
-  </x:si>
-  <x:si>
-    <x:t>90일 이상 -&gt; Low</x:t>
-  </x:si>
-  <x:si>
-    <x:t>160명: RFM H/H/H</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 공유하기 버튼 클릭횟수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 평균 객단가 22만원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 회원가입:3,200명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 브랜드 충성도 매우 낮음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 직장인 코디네이션 및 큐레이팅 최대한 어필될 수 있는 컨텐츠</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; cart conversion rate(장바구니 전환율)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>찜, 쿠폰, CRM, 리타게팅 마케팅을 통해서 재방문율 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 자사 경쟁력(상품, 플랫폼, 서비스, 기술 등) 기반 분석</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사용자의 특정행위에 따른 광고 과금 방식(회원가입,다운로드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 선별된 키워드 활용 -&gt; 광고카피 문안 변환 (채널별)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-트랜디함을 좋아하는 고객들로 추정, 우연하게 브랜드 노출</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SO전략: 강점을 활용한 시장의 기회요소를 포착하겠다는 전략</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt;GA4,GTM 등의 트래픽 수집, 분석 툴 데이터 취합 비교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>리뷰와 데이터를 기반으로 실패없는 데일리 패션을 경험하세요</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 공식 인스타계정, 유튜브계정, 공식 블로그 계정,사이트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12. WBS = Work Breakdown Structure</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-Product/ Price / Place / Promtion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; GA4 &gt; 데이터 스트림 코드를 통해서 삽압 vs 구글</x:t>
-  </x:si>
-  <x:si>
-    <x:t>니즈: 출근 시 선택할 수 있는 출근룩 관련 스트레스 감소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- UX/UI 전략(눈에 보이는 시각적인 서비스 개선. 효율성)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-&gt; 출혈경쟁 (단가경쟁) -&gt; 원가 절감 성공한 기업만 생존</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 유료의 비용을 지불하고 사용자들의 트래픽을 획득하는 매체</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사용자의 실질적인 참여(댓글등록, 이벤트 영상 )발생되었을</x:t>
-  </x:si>
-  <x:si>
-    <x:t>리크스 관리(해야할 것, 하지말아야할 것, 우선시 해야할 것)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1) Desk Research: 오픈 서베이, 메조미디너, 나스미디어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 상품 목록페이지 기준, 상품 상세페이지 이동 유입경로 분석 보고서</x:t>
-  </x:si>
-  <x:si>
-    <x:t>폼 형식의 광고를 보고 소비자들이 최대한 많이 참여할 수 있도록 할때</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15초까지 무조건 영상을 다 봐야하는 부담 -&gt; 인지도, 각인효과 기대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구글 포털사이트 &gt; 쇼핑 관련 상품명 입력시, 구글 쇼핑 색션 출력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(*세션-&gt; 30분 시간을 기준으로 사용자의 액션행위 체크 단위)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">-어떻게 메세지를 전달, 어ᄄᅠᆫ 컨텐츠로 접근, 가치를 부여? </x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 구글애즈 키워드 플래너: 현실적인 키워드 입찰가를 중심으로 확인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 사용자가 관심상품으로 선택한 상품을 재조회하는 재조회률 30% 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문제1: 실제 유입이 저조/ 우리 홈페이지(브랜드 ) 인지도 낮음</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">&gt; 자사 자산을 스캔, 검색, 조회를 통해 인지 +리뷰 데이터 조회 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 해당 키워드가 우리 업종, 업계, 산업과 연관성을 가질 수록 유리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(*우리 홈페이지에 유입되는 신규사용자 -New Visitor 수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 그래서 무진사는 당신에게 맞는 스타일을 먼저 큐레이션해드립니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대 30초 / 북미 시장 가능, 국내 광고 -&gt; 구글과의 협의 필요</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Before(이전) -&gt;After(이후) -&gt; Bridge(단계)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 포털 사이트 등을 통한 자연 검색 유입 비중 20% 이상 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-&gt; "합리적"이라는 것의 정의 = 심리적으로 받아들여질 수 있는 가격</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4) Promotion 전략(어떤 메세지로 소비자를 설득할 것인가)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WO전략: 약점의 개선으로 시장의 기회요소를 최대한 활용하겠다는 전략</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="맑은 고딕"/>
-        <x:sz val="11"/>
-        <x:color rgb="ff000000"/>
-        <x:b val="1"/>
-      </x:rPr>
-      <x:t>&gt; Segmentation A(</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="맑은 고딕"/>
-        <x:sz val="11"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>트랜드 탐색, 검색 선호하는 유형)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>4. GAds는 해당 데이터를 활용하여 잠재고객 설정-&gt; 우선광고 집행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 전자상거래 이벤트 -&gt;purchase conversion rate</x:t>
-  </x:si>
-  <x:si>
     <x:t>SNS광고캠페인 문구</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">290명: L/L/L </x:t>
-  </x:si>
-  <x:si>
-    <x:t>18만원 이상 -&gt;High</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3) Positioning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>=&gt; 과소비 X, 합리적o</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마케팅 전략 기획안 발표</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블로그(정보전달 컨텐츠)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- Pain Point:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 구매자: 1,050명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3. FUNNEL 구조 설계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내 취향에 맞는 사이트인가?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-패션 관심도 매우 높음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 니치 마케팅 = 틈새시장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>320명 : H/M/M</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 월소득 :350만원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 1회 구매후 재방문 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상품 상세페이지 기획안 정리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비교하기 쉽게 보고싶어!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5. Journey map</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1) 브랜드 및 상품 정체성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3) Competitor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2순위: Retention</x:t>
-  </x:si>
-  <x:si>
-    <x:t>채널/매체별 메세지 전략</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2) 장기적인 비전  제시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8~18만원 -&gt; Mid</x:t>
-  </x:si>
-  <x:si>
-    <x:t>* 상품 리뷰 의존도 높음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사용자 맞춤 기준 불명확</x:t>
-  </x:si>
-  <x:si>
-    <x:t>* 재방문 유입 확률 높음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월평균 클릭률 1% 마지노선</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Revenue(매출향상)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상품 특장점 인사이트 도출</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3회이상 -&gt; High</x:t>
-  </x:si>
-  <x:si>
-    <x:t>*구글 애즈 유튜브 광고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T-Threat (위협)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>60일 이내 -&gt; mid</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정보 구조 미비, 정보 부족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3) 상세검토 -&gt; 확신형성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 리뷰/평점 확인 필수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-&gt; 생존과 가장 밀접</x:t>
-  </x:si>
-  <x:si>
-    <x:t>광고 캠페인 채널 세팅</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15. 컨텐츠 기획.제작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 충성도가 매우 높음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt;앱푸쉬알람 클릭률5% 이상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 구매전환율 2.5% 달성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3. Earned Media</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2) Targeting</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나에게 맞는 룩 확인하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가설기반 덴드시 테스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>shorts광고 (CPM)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 메타 비즈니스 관리자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초개인화 맞춤 매체전략</x:t>
-  </x:si>
-  <x:si>
-    <x:t>W- Weakness(약점)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Retention(재방문)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타겟 유저 = 페르소나 결정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Top Of Funnel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>앱설치 시 광고과금 방식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1회 클릭당 광고 과금방식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>데스크탑 UI/UX기획</x:t>
-  </x:si>
-  <x:si>
     <x:t>WBS by PM</x:t>
   </x:si>
   <x:si>
     <x:t>객단가 상승 정략</x:t>
   </x:si>
   <x:si>
-    <x:t>퍼널 이벤트 설계</x:t>
-  </x:si>
-  <x:si>
     <x:t>place 전략실행</x:t>
   </x:si>
   <x:si>
-    <x:t>- 실행 일정 관리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 나이 : 31세</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">경쟁정도 중간-낮음 </x:t>
+    <x:t xml:space="preserve">price 전략실행 </x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -1502,388 +1479,710 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">price 전략실행 </x:t>
+    <x:t>2026.04.28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세부 작업내용 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퍼널 이벤트 설계</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">경쟁정도 중간-낮음 </x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">키워드 범주: </x:t>
   </x:si>
   <x:si>
-    <x:t>2026.04.28</x:t>
-  </x:si>
-  <x:si>
     <x:t>(유혹,위기=&gt;자본)</x:t>
   </x:si>
   <x:si>
     <x:t>- 온라인.포으라인</x:t>
   </x:si>
   <x:si>
-    <x:t>세부 작업내용 설명</x:t>
-  </x:si>
-  <x:si>
     <x:t>=&gt; 일관성 흐트러짐</x:t>
   </x:si>
   <x:si>
     <x:t>-&gt; 2인자의 전략</x:t>
   </x:si>
   <x:si>
+    <x:t>- 실행 일정 관리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 나이 : 31세</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EX)한경희 생활과학</x:t>
+  </x:si>
+  <x:si>
     <x:t>&gt; 성.비수기 존재</x:t>
   </x:si>
   <x:si>
+    <x:t>EX) 아모레퍼시픽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카카오 (메신저)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4) 행동 키워드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3회 이상 구매</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16. 무드보드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17. 컨텐츠 제작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지금 스타일 추천받기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>재방문할 명문 부족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1) Customer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10. SWOT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 리뷰 작성률 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Segment 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1) 상황별 키워드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Frequency</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Segment 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인기 출근룩 확인하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2회 -&gt;Mid</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4) 구매의사결정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) 감정 키워드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Monetary</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">&gt; 광고메세지 x </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">-&gt; 충성도 X, </x:t>
+  </x:si>
+  <x:si>
+    <x:t>스토리 구조 컨텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1) PAS: </x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 브랜드 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- Solution:</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30일 이내 구매</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9. Persona</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 이름 : 김서연</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가장 높은 피로감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1회 -&gt; Low</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Recency </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Segment 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) Company</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Segment 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장바구니, 구매 고민</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 컨텐츠 전략 :</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">&gt; 재방문 세션수 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>신뢰할만한 정보 부족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>High (3점)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3) 가치 키워드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘의 코디 바로보기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>광고 상품 종류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범퍼광고(CPM)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오디오 도달 범위</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동영상 도달범위</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전환을 유도하세요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정보 중심 컨텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인지도, 트래픽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잠재고객, 판매</x:t>
+  </x:si>
+  <x:si>
+    <x:t>shorts광고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- Figma 인스타그램 광고컨텐츠, 유튜브 광고컨텐츠 -&gt; 광고카피(슬로건), 컬러가이드, 타이포그래피 -&gt; API -&gt; Notion 페이지 (Figma 컨텐츠)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 자사 경쟁력(상품, 플랫폼, 서비스, 기술 등) 기반 분석</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-트랜디함을 좋아하는 고객들로 추정, 우연하게 브랜드 노출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 공식 인스타계정, 유튜브계정, 공식 블로그 계정,사이트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; GA4 &gt; 데이터 스트림 코드를 통해서 삽압 vs 구글</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- UX/UI 전략(눈에 보이는 시각적인 서비스 개선. 효율성)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; cart conversion rate(장바구니 전환율)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SO전략: 강점을 활용한 시장의 기회요소를 포착하겠다는 전략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 테스트 진행 시, 변수는 1개 원칙 (실무적으로 최소화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>니즈: 출근 시 선택할 수 있는 출근룩 관련 스트레스 감소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>출근룩 고민을 줄이고 당신에게 어울리는 스타일을 추천합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>찜, 쿠폰, CRM, 리타게팅 마케팅을 통해서 재방문율 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 유료의 비용을 지불하고 사용자들의 트래픽을 획득하는 매체</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">- 지금 당장 고객들이 원하는 니즈 파악 + 장기적인 방향? </x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 직장인 코디네이션 및 큐레이팅 최대한 어필될 수 있는 컨텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사용자의 특정행위에 따른 광고 과금 방식(회원가입,다운로드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; 출혈경쟁 (단가경쟁) -&gt; 원가 절감 성공한 기업만 생존</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 단순히 광고소재를 여러개 만들어서 집행 -&gt; A/B x</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1) Product 전략 (판매요소 = 상품|서비스|플랫폼)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 합리적 소비를 위한 상품비교가 익숙한 25-34 직장인 여성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt;GA4,GTM 등의 트래픽 수집, 분석 툴 데이터 취합 비교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 선별된 키워드 활용 -&gt; 광고카피 문안 변환 (채널별)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12. WBS = Work Breakdown Structure</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-Product/ Price / Place / Promtion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필터 및 검색기능 강화, 상품정보 큐레이션 UI/UX 개선</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리뷰와 데이터를 기반으로 실패없는 데일리 패션을 경험하세요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사용자의 실질적인 참여(댓글등록, 이벤트 영상 )발생되었을</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리크스 관리(해야할 것, 하지말아야할 것, 우선시 해야할 것)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">앱 다운로드를 유도                                                    </x:t>
+  </x:si>
+  <x:si>
+    <x:t>(*CTR 데이터 수집,분석 : page_view 이벤트 / click_purchase_button 이벤트)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 소비성향 : 합리적이고 가성비있는 소비 지향/ 가격대비 활용도 중요/ 브랜드 이름보다는 스타일링 및 코디 관심</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카페 24 접속 &gt; 쇼핑몰 설정 &gt; 기본설정 &gt; 검색엔진 최적화(SEO) &gt; 코드 직접 입력 &gt; 코드 붙여넣기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 당연적 요소 컨텐츠: 소비자 입장에서 당연히 있어야 할것으로 기대하는 컨텐츠 
+(ex. 쇼핑몰 - 검색창 )</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-첫 구매 만족도 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메인배너, 추천상품 스캔</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mid of fUnnel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-Key Results</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18. Wire Frame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-할인 시즌만 겨냥해서 구매</x:t>
+  </x:si>
+  <x:si>
+    <x:t>160명: RFM H/H/H</x:t>
+  </x:si>
+  <x:si>
+    <x:t>promotion 전략실행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>90일 이상 -&gt; Low</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Funnel 구조 설계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>차선고객 = 성장가능 고객</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">280명 : M/L/L </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">- 장바구니에 담는 전환률 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>30일 이내-&gt; High</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1순위: Revenue</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">product 전략 실행 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>개선 (solution)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5) 이탈 또는 재방문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt;KPI(핵심성과지표)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2) 탐색 -&gt; 비교 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>- KeyResults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4) Form활용 리서치</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1) 유입 -&gt;  첫인상 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>8만원 이하 -&gt;Lovw</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 브랜드 충성도 매우 낮음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. FUNNEL 구조 설계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18만원 이상 -&gt;High</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 니치 마케팅 = 틈새시장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>=&gt; 과소비 X, 합리적o</x:t>
+  </x:si>
+  <x:si>
+    <x:t>320명 : H/M/M</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블로그(정보전달 컨텐츠)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마케팅 전략 기획안 발표</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- Pain Point:</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-패션 관심도 매우 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 월소득 :350만원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상품 상세페이지 기획안 정리</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">290명: L/L/L </x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 공유하기 버튼 클릭횟수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 구매자: 1,050명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내 취향에 맞는 사이트인가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3) Competitor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>채널/매체별 메세지 전략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8~18만원 -&gt; Mid</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 1회 구매후 재방문 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 평균 객단가 22만원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) 장기적인 비전  제시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사용자 맞춤 기준 불명확</x:t>
+  </x:si>
+  <x:si>
+    <x:t>* 재방문 유입 확률 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5. Journey map</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2순위: Retention</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3) Positioning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1) 브랜드 및 상품 정체성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>* 상품 리뷰 의존도 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비교하기 쉽게 보고싶어!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월평균 클릭률 1% 마지노선</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 회원가입:3,200명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>shorts광고 (CPM)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Revenue(매출향상)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정보 구조 미비, 정보 부족</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3회이상 -&gt; High</x:t>
+  </x:si>
+  <x:si>
+    <x:t>*구글 애즈 유튜브 광고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초개인화 맞춤 매체전략</x:t>
+  </x:si>
+  <x:si>
+    <x:t>W- Weakness(약점)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3) 상세검토 -&gt; 확신형성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 리뷰/평점 확인 필수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T-Threat (위협)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>광고 캠페인 채널 세팅</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 구매전환율 2.5% 달성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; 생존과 가장 밀접</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상품 특장점 인사이트 도출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt;앱푸쉬알람 클릭률5% 이상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. Earned Media</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나에게 맞는 룩 확인하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Retention(재방문)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타겟 유저 = 페르소나 결정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 메타 비즈니스 관리자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>앱설치 시 광고과금 방식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1회 클릭당 광고 과금방식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가설기반 덴드시 테스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) Targeting</x:t>
+  </x:si>
+  <x:si>
+    <x:t>60일 이내 -&gt; mid</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15. 컨텐츠 기획.제작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>데스크탑 UI/UX기획</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Top Of Funnel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 충성도가 매우 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>첫 직장에 입사한지 3개월</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인피드 광고 (CPC)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>*서브카피(설득 강화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>=-가설기반 반드시 테스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>앱 다운로드 유도를 위함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키워드 -&gt; 카피 문구 전환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안내없이 캠페인 만들기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>광고 캠페인 매체 선정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"AI 스타일 추천받기"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 일상에서의 출근 상황</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">&gt; 이미지, 카피CTA-&gt; </x:t>
+  </x:si>
+  <x:si>
+    <x:t>4) CTA 문구 테스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3) 리뷰 강조 A/B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"지금 스타일 확인하기"</x:t>
+  </x:si>
+  <x:si>
     <x:t>Youtube 구독 및 참여</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">&gt; 이미지, 카피CTA-&gt; </x:t>
-  </x:si>
-  <x:si>
-    <x:t>*서브카피(설득 강화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안내없이 캠페인 만들기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>앱 다운로드 유도를 위함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>광고 캠페인 매체 선정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>첫 직장에 입사한지 3개월</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인피드 광고 (CPC)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키워드 -&gt; 카피 문구 전환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 네이버 데이터랩(이커머스 쇼핑업종 &gt; 연,상하반기 .분기.월 단위 -&gt; 어ᄄᅠᆫ 업종의 어떤 키우ㅝ드가 이슈) : 트랜드 추이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8) 게슈탈트 심리학 :  유사성의 법칙 -&gt;  비슷한 속성값을 가지고 있는 요소들을 비슷한 컬러, 도형으로 만들수록 기억에 오래남음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 단순히 저렴한 금액으로 상품 판매,해당 서비스가 이 가격대에 충분히 합리적이고, 만족스럽다는 느낌을 가질 수 있도로 설계하는 과정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- Objective (미시적 목표) : 사용자가 자발적으로 Earned Media에 가서 상품 및 서비스를 공유, 광고 비율 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 동질집단 분석 보고서(cohort=동질집단). 1월 2주차 프로모션 행사를 통해서 유입된 사용자들의 7일내 재방문율 25% 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지금 스타일 추천받기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16. 무드보드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17. 컨텐츠 제작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EX)한경희 생활과학</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EX) 아모레퍼시픽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카카오 (메신저)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4) 행동 키워드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3회 이상 구매</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스토리 구조 컨텐츠</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2) 감정 키워드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인기 출근룩 확인하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">-&gt; 충성도 X, </x:t>
-  </x:si>
-  <x:si>
-    <x:t>Segment 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Monetary</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4) 구매의사결정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1) 상황별 키워드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Frequency</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1) Customer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2회 -&gt;Mid</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10. SWOT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Segment 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 리뷰 작성률 높음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>재방문할 명문 부족</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">&gt; 광고메세지 x </x:t>
-  </x:si>
-  <x:si>
-    <x:t>신뢰할만한 정보 부족</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Segment 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">&gt; 재방문 세션수 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>장바구니, 구매 고민</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1) PAS: </x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 브랜드 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 컨텐츠 전략 :</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2) Company</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9. Persona</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가장 높은 피로감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Segment 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Recency </x:t>
-  </x:si>
-  <x:si>
-    <x:t>- Solution:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30일 이내 구매</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 이름 : 김서연</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1회 -&gt; Low</x:t>
-  </x:si>
-  <x:si>
-    <x:t>High (3점)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>동영상 도달범위</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정보 중심 컨텐츠</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오늘의 코디 바로보기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전환을 유도하세요</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오디오 도달 범위</x:t>
-  </x:si>
-  <x:si>
-    <x:t>광고 상품 종류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>shorts광고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인지도, 트래픽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범퍼광고(CPM)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잠재고객, 판매</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3) 가치 키워드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ex)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> </x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판매</x:t>
-  </x:si>
-  <x:si>
-    <x:t>참여</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CPE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CPS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>트래픽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CPC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인지도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>앱홍보</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>앱</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쇼핑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호기심</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쇠퇴기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>백종원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성숙기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>단계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>`</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산출물</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>동영상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2회</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">- </x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>담당자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1회</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성장기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역할</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도입기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>검색</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>개인화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인피드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CPA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CPM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>리드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김승리</x:t>
+    <x:r>
+      <x:t>&gt;</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+        <x:b val="1"/>
+      </x:rPr>
+      <x:t>가격민감+ 가치추구 혼합형</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>동영상을 조회한 후 실제 상품 및 브랜드에 관심을 가질 법한 사용자들에게 광고집행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실제 동영상광고를 본 후 구매까지 도달할 확률이 높은 소비자를 대상으로 광고 집행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 다양한 플랫폼 대비, 직장인 출근룩을 디테일하게 큐레이션하는 플랫폼, 서비스 부재</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A/B 테스트 -&gt; 단기간 내 상대적으로 더많은 호감을 받는 컨텐츠 문구를 채택</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- MD와 협업하여 업종, 상품 가장 많이 판매되는 퍼널 사전 가설,검증, 전략 설계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 잠재고객 : 일반 유입 고객대비, 상품 및 서비스 결제확률이 매우 높은 고객</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">동영상을 통해 나의 상품, 브랜드를 광고,홍보해서 해당 요소의 존재감을 인지시킨다. </x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 어떠한 서비스, 상품, 플랫폼 출시, 리뉴얼 -&gt; 시장 소비자들에게 선보이겠다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 신규 스타트업 비즈니스 모델 적용X// 이미 비즈니스가 운영되고 있는 경우에 한함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>건너뛸 수 있거나 없는 인스트림 광고 혹은 범퍼 광고들을 조합해서 스토리텔링 전개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유튜브 내 인스트림 광고 외 외부 제휴채널 내 건너뛰기 기능 없이 출력가능한 광고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>데이터 세트 &gt; 설정 &gt; 이벤트 설정 &gt; 이벤트 설정도구 열기 &gt; 카페24 링크 넣기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문제 2: 유입은 발생, 구매전환률이 낮음/ 우리 홈페이지(브랜드) 신뢰도 낮음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>짧은 동영상을 통해 생각지 못한 나의 결핍과 수요를 문득 창출시켜주고자 하는 목적</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t xml:space="preserve">- </x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+        <x:b val="1"/>
+      </x:rPr>
+      <x:t>명확한 고객행동지표를 기반으로 선정하기 위한 중간절차</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>-</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="맑은 고딕"/>
+        <x:sz val="11"/>
+        <x:color rgb="ff000000"/>
+        <x:b val="1"/>
+      </x:rPr>
+      <x:t xml:space="preserve"> 충성도가 높은 전략 -&gt; 1인당 고객 LTV높게 </x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">매일 옷태문에 스트레스를 받던 그녀느 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Referral (주변추천, 바이럴 단계)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 리뷰작성빈도 및 작성률 (SQL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 모든 비지니스 업무 마감기한 존재</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브랜드가 제공하고자 하는 혜택 관련 컨텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- Low End: 저가전략(가성비)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>youtube 도달범위, 조회수,참여도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보류 후 종료 또는 재방문 구매 의사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 위 전략을 통해 기대하는 KPI 지표:</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 장바구지-&gt; 구매 전활율 전호나 35%</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -1905,70 +2204,79 @@
     </x:r>
   </x:si>
   <x:si>
+    <x:t>- 전략적으로 타겟(과녁) 고객을 선정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. NSM 정의: 거시적 목표 =큰목표</x:t>
+  </x:si>
+  <x:si>
+    <x:t>* 출근시 착용가능한 출근룩 고민많음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 두번째 재구매로 이어지는 비중이 약함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상세페이지, 리뷰, 포토 혹은 동영상 조회</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 후기 작성률, 기존 대비 10% 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 출근준비시간이 10분 줄었습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Activation(사용자 경험 및 실행)</x:t>
+  </x:si>
+  <x:si>
     <x:t>&gt; 국내 소비자 트랜드 &amp; 대중심리 민감</x:t>
   </x:si>
   <x:si>
-    <x:t>&gt; 후기 작성률, 기존 대비 10% 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">매일 옷태문에 스트레스를 받던 그녀느 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>Referral (주변추천, 바이럴 단계)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- Low End: 저가전략(가성비)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상세페이지, 리뷰, 포토 혹은 동영상 조회</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 모든 비지니스 업무 마감기한 존재</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 리뷰작성빈도 및 작성률 (SQL)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 출근준비시간이 10분 줄었습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 전략적으로 타겟(과녁) 고객을 선정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2. NSM 정의: 거시적 목표 =큰목표</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브랜드가 제공하고자 하는 혜택 관련 컨텐츠</x:t>
-  </x:si>
-  <x:si>
-    <x:t>youtube 도달범위, 조회수,참여도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>* 출근시 착용가능한 출근룩 고민많음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보류 후 종료 또는 재방문 구매 의사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 두번째 재구매로 이어지는 비중이 약함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Activation(사용자 경험 및 실행)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 위 전략을 통해 기대하는 KPI 지표:</x:t>
-  </x:si>
-  <x:si>
     <x:t>빠르게 선택하는 직장인 데일리룩 플랫폼</x:t>
   </x:si>
   <x:si>
+    <x:t>건너뛸 수 있는 인스트림 광고(CPV)</x:t>
+  </x:si>
+  <x:si>
     <x:t>&gt; 시간은 없고 스타일은 포기하기 싫다면</x:t>
   </x:si>
   <x:si>
-    <x:t>&gt; 장바구지-&gt; 구매 전활율 전호나 35%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>건너뛸 수 있는 인스트림 광고(CPV)</x:t>
+    <x:t>건너뛸 수 있는 인스트림 광고 (CPV)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고민없는 스타일 선택, 리뷰로 증명된 쇼핑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 맘카페, 디시인사이드, 웃긴대학 등</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유튜브 내 오디오 팟캐스트 관련 광고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제는 스타일 고민없이 하루를 시작하세요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>편안한, 세련된, 단정한, 고민끝, 자신감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026.03.30~2026.04.15</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">오늘도 옷 때문에 늦을까봐 걱정했다면 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>실제 상품이 1건 판매되었을 대 발생</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owned Media( 지속적 재방문)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026.03.30~2026.04.08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예쁘다? -&gt; 감성적 설득, 마케팅 설득</x:t>
+  </x:si>
+  <x:si>
+    <x:t>건너뛸 수 없는 인스트림광고(CPM)</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -1990,158 +2298,34 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>예쁘다? -&gt; 감성적 설득, 마케팅 설득</x:t>
+    <x:t>출근 준비를 가볍게 만드는 스타일 쇼핑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 컨텐츠 만족에 따른 구매전환율 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>핵심 타겟 상품 특장점 도출(TPO타겐)</x:t>
   </x:si>
   <x:si>
     <x:t>&gt; 중국산 값싼 브랜드,플랫폼의 국내 진출</x:t>
   </x:si>
   <x:si>
-    <x:t>실제 상품이 1건 판매되었을 대 발생</x:t>
-  </x:si>
-  <x:si>
-    <x:t>편안한, 세련된, 단정한, 고민끝, 자신감</x:t>
+    <x:t xml:space="preserve">브랜드가 전달하고자하는 깊이있는 메세지 </x:t>
   </x:si>
   <x:si>
     <x:t>&gt; 가성비 : 원가 절감 // 대량생산</x:t>
   </x:si>
   <x:si>
-    <x:t>2026.03.30~2026.04.08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026.03.30~2026.04.15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owned Media( 지속적 재방문)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>출근 준비를 가볍게 만드는 스타일 쇼핑</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">브랜드가 전달하고자하는 깊이있는 메세지 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>건너뛸 수 없는 인스트림광고(CPM)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 컨텐츠 만족에 따른 구매전환율 높음</x:t>
-  </x:si>
-  <x:si>
     <x:t>&gt; 메세지: 고급화된 메세지의 일관된 소통</x:t>
   </x:si>
   <x:si>
-    <x:t>고민없는 스타일 선택, 리뷰로 증명된 쇼핑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 맘카페, 디시인사이드, 웃긴대학 등</x:t>
-  </x:si>
-  <x:si>
-    <x:t>건너뛸 수 있는 인스트림 광고 (CPV)</x:t>
+    <x:t>Owned Media( 지속적 관계 관리)</x:t>
   </x:si>
   <x:si>
     <x:t>문제 해결 관련 키워드 중심의 컨텐츠</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">오늘도 옷 때문에 늦을까봐 걱정했다면 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제는 스타일 고민없이 하루를 시작하세요</x:t>
-  </x:si>
-  <x:si>
-    <x:t>핵심 타겟 상품 특장점 도출(TPO타겐)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owned Media( 지속적 관계 관리)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유튜브 내 오디오 팟캐스트 관련 광고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B 문제해결형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A 감성형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>product = 실물 상품만 의미 X (플랫폼, 서비스, 교육, 컨텐츠 등)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 유튜브 동영상 컨텐츠 노출 &gt; 브랜드/상품의 존재 먼저 인지한 경우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실제 광고를 보고 우리의 사이트(랜딩 페이지)에 최대한 많이 유입시키고자 할때</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-&gt; STP전략의 Positioning에서 도출된 방향성과 정체성 반드시 일치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2) Field Research: 해당 업종 관계자, 전문가 섭외, 인터뷰</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 직장인 데일리룩 구매, 큐레이션 효과적으로 추천 -&gt; 고객 만족도 경험</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 1개의 의류상춤 +화장품+악세사리까지 토탈 코디네이션 &amp; 출근룩 큐레이션</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 상세페이지 및 컨텐츠 내 기존 소비자 리뷰만족도를 어필할 수 있는 컨텐츠</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 힉의 법칙 =&gt; 사람은 너무 많은 성택지를 주먼 오히려 선택을 힘들어한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 인구통계학적 질문/ 업계 및 브랜드 관심도/ 구매행동기반 / 컨텐츠 소비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30일 이내 구매한 한달에 3회 이상 구매한, 총 18만원 이상을 지불한 금액</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoAS: Return On Ads Spend: 마케팅 비용대비 ,매출액</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-구매하기 전까지 많은 정보 수집, 비교 -&gt; 구매가지 걸리는 시간 많음</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">-High Fidelity WireFrame: 고품질 와이어 프레임 -&gt; </x:t>
-  </x:si>
-  <x:si>
-    <x:t>=&gt; 예쁘기 때문에, 더 비싸도 살거야! =&gt; 가격의 합리적이게 다가오것</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2) Price 전략 (해당 브랜드, 상품은 어떤 가격대에 포지셔닝 인식)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유튜브 내 쇼츠 카테고리 노출되는 광고. 60ch 이하. 세로 형태 타입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3) Place 전략(어디에서 어ᄄᅠᇂ게 소비자의 경험을 제공할 것인가)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 경쟁업체의 현 판매가를 가장 높은 비중으로 반영하여 Price전략 구축</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-&gt; 주간 구매 사용자수(Weekly Purchasing Users) 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 이전에 온라인으로 출근룩 구매 -&gt; 생각보다 저품질, 소재,주변반응 별로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>출근룩 고민때문에 아침시간이 부족했다면 
-지금바로 스타일 추천 받아보세요</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">- 위에서 발견한 고객 성향에 따른 자사 경쟁력 &amp; 개선할 부분까지 나열 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt;GTM활용 10,25,50,75,90  세부적인 스크롤 깊이 단위까지 확인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 스크롤 깊이(Scroll Depth) 50% 이상 도달률 40% 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>리뉴얼 전략 &gt; 기존브랜드 리뉴얼 vs 자매 브랜드런칭(-&gt;엄브렐러 전략)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1) 메세지 유형 (키워드 분류) 다르게 A/B</x:t>
+    <x:t>&gt; 출근 준비 시간을 줄이는 스타일 추천!</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -2178,121 +2362,139 @@
     </x:r>
   </x:si>
   <x:si>
+    <x:t>-상품 구매후 만족시, 재구매 가능성이 매우 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; Google Form / Naver Form</x:t>
+  </x:si>
+  <x:si>
+    <x:t>현실적인 주제, 실현가능한 프로젝트인지 파악</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Objective: 실질적 상품 구매전환률 향상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-리뷰가 존재x, 할인 비시즌 거의 활동 전무</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">- 핀터레스트, 인스타그램, 구글링, 해외사이트 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>⇒ 방문을통해서 구매전환까지 매력도(설들력) 약함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ST전략: 강점을 활용한 시장의 위협요소 방어전략</x:t>
+  </x:si>
+  <x:si>
     <x:t>&gt; 단순 상품을 판매하는 것이 아닌 경험을 판매</x:t>
   </x:si>
   <x:si>
-    <x:t>-비즈니스 포트폴리오 최대 2개까지 생성 가능</x:t>
+    <x:t>&gt; 평균 주문 구매금액 7만원 유지(평균객단가)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 가격보다 상품,브랜드 ,플랫폼 이미지 중요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-가격대비 만족도 높아야하는 고객 = 가성비 추구</x:t>
   </x:si>
   <x:si>
     <x:t>다시는 마주하고 싶지 않다.
 꼭 다시 오고 싶다.</x:t>
   </x:si>
   <x:si>
+    <x:t>- 목적에 따른 특정 아이템 빠르게 검색 후 구매</x:t>
+  </x:si>
+  <x:si>
     <x:t>처음 구매를 하려고 하는데, 실패하지 않을까?</x:t>
   </x:si>
   <x:si>
-    <x:t>⇒ 방문을통해서 구매전환까지 매력도(설들력) 약함</x:t>
+    <x:t>&gt; 상품 공유하기 버튼 클릭율 3% 이상 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 4계절 존재 -&gt; 시즌 트랜드가 빠르게 흘러감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 우리 홈페이지의 인기상품군들의 구매비중 50%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; Returning User = Visiors</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; New Product Development</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-비즈니스 포트폴리오 최대 2개까지 생성 가능</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; User id &gt; Avg order value</x:t>
   </x:si>
   <x:si>
     <x:t>- SNS 광고 통해서 유입한 고객 (대부분)</x:t>
   </x:si>
   <x:si>
-    <x:t>&gt; 우리 홈페이지의 인기상품군들의 구매비중 50%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-상품 구매후 만족시, 재구매 가능성이 매우 높음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 목적에 따른 특정 아이템 빠르게 검색 후 구매</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 평균 주문 구매금액 7만원 유지(평균객단가)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; Google Form / Naver Form</x:t>
-  </x:si>
-  <x:si>
-    <x:t>현실적인 주제, 실현가능한 프로젝트인지 파악</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 상품 공유하기 버튼 클릭율 3% 이상 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Objective: 실질적 상품 구매전환률 향상</x:t>
-  </x:si>
-  <x:si>
     <x:t>* 가성비(가격 민감성) &amp; 품질 어느정도 유지</x:t>
   </x:si>
   <x:si>
-    <x:t>-리뷰가 존재x, 할인 비시즌 거의 활동 전무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 4계절 존재 -&gt; 시즌 트랜드가 빠르게 흘러감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; Returning User = Visiors</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">- 핀터레스트, 인스타그램, 구글링, 해외사이트 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; New Product Development</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 가격보다 상품,브랜드 ,플랫폼 이미지 중요</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ST전략: 강점을 활용한 시장의 위협요소 방어전략</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-가격대비 만족도 높아야하는 고객 = 가성비 추구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; User id &gt; Avg order value</x:t>
+    <x:t>1) 메세지 유형 (키워드 분류) 다르게 A/B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 브랜드 및 기업이 직접 소유, 관리하는 매체</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. GTM을 통해서 사용자 방문 트래픽 수집</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-전혀 관리가 불가능한 제3의 커뮤니티 영역</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 상품 조회하는데 소요하는 시간 = 체류시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>랜딩페이지 유입.접속 증대를 위한 광고 캠페인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Paid Media (최초 신규 고객 유입)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. GTM운 해당 수집 데이터를 GA4에 전달</x:t>
+  </x:si>
+  <x:si>
+    <x:t>모든 것을 내가 직접 맞춤으로 광고캠페인 세팅</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">- 앞 단계에서 도출된 사용자 정보를 기반으로 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>소비자들에게 최대한 많이 광고를 노출하고자 할때</x:t>
+  </x:si>
+  <x:si>
+    <x:t>건너뛸 수 없는 30초 인스트림 광고 (CPM)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-&gt; 직관적: 매출 영업이익 결과 바로 도출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자체적인 유튜브 채널 &gt; 구독자수 증가를 위함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. Owned media =&gt; 브랜드 인지도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-단순히 광고소재를 여러개 만들어서 지밴한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ex) 왼쪽 상단:로고/ 우측상단: 로그인 버튼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>*브랜드 헤드라인 사전 정의(브랜드 정체성 강조)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 유입경로 채널: 인스타그램, 틱톡, 유트브</x:t>
   </x:si>
   <x:si>
     <x:t>-&gt; 감성설득 -&gt; 죽어도 이 브랜드 상품 선텍</x:t>
   </x:si>
   <x:si>
-    <x:t>자체적인 유튜브 채널 &gt; 구독자수 증가를 위함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 유입경로 채널: 인스타그램, 틱톡, 유트브</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 상품 조회하는데 소요하는 시간 = 체류시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2. Owned media =&gt; 브랜드 인지도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-단순히 광고소재를 여러개 만들어서 지밴한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. GTM을 통해서 사용자 방문 트래픽 수집</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2. GTM운 해당 수집 데이터를 GA4에 전달</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ex) 왼쪽 상단:로고/ 우측상단: 로그인 버튼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>*브랜드 헤드라인 사전 정의(브랜드 정체성 강조)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>- 브랜드 및 기업이 직접 소유, 관리하는 매체</x:t>
-  </x:si>
-  <x:si>
-    <x:t>모든 것을 내가 직접 맞춤으로 광고캠페인 세팅</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-전혀 관리가 불가능한 제3의 커뮤니티 영역</x:t>
-  </x:si>
-  <x:si>
-    <x:t>랜딩페이지 유입.접속 증대를 위한 광고 캠페인</x:t>
-  </x:si>
-  <x:si>
     <x:t>2) 자체적인 유튜브 공식 채널 계정 운영관리</x:t>
   </x:si>
   <x:si>
@@ -2303,21 +2505,6 @@
   </x:si>
   <x:si>
     <x:t>구글 외 구글 제휴 사이트 내 광고 캠페인 집행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Paid Media (최초 신규 고객 유입)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">- 앞 단계에서 도출된 사용자 정보를 기반으로 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>-&gt; 직관적: 매출 영업이익 결과 바로 도출</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소비자들에게 최대한 많이 광고를 노출하고자 할때</x:t>
-  </x:si>
-  <x:si>
-    <x:t>건너뛸 수 없는 30초 인스트림 광고 (CPM)</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -2348,54 +2535,112 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:r>
-      <x:t>&gt;</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="맑은 고딕"/>
-        <x:sz val="11"/>
-        <x:color rgb="ff000000"/>
-        <x:b val="1"/>
-      </x:rPr>
-      <x:t>가격민감+ 가치추구 혼합형</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 출근 준비 시간을 줄이는 스타일 추천!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A/B</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B</x:t>
-  </x:si>
-  <x:si>
-    <x:t>=-CTA=Call To Action=사용자로 하여금 무언가의 액션을 불러일으키게 하는 요소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"지금 스타일 확인하기"</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3) 리뷰 강조 A/B</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4) CTA 문구 테스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"AI 스타일 추천받기"</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt; 일상에서의 출근 상황</x:t>
-  </x:si>
-  <x:si>
-    <x:t>=-가설기반 반드시 테스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A 일상에서의 라이프스타일 연상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2) 이미지 스타일 다르게 A/B</x:t>
+    <x:t>&gt; 지상파 광고 (표준 광고 소재 시간 규격)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 팀프로젝트 : 광고 캠페인 전략 &gt; 영상컨텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 실무부서 전략에 입각해서 전체예산 세부조율</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-장점: 돈을 사용하기 대문에 빠른 노출 사능, 성과 분석 / 단점: 돈없으면 노출 자체가 금지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2) 선형편집 (리니어 편집) : 선이 연결되어 있는 장비를 가지고 편집 -&gt; 편집데크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 아름다운 모델, 상쾌한 모습으로 행복하게 출근하는 모습</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리미어 : 컷편집 프로그램 (효과, 자막, 트랜지션, 오디오)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15초, 30초 -&gt; 20초</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11~15초 : CTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>*광고소재 = 영상소재</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 메모리카드 데이터 저장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 지금 바로 선택하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3~7초 : 문제 -&gt; 해결</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유튜브 광고소재 사이즈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. 핵심주제 인사이트 도출 :SUmmary</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6. 사용자 행동 유도 cta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Notion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 회사(인하우스)에서 직접 SEO를 제작하는 곳은 가급적 안가길</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 외부 바이럴 업체 컨트롤을 통해 SEO를 관리하는 곳으로 취업하길</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. SEM: Search Engine Marketing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 유료결제를 통해서 광고상품을 활용 -&gt; 상위 노출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4. 해결책 SOULTIO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>=&gt; 누군가가 검색을 하며 뜨는 페이지에 나의 광고 기재</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. SERP: Search Engine Result Page</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4. AEO : Answer Engine Optimization</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.GEO: Generative Engine Optimization</x:t>
+  </x:si>
+  <x:si>
+    <x:t>컨텐츠 제목: SEO +CTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AI 모델이 어떤 데이터,어떻게 생긴 컨텐츠롸 다입안?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 문제제기형 질의 응답 형식(검색 최적화용 답변)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt; 근거자료, 수치, 데이터, 차트, 그래프들 함 3-5개정도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- 팀프로젝트 : 커뮤니케이션 공간 (Slack) -&gt; 작업물 저장 x</x:t>
+  </x:si>
+  <x:si>
+    <x:t>- Notion 내 컨텐츠 업데이트, 변경 발생 -&gt; Slack</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1) 광고 수익률이 네이버 블로그보다 좋음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-외부 관계자와의 공유&amp;협업 효율 플랫폼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-업무 프로세스 관리,체크리스트 관리 용이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-컨텐츠 운영.관리 효율적(페이지,블록,데이터베이스)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2724,7 +2969,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="44">
+  <x:cellXfs count="46">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -2915,6 +3160,15 @@
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" hs:applyExtension="1">
@@ -2928,13 +3182,10 @@
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -3344,7 +3595,7 @@
 </x:styleSheet>
 </file>
 
-<file path=xl/drawings/drawing0.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3376,6 +3627,49 @@
         <a:xfrm>
           <a:off x="2743200" y="5867400"/>
           <a:ext cx="2638425" cy="1990725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="1" fPrintsWithSheet="1"/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>123824</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic macro="" fPublished="0">
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="695325" y="9020175"/>
+          <a:ext cx="5963482" cy="3048425"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3649,32 +3943,32 @@
   <x:sheetData>
     <x:row r="8" spans="3:3">
       <x:c r="C8" t="s">
-        <x:v>139</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="3:3">
       <x:c r="C9" t="s">
-        <x:v>249</x:v>
+        <x:v>387</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:3">
       <x:c r="C11" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="3:3">
       <x:c r="C12" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>628</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="3:3">
       <x:c r="C13" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>266</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="3:3">
       <x:c r="C14" s="3" t="s">
-        <x:v>641</x:v>
+        <x:v>686</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3691,27 +3985,27 @@
   <x:sheetData>
     <x:row r="6" spans="3:3" ht="22.05000000000000071054">
       <x:c r="C6" s="27" t="s">
-        <x:v>475</x:v>
+        <x:v>440</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="3:3">
       <x:c r="C7" t="s">
-        <x:v>168</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="3:3">
       <x:c r="C9" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:3">
       <x:c r="C10" t="s">
-        <x:v>45</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:3">
       <x:c r="C11" t="s">
-        <x:v>354</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="15:17">
@@ -3721,7 +4015,7 @@
     </x:row>
     <x:row r="13" spans="3:17">
       <x:c r="C13" s="15" t="s">
-        <x:v>418</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="O13" s="18"/>
       <x:c r="P13" s="18"/>
@@ -3729,7 +4023,7 @@
     </x:row>
     <x:row r="14" spans="3:17">
       <x:c r="C14" t="s">
-        <x:v>282</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="O14" s="18"/>
       <x:c r="P14" s="18"/>
@@ -3737,7 +4031,7 @@
     </x:row>
     <x:row r="15" spans="3:17">
       <x:c r="C15" t="s">
-        <x:v>31</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="O15" s="18"/>
       <x:c r="P15" s="18"/>
@@ -3745,7 +4039,7 @@
     </x:row>
     <x:row r="16" spans="3:17">
       <x:c r="C16" t="s">
-        <x:v>589</x:v>
+        <x:v>674</x:v>
       </x:c>
       <x:c r="O16" s="18"/>
       <x:c r="P16" s="18"/>
@@ -3758,7 +4052,7 @@
     </x:row>
     <x:row r="18" spans="3:17">
       <x:c r="C18" s="15" t="s">
-        <x:v>37</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="O18" s="18"/>
       <x:c r="P18" s="18"/>
@@ -3766,7 +4060,7 @@
     </x:row>
     <x:row r="19" spans="3:17">
       <x:c r="C19" t="s">
-        <x:v>43</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="O19" s="18"/>
       <x:c r="P19" s="18"/>
@@ -3774,7 +4068,7 @@
     </x:row>
     <x:row r="20" spans="3:17">
       <x:c r="C20" t="s">
-        <x:v>152</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="O20" s="18"/>
       <x:c r="P20" s="18"/>
@@ -3787,69 +4081,69 @@
     </x:row>
     <x:row r="22" spans="3:3">
       <x:c r="C22" s="15" t="s">
-        <x:v>400</x:v>
+        <x:v>580</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="3:3">
       <x:c r="C23" t="s">
-        <x:v>586</x:v>
+        <x:v>672</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="3:3">
       <x:c r="C24" t="s">
-        <x:v>242</x:v>
+        <x:v>377</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="3:3">
       <x:c r="C25" t="s">
-        <x:v>562</x:v>
+        <x:v>651</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="3:3">
       <x:c r="C26" t="s">
-        <x:v>653</x:v>
+        <x:v>696</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="3:3">
       <x:c r="C27" t="s">
-        <x:v>441</x:v>
+        <x:v>430</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="3:3">
       <x:c r="C30" t="s">
-        <x:v>59</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="3:12">
       <x:c r="C31" t="s">
-        <x:v>331</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="L31" s="20" t="s">
-        <x:v>35</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="3:12">
       <x:c r="C32" t="s">
-        <x:v>658</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="L32" s="20" t="s">
-        <x:v>440</x:v>
+        <x:v>426</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="3:12">
       <x:c r="C33" t="s">
-        <x:v>363</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="L33" s="20" t="s">
-        <x:v>60</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="3:12">
       <x:c r="C34" t="s">
-        <x:v>149</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L34" s="20" t="s">
-        <x:v>405</x:v>
+        <x:v>583</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3866,37 +4160,37 @@
   <x:sheetData>
     <x:row r="3" spans="3:3" ht="22.05000000000000071054">
       <x:c r="C3" s="27" t="s">
-        <x:v>106</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="3:3">
       <x:c r="C4" t="s">
-        <x:v>656</x:v>
+        <x:v>699</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="3:3">
       <x:c r="C5" t="s">
-        <x:v>609</x:v>
+        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="3:3">
       <x:c r="C7" t="s">
-        <x:v>386</x:v>
+        <x:v>566</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="3:3">
       <x:c r="C8" s="20" t="s">
-        <x:v>612</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:3">
       <x:c r="C10" t="s">
-        <x:v>390</x:v>
+        <x:v>560</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:3">
       <x:c r="C11" s="20" t="s">
-        <x:v>194</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3920,128 +4214,128 @@
   <x:sheetData>
     <x:row r="4" spans="3:3">
       <x:c r="C4" t="s">
-        <x:v>335</x:v>
+        <x:v>504</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="3:3">
       <x:c r="C5" s="20" t="s">
-        <x:v>429</x:v>
+        <x:v>427</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="3:3">
       <x:c r="C6" s="20" t="s">
-        <x:v>183</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="3:3">
       <x:c r="C7" s="20" t="s">
-        <x:v>568</x:v>
+        <x:v>635</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="3:3">
       <x:c r="C8" s="20" t="s">
-        <x:v>162</x:v>
+        <x:v>623</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="3:3">
       <x:c r="C12" s="18" t="s">
-        <x:v>425</x:v>
+        <x:v>413</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="3:12">
       <x:c r="C14" s="28" t="s">
-        <x:v>104</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="D14" s="28" t="s">
-        <x:v>113</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E14" s="28" t="s">
-        <x:v>438</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="F14" s="28" t="s">
-        <x:v>533</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G14" s="28" t="s">
-        <x:v>545</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H14" s="28" t="s">
-        <x:v>554</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="I14" s="28"/>
       <x:c r="J14" s="29" t="s">
-        <x:v>542</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K14" s="29" t="s">
-        <x:v>95</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="L14" s="29" t="s">
-        <x:v>538</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="3:10">
       <x:c r="C15" s="18" t="s">
-        <x:v>315</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="D15" s="18" t="s">
-        <x:v>397</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="E15" s="18" t="s">
-        <x:v>604</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="F15" s="18" t="s">
-        <x:v>22</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G15" s="18" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="H15" s="18" t="s">
+        <x:v>665</x:v>
+      </x:c>
+      <x:c r="I15" s="18" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="J15" t="s">
         <x:v>116</x:v>
-      </x:c>
-      <x:c r="H15" s="18" t="s">
-        <x:v>590</x:v>
-      </x:c>
-      <x:c r="I15" s="18" t="s">
-        <x:v>534</x:v>
-      </x:c>
-      <x:c r="J15" t="s">
-        <x:v>560</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="3:9">
       <x:c r="C16" s="18"/>
       <x:c r="D16" s="18" t="s">
-        <x:v>55</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E16" s="18" t="s">
-        <x:v>604</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="F16" s="18"/>
       <x:c r="G16" s="18"/>
       <x:c r="H16" s="18" t="s">
-        <x:v>590</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="I16" s="18" t="s">
-        <x:v>534</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="3:9">
       <x:c r="C17" s="18"/>
       <x:c r="D17" s="18" t="s">
-        <x:v>383</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="E17" s="18"/>
       <x:c r="F17" s="18"/>
       <x:c r="G17" s="18"/>
       <x:c r="H17" s="18" t="s">
-        <x:v>591</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="I17" s="18" t="s">
-        <x:v>559</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="3:9">
       <x:c r="C18" s="18" t="s">
-        <x:v>433</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="D18" s="18" t="s">
-        <x:v>49</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="E18" s="18"/>
       <x:c r="F18" s="18"/>
@@ -4052,7 +4346,7 @@
     <x:row r="19" spans="3:9">
       <x:c r="C19" s="18"/>
       <x:c r="D19" s="18" t="s">
-        <x:v>136</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E19" s="18"/>
       <x:c r="F19" s="18"/>
@@ -4063,7 +4357,7 @@
     <x:row r="20" spans="3:9">
       <x:c r="C20" s="18"/>
       <x:c r="D20" s="18" t="s">
-        <x:v>426</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="E20" s="18"/>
       <x:c r="F20" s="18"/>
@@ -4073,10 +4367,10 @@
     </x:row>
     <x:row r="21" spans="3:9">
       <x:c r="C21" s="18" t="s">
-        <x:v>428</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="D21" s="18" t="s">
-        <x:v>424</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E21" s="18"/>
       <x:c r="F21" s="18"/>
@@ -4087,7 +4381,7 @@
     <x:row r="22" spans="3:9">
       <x:c r="C22" s="18"/>
       <x:c r="D22" s="18" t="s">
-        <x:v>417</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="E22" s="18"/>
       <x:c r="F22" s="18"/>
@@ -4098,7 +4392,7 @@
     <x:row r="23" spans="3:9">
       <x:c r="C23" s="18"/>
       <x:c r="D23" s="18" t="s">
-        <x:v>42</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="E23" s="18"/>
       <x:c r="F23" s="18"/>
@@ -4108,10 +4402,10 @@
     </x:row>
     <x:row r="24" spans="3:9">
       <x:c r="C24" s="18" t="s">
-        <x:v>287</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="D24" s="18" t="s">
-        <x:v>447</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="E24" s="18"/>
       <x:c r="F24" s="18"/>
@@ -4122,7 +4416,7 @@
     <x:row r="25" spans="3:9">
       <x:c r="C25" s="18"/>
       <x:c r="D25" s="18" t="s">
-        <x:v>20</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E25" s="18"/>
       <x:c r="F25" s="18"/>
@@ -4133,7 +4427,7 @@
     <x:row r="26" spans="3:9">
       <x:c r="C26" s="18"/>
       <x:c r="D26" s="18" t="s">
-        <x:v>406</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="E26" s="18"/>
       <x:c r="F26" s="18"/>
@@ -4144,7 +4438,7 @@
     <x:row r="27" spans="3:9">
       <x:c r="C27" s="18"/>
       <x:c r="D27" s="18" t="s">
-        <x:v>124</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="E27" s="18"/>
       <x:c r="F27" s="18"/>
@@ -4155,7 +4449,7 @@
     <x:row r="28" spans="3:9">
       <x:c r="C28" s="18"/>
       <x:c r="D28" s="18" t="s">
-        <x:v>427</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="E28" s="18"/>
       <x:c r="F28" s="18"/>
@@ -4165,33 +4459,33 @@
     </x:row>
     <x:row r="31" spans="3:9">
       <x:c r="C31" t="s">
-        <x:v>372</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="H31" t="s">
-        <x:v>435</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="I31" t="s">
-        <x:v>145</x:v>
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="3:3">
       <x:c r="C35" t="s">
-        <x:v>78</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="3:3">
       <x:c r="C36" t="s">
-        <x:v>648</x:v>
+        <x:v>682</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="3:3">
       <x:c r="C37" t="s">
-        <x:v>343</x:v>
+        <x:v>509</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="3:3">
       <x:c r="C38" t="s">
-        <x:v>137</x:v>
+        <x:v>242</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4208,142 +4502,142 @@
   <x:sheetData>
     <x:row r="4" spans="3:3">
       <x:c r="C4" t="s">
-        <x:v>130</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="3:3">
       <x:c r="C5" s="20" t="s">
-        <x:v>336</x:v>
+        <x:v>505</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="3:3">
       <x:c r="C7" t="s">
-        <x:v>165</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="3:3">
       <x:c r="C8" s="20" t="s">
-        <x:v>637</x:v>
+        <x:v>688</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="3:3">
       <x:c r="C9" s="20" t="s">
-        <x:v>114</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:3">
       <x:c r="C10" s="20" t="s">
-        <x:v>614</x:v>
+        <x:v>283</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:3">
       <x:c r="C11" s="20" t="s">
-        <x:v>339</x:v>
+        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="3:3">
       <x:c r="C12" s="20" t="s">
-        <x:v>207</x:v>
+        <x:v>343</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="4:4">
       <x:c r="D13" s="21" t="s">
-        <x:v>273</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="4:4">
       <x:c r="D14" s="20" t="s">
-        <x:v>579</x:v>
+        <x:v>640</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="5:5">
       <x:c r="E15" s="20" t="s">
-        <x:v>38</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="5:5">
       <x:c r="E16" s="20" t="s">
-        <x:v>301</x:v>
+        <x:v>527</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="5:5">
       <x:c r="E17" s="20" t="s">
-        <x:v>664</x:v>
+        <x:v>708</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="5:5">
       <x:c r="E18" s="20" t="s">
-        <x:v>382</x:v>
+        <x:v>558</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="3:3">
       <x:c r="C20" t="s">
-        <x:v>624</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="3:3">
       <x:c r="C21" s="20" t="s">
-        <x:v>453</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="3:3">
       <x:c r="C22" s="20" t="s">
-        <x:v>627</x:v>
+        <x:v>290</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="4:4">
       <x:c r="D23" s="20" t="s">
-        <x:v>340</x:v>
+        <x:v>498</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="4:4">
       <x:c r="D24" s="20" t="s">
-        <x:v>361</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="5:5">
       <x:c r="E25" s="20" t="s">
-        <x:v>623</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="5:5">
       <x:c r="E26" t="s">
-        <x:v>585</x:v>
+        <x:v>666</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="3:3">
       <x:c r="C27" s="20" t="s">
-        <x:v>350</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="3:3">
       <x:c r="C28" s="20" t="s">
-        <x:v>371</x:v>
+        <x:v>543</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="3:3">
       <x:c r="C29" s="20" t="s">
-        <x:v>61</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="3:3">
       <x:c r="C30" s="20" t="s">
-        <x:v>202</x:v>
+        <x:v>337</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="3:3">
       <x:c r="C31" s="20" t="s">
-        <x:v>661</x:v>
+        <x:v>723</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="3:3">
       <x:c r="C32" s="20" t="s">
-        <x:v>294</x:v>
+        <x:v>631</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="3:7">
       <x:c r="C33" s="21" t="s">
-        <x:v>566</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="D33" s="18"/>
       <x:c r="E33" s="18"/>
@@ -4352,10 +4646,10 @@
     </x:row>
     <x:row r="34" spans="3:7">
       <x:c r="C34" s="18" t="s">
-        <x:v>532</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D34" s="21" t="s">
-        <x:v>681</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="E34" s="18"/>
       <x:c r="F34" s="18"/>
@@ -4364,7 +4658,7 @@
     <x:row r="35" spans="3:7">
       <x:c r="C35" s="18"/>
       <x:c r="D35" s="21" t="s">
-        <x:v>467</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="E35" s="18"/>
       <x:c r="F35" s="18"/>
@@ -4372,37 +4666,37 @@
     </x:row>
     <x:row r="37" spans="3:3">
       <x:c r="C37" t="s">
-        <x:v>626</x:v>
+        <x:v>286</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="3:3">
       <x:c r="C38" s="20" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="3:3">
       <x:c r="C39" s="20" t="s">
-        <x:v>437</x:v>
+        <x:v>424</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="3:3">
       <x:c r="C40" t="s">
-        <x:v>210</x:v>
+        <x:v>344</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="3:3">
       <x:c r="C41" s="20" t="s">
-        <x:v>160</x:v>
+        <x:v>620</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="3:3">
       <x:c r="C42" s="20" t="s">
-        <x:v>663</x:v>
+        <x:v>722</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="3:3">
       <x:c r="C43" s="20" t="s">
-        <x:v>169</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="3:3">
@@ -4413,32 +4707,32 @@
     </x:row>
     <x:row r="47" spans="3:3">
       <x:c r="C47" t="s">
-        <x:v>362</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="3:3">
       <x:c r="C48" s="20" t="s">
-        <x:v>56</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="3:3">
       <x:c r="C49" s="20" t="s">
-        <x:v>597</x:v>
+        <x:v>675</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="3:3">
       <x:c r="C50" s="20" t="s">
-        <x:v>147</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="4:4">
       <x:c r="D51" s="20" t="s">
-        <x:v>166</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="4:4">
       <x:c r="D52" s="20" t="s">
-        <x:v>268</x:v>
+        <x:v>401</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4459,78 +4753,78 @@
   <x:sheetData>
     <x:row r="4" spans="3:3">
       <x:c r="C4" t="s">
-        <x:v>123</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="3:3">
       <x:c r="C5" s="20" t="s">
-        <x:v>40</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="3:3">
       <x:c r="C6" s="20" t="s">
-        <x:v>209</x:v>
+        <x:v>350</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="3:3">
       <x:c r="C7" s="20" t="s">
-        <x:v>184</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="3:3">
       <x:c r="C8" s="20" t="s">
-        <x:v>436</x:v>
+        <x:v>423</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="3:3">
       <x:c r="C9" s="20" t="s">
-        <x:v>439</x:v>
+        <x:v>425</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="3:3">
       <x:c r="C12" s="30" t="s">
-        <x:v>547</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="3:3">
       <x:c r="C13" s="30" t="s">
-        <x:v>544</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="3:3">
       <x:c r="C14" s="30" t="s">
-        <x:v>529</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="3:3">
       <x:c r="C15" s="30" t="s">
-        <x:v>527</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="3:3">
       <x:c r="C16" t="s">
-        <x:v>634</x:v>
+        <x:v>303</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="3:4">
       <x:c r="C17" t="s">
-        <x:v>133</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="D17" t="s">
-        <x:v>135</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="3:4">
       <x:c r="C18" t="s">
-        <x:v>460</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="D18" t="s">
-        <x:v>459</x:v>
+        <x:v>429</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="4:4">
       <x:c r="D19" t="s">
-        <x:v>528</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4554,430 +4848,430 @@
   <x:sheetData>
     <x:row r="4" spans="3:3" ht="22.05000000000000071054">
       <x:c r="C4" s="27" t="s">
-        <x:v>407</x:v>
+        <x:v>596</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="3:3">
       <x:c r="C5" t="s">
-        <x:v>167</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="3:3">
       <x:c r="C6" s="20" t="s">
-        <x:v>355</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="4:4">
       <x:c r="D7" s="18" t="s">
-        <x:v>203</x:v>
+        <x:v>338</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="4:4">
       <x:c r="D8" s="18" t="s">
-        <x:v>351</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="4:4">
       <x:c r="D9" s="18" t="s">
-        <x:v>451</x:v>
+        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="4:4">
       <x:c r="D10" t="s">
-        <x:v>57</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="3:3">
       <x:c r="C12" s="31" t="s">
-        <x:v>41</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="3:3">
       <x:c r="C13" t="s">
-        <x:v>277</x:v>
+        <x:v>314</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="3:3">
       <x:c r="C14" t="s">
-        <x:v>284</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="4:4">
       <x:c r="D15" s="20" t="s">
-        <x:v>219</x:v>
+        <x:v>347</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="3:3">
       <x:c r="C16" t="s">
-        <x:v>271</x:v>
+        <x:v>317</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="4:4">
       <x:c r="D17" t="s">
-        <x:v>379</x:v>
+        <x:v>542</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="3:3">
       <x:c r="C20" t="s">
-        <x:v>395</x:v>
+        <x:v>569</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="3:3">
       <x:c r="C21" t="s">
-        <x:v>431</x:v>
+        <x:v>421</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="3:3">
       <x:c r="C22" t="s">
-        <x:v>36</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="4:4">
       <x:c r="D23" t="s">
-        <x:v>620</x:v>
+        <x:v>289</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="4:4">
       <x:c r="D24" t="s">
-        <x:v>267</x:v>
+        <x:v>399</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="3:3" ht="19.25">
       <x:c r="C26" s="32" t="s">
-        <x:v>144</x:v>
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="3:5">
       <x:c r="C27" t="s">
-        <x:v>471</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="E27" t="s">
-        <x:v>182</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="3:5">
       <x:c r="C28" t="s">
-        <x:v>465</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="E28" t="s">
-        <x:v>588</x:v>
+        <x:v>660</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="3:5">
       <x:c r="C29" t="s">
-        <x:v>507</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="E29" t="s">
-        <x:v>222</x:v>
+        <x:v>352</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="3:5">
       <x:c r="C30" t="s">
-        <x:v>462</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="E30" t="s">
-        <x:v>213</x:v>
+        <x:v>355</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="3:3" ht="19.25">
       <x:c r="C32" s="32" t="s">
-        <x:v>450</x:v>
+        <x:v>605</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="3:3">
       <x:c r="C33" s="23" t="s">
-        <x:v>484</x:v>
+        <x:v>454</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="3:3">
       <x:c r="C34" t="s">
-        <x:v>283</x:v>
+        <x:v>309</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="3:3">
       <x:c r="C35" t="s">
-        <x:v>220</x:v>
+        <x:v>349</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="3:3">
       <x:c r="C36" t="s">
-        <x:v>581</x:v>
+        <x:v>654</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="3:3">
       <x:c r="C37" t="s">
-        <x:v>357</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="3:3">
       <x:c r="C39" s="31" t="s">
-        <x:v>108</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="3:3">
       <x:c r="C40" t="s">
-        <x:v>359</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="3:3">
       <x:c r="C41" t="s">
-        <x:v>212</x:v>
+        <x:v>346</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="3:3">
       <x:c r="C42" t="s">
-        <x:v>52</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="3:3">
       <x:c r="C43" t="s">
-        <x:v>215</x:v>
+        <x:v>353</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="3:3">
       <x:c r="C45" t="s">
-        <x:v>432</x:v>
+        <x:v>417</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="3:3">
       <x:c r="C46" t="s">
-        <x:v>448</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="3:3">
       <x:c r="C47" t="s">
-        <x:v>564</x:v>
+        <x:v>632</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="3:3">
       <x:c r="C48" t="s">
-        <x:v>34</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="3:3">
       <x:c r="C49" t="s">
-        <x:v>570</x:v>
+        <x:v>649</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="3:3">
       <x:c r="C51" t="s">
-        <x:v>285</x:v>
+        <x:v>406</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="3:3">
       <x:c r="C52" t="s">
-        <x:v>602</x:v>
+        <x:v>662</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="3:3">
       <x:c r="C53" t="s">
-        <x:v>603</x:v>
+        <x:v>659</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="3:3">
       <x:c r="C56" s="23" t="s">
-        <x:v>389</x:v>
+        <x:v>556</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="3:3">
       <x:c r="C58" s="18" t="s">
-        <x:v>541</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="3:3">
       <x:c r="C59" s="18" t="s">
-        <x:v>102</x:v>
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="3:3">
       <x:c r="C60" s="18" t="s">
-        <x:v>101</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="3:3">
       <x:c r="C61" s="18" t="s">
-        <x:v>134</x:v>
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="3:4">
       <x:c r="C62" s="18" t="s">
-        <x:v>479</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="D62" s="18" t="s">
-        <x:v>2</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="3:3">
       <x:c r="C64" t="s">
-        <x:v>373</x:v>
+        <x:v>545</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="3:3">
       <x:c r="C65" t="s">
-        <x:v>498</x:v>
+        <x:v>478</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="3:3">
       <x:c r="C66" t="s">
-        <x:v>464</x:v>
+        <x:v>453</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="3:3">
       <x:c r="C67" t="s">
-        <x:v>224</x:v>
+        <x:v>345</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="3:3">
       <x:c r="C69" t="s">
-        <x:v>461</x:v>
+        <x:v>432</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="3:3">
       <x:c r="C70" t="s">
-        <x:v>550</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="3:3">
       <x:c r="C71" t="s">
-        <x:v>214</x:v>
+        <x:v>357</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="3:3">
       <x:c r="C73" t="s">
-        <x:v>141</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="3:3">
       <x:c r="C74" t="s">
-        <x:v>594</x:v>
+        <x:v>673</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="3:3">
       <x:c r="C75" t="s">
-        <x:v>573</x:v>
+        <x:v>636</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="3:3">
       <x:c r="C77" t="s">
-        <x:v>94</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="3:3">
       <x:c r="C78" t="s">
-        <x:v>601</x:v>
+        <x:v>677</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="3:3">
       <x:c r="C79" t="s">
-        <x:v>218</x:v>
+        <x:v>348</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="3:13">
       <x:c r="C84" s="18" t="s">
-        <x:v>510</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H84" s="29" t="s">
-        <x:v>670</x:v>
+        <x:v>721</x:v>
       </x:c>
       <x:c r="I84" s="29"/>
       <x:c r="J84" s="28" t="s">
-        <x:v>444</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="K84" s="29"/>
       <x:c r="L84" s="28" t="s">
-        <x:v>92</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="M84" s="29" t="s">
-        <x:v>367</x:v>
+        <x:v>412</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="3:13" ht="31.5" customHeight="1">
       <x:c r="C85" s="18" t="s">
-        <x:v>420</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="H85" t="s">
-        <x:v>593</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="J85" s="18" t="s">
-        <x:v>164</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="L85" s="18" t="s">
-        <x:v>456</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="M85" s="33" t="s">
-        <x:v>246</x:v>
+        <x:v>390</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="3:13" ht="32.75">
       <x:c r="C86" t="s">
-        <x:v>211</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="H86" t="s">
-        <x:v>580</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="J86" s="18" t="s">
-        <x:v>333</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="L86" s="18" t="s">
-        <x:v>466</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="M86" s="33" t="s">
-        <x:v>630</x:v>
+        <x:v>287</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="3:13" ht="32.75">
       <x:c r="C87" t="s">
-        <x:v>338</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="H87" t="s">
-        <x:v>598</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="J87" s="18" t="s">
-        <x:v>221</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="L87" s="18" t="s">
-        <x:v>499</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="M87" s="33" t="s">
-        <x:v>216</x:v>
+        <x:v>354</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="3:12">
       <x:c r="C88" t="s">
-        <x:v>72</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="L88" s="18" t="s">
-        <x:v>413</x:v>
+        <x:v>587</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="3:3">
       <x:c r="C89" t="s">
-        <x:v>434</x:v>
+        <x:v>422</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="3:3">
       <x:c r="C90" t="s">
-        <x:v>73</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="3:3">
       <x:c r="C91" t="s">
-        <x:v>67</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="3:3">
       <x:c r="C92" t="s">
-        <x:v>62</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="3:3">
       <x:c r="C93" t="s">
-        <x:v>19</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="3:3">
       <x:c r="C95" t="s">
-        <x:v>158</x:v>
+        <x:v>619</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4994,27 +5288,27 @@
   <x:sheetData>
     <x:row r="5" spans="3:3" ht="22.05000000000000071054">
       <x:c r="C5" s="27" t="s">
-        <x:v>457</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="3:3">
       <x:c r="C6" s="20" t="s">
-        <x:v>680</x:v>
+        <x:v>713</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="3:3">
       <x:c r="C7" s="20" t="s">
-        <x:v>329</x:v>
+        <x:v>503</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="3:3">
       <x:c r="C8" s="20" t="s">
-        <x:v>223</x:v>
+        <x:v>359</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="3:3">
       <x:c r="C9" s="20" t="s">
-        <x:v>655</x:v>
+        <x:v>685</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5031,12 +5325,12 @@
   <x:sheetData>
     <x:row r="6" spans="3:3">
       <x:c r="C6" t="s">
-        <x:v>314</x:v>
+        <x:v>519</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="3:3">
       <x:c r="C8" s="20" t="s">
-        <x:v>261</x:v>
+        <x:v>256</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5056,45 +5350,45 @@
   <x:sheetData>
     <x:row r="4" spans="3:3">
       <x:c r="C4" t="s">
-        <x:v>458</x:v>
+        <x:v>436</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="3:3">
       <x:c r="C6" t="s">
-        <x:v>175</x:v>
+        <x:v>323</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="3:3">
       <x:c r="C7" t="s">
-        <x:v>279</x:v>
+        <x:v>320</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="4:4" ht="32.75">
       <x:c r="D8" s="34" t="s">
-        <x:v>189</x:v>
+        <x:v>514</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="3:4" ht="32.75">
       <x:c r="C9" s="20" t="s">
-        <x:v>622</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="D9" s="34" t="s">
-        <x:v>12</x:v>
+        <x:v>327</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="4:4">
       <x:c r="D10" s="20" t="s">
-        <x:v>10</x:v>
+        <x:v>326</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="3:3">
       <x:c r="C12" s="18" t="s">
-        <x:v>172</x:v>
+        <x:v>321</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="4:4">
       <x:c r="D13" t="s">
-        <x:v>91</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="3:3">
@@ -5104,27 +5398,27 @@
     </x:row>
     <x:row r="16" spans="3:3">
       <x:c r="C16" s="18" t="s">
-        <x:v>272</x:v>
+        <x:v>313</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="4:4">
       <x:c r="D17" t="s">
-        <x:v>669</x:v>
+        <x:v>720</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="3:3">
       <x:c r="C18" s="18" t="s">
-        <x:v>9</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="3:3">
       <x:c r="C19" s="18" t="s">
-        <x:v>252</x:v>
+        <x:v>389</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="3:3">
       <x:c r="C20" s="18" t="s">
-        <x:v>452</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5144,65 +5438,65 @@
   <x:sheetData>
     <x:row r="6" spans="4:4">
       <x:c r="D6" t="s">
-        <x:v>70</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="4:4">
       <x:c r="D8" t="s">
-        <x:v>676</x:v>
+        <x:v>725</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="4:4">
       <x:c r="D9" s="20" t="s">
-        <x:v>341</x:v>
+        <x:v>494</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="4:4">
       <x:c r="D10" t="s">
-        <x:v>208</x:v>
+        <x:v>334</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="4:4">
       <x:c r="D12" s="18" t="s">
-        <x:v>665</x:v>
+        <x:v>718</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="4:4">
       <x:c r="D13" s="21" t="s">
-        <x:v>671</x:v>
+        <x:v>705</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="4:4">
       <x:c r="D14" t="s">
-        <x:v>334</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="4:4">
       <x:c r="D16" s="18" t="s">
-        <x:v>411</x:v>
+        <x:v>586</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="4:4">
       <x:c r="D17" s="20" t="s">
-        <x:v>673</x:v>
+        <x:v>707</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="4:4">
       <x:c r="D18" t="s">
-        <x:v>599</x:v>
+        <x:v>657</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="4:4">
       <x:c r="D20" t="s">
-        <x:v>29</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="4:5">
       <x:c r="D21" t="s">
-        <x:v>530</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E21" s="18" t="s">
-        <x:v>679</x:v>
+        <x:v>710</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="5:5">
@@ -5210,10 +5504,10 @@
     </x:row>
     <x:row r="23" spans="4:5">
       <x:c r="D23" t="s">
-        <x:v>508</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E23" s="18" t="s">
-        <x:v>605</x:v>
+        <x:v>676</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="5:5">
@@ -5221,10 +5515,10 @@
     </x:row>
     <x:row r="25" spans="4:5">
       <x:c r="D25" t="s">
-        <x:v>546</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E25" s="18" t="s">
-        <x:v>205</x:v>
+        <x:v>333</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="5:5">
@@ -5232,10 +5526,10 @@
     </x:row>
     <x:row r="27" spans="4:5">
       <x:c r="D27" t="s">
-        <x:v>549</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E27" s="18" t="s">
-        <x:v>592</x:v>
+        <x:v>664</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="5:5">
@@ -5243,10 +5537,10 @@
     </x:row>
     <x:row r="29" spans="4:5">
       <x:c r="D29" t="s">
-        <x:v>555</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E29" s="18" t="s">
-        <x:v>201</x:v>
+        <x:v>332</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5263,17 +5557,17 @@
   <x:sheetData>
     <x:row r="8" spans="3:3">
       <x:c r="C8" t="s">
-        <x:v>572</x:v>
+        <x:v>644</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="3:3">
       <x:c r="C9" s="2" t="s">
-        <x:v>243</x:v>
+        <x:v>380</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:3">
       <x:c r="C10" s="2" t="s">
-        <x:v>628</x:v>
+        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:3">
@@ -5302,12 +5596,12 @@
   <x:sheetData>
     <x:row r="5" spans="4:4">
       <x:c r="D5" t="s">
-        <x:v>23</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="4:4">
       <x:c r="D7" t="s">
-        <x:v>416</x:v>
+        <x:v>590</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="5:5">
@@ -5315,77 +5609,77 @@
     </x:row>
     <x:row r="9" spans="5:5">
       <x:c r="E9" s="18" t="s">
-        <x:v>170</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="5:5">
       <x:c r="E10" s="18" t="s">
-        <x:v>13</x:v>
+        <x:v>329</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="5:5">
       <x:c r="E11" t="s">
-        <x:v>269</x:v>
+        <x:v>402</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="5:5">
       <x:c r="E12" t="s">
-        <x:v>206</x:v>
+        <x:v>342</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="5:5">
       <x:c r="E13" t="s">
-        <x:v>217</x:v>
+        <x:v>356</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="5:5">
       <x:c r="E15" s="23" t="s">
-        <x:v>75</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="6:6">
       <x:c r="F16" s="21" t="s">
-        <x:v>129</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="6:6">
       <x:c r="F17" s="21" t="s">
-        <x:v>638</x:v>
+        <x:v>700</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="6:6">
       <x:c r="F18" s="21" t="s">
-        <x:v>239</x:v>
+        <x:v>363</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="6:6">
       <x:c r="F19" s="18" t="s">
-        <x:v>263</x:v>
+        <x:v>397</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="6:6">
       <x:c r="F21" s="35" t="s">
-        <x:v>204</x:v>
+        <x:v>339</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="5:5" ht="16.5" customHeight="1">
       <x:c r="E23" s="18" t="s">
-        <x:v>176</x:v>
+        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="5:5">
       <x:c r="E25" t="s">
-        <x:v>190</x:v>
+        <x:v>513</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="5:5">
       <x:c r="E27" t="s">
-        <x:v>131</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="5:5">
       <x:c r="E28" t="s">
-        <x:v>151</x:v>
+        <x:v>627</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5406,123 +5700,123 @@
   <x:sheetData>
     <x:row r="5" spans="4:4">
       <x:c r="D5" t="s">
-        <x:v>502</x:v>
+        <x:v>473</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="4:5">
       <x:c r="D6" t="s">
-        <x:v>520</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E6" t="s">
-        <x:v>682</x:v>
+        <x:v>714</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="4:5">
       <x:c r="D7" t="s">
-        <x:v>518</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E7" t="s">
-        <x:v>611</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="4:5">
       <x:c r="D8" t="s">
-        <x:v>514</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E8" t="s">
-        <x:v>346</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="4:5">
       <x:c r="D9" t="s">
-        <x:v>88</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E9" t="s">
-        <x:v>257</x:v>
+        <x:v>393</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="4:5">
       <x:c r="D10" t="s">
-        <x:v>521</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E10" t="s">
-        <x:v>275</x:v>
+        <x:v>318</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="4:5">
       <x:c r="D11" t="s">
-        <x:v>513</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E11" t="s">
-        <x:v>179</x:v>
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="4:4">
       <x:c r="D14" t="s">
-        <x:v>286</x:v>
+        <x:v>524</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="4:4">
       <x:c r="D15" t="s">
-        <x:v>509</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="4:4">
       <x:c r="D16" t="s">
-        <x:v>509</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="4:4">
       <x:c r="D17" t="s">
-        <x:v>553</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="4:4">
       <x:c r="D18" t="s">
-        <x:v>553</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="4:4">
       <x:c r="D19" t="s">
-        <x:v>553</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="4:4">
       <x:c r="D20" t="s">
-        <x:v>6</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="4:7">
       <x:c r="D21" t="s">
-        <x:v>85</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="E21" t="s">
-        <x:v>421</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="G21" t="s">
-        <x:v>504</x:v>
+        <x:v>479</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="4:7">
       <x:c r="D22" t="s">
-        <x:v>96</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E22" t="s">
-        <x:v>288</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="G22" t="s">
-        <x:v>80</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="4:7">
       <x:c r="D23" t="s">
-        <x:v>93</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="E23" t="s">
-        <x:v>66</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G23" t="s">
-        <x:v>506</x:v>
+        <x:v>480</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5542,178 +5836,178 @@
   <x:sheetData>
     <x:row r="6" spans="3:3">
       <x:c r="C6" t="s">
-        <x:v>509</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="3:3">
       <x:c r="C7" s="20" t="s">
-        <x:v>666</x:v>
+        <x:v>719</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="3:3">
       <x:c r="C8" t="s">
-        <x:v>414</x:v>
+        <x:v>593</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="3:3">
       <x:c r="C9" t="s">
-        <x:v>17</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:3">
       <x:c r="C10" t="s">
-        <x:v>443</x:v>
+        <x:v>610</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="3:3">
       <x:c r="C12" t="s">
-        <x:v>296</x:v>
+        <x:v>408</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C19" s="41" t="s">
-        <x:v>688</x:v>
+      <x:c r="C19" s="40" t="s">
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C20" s="41" t="s">
-        <x:v>5</x:v>
+      <x:c r="C20" s="40" t="s">
+        <x:v>499</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C21" s="43" t="s">
-        <x:v>696</x:v>
+      <x:c r="C21" s="42" t="s">
+        <x:v>603</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C22" s="41" t="s">
-        <x:v>4</x:v>
+      <x:c r="C22" s="40" t="s">
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C23" s="41" t="s">
-        <x:v>192</x:v>
+      <x:c r="C23" s="40" t="s">
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="3:3">
-      <x:c r="C24" s="42"/>
+      <x:c r="C24" s="41"/>
     </x:row>
     <x:row r="25" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C25" s="41" t="s">
-        <x:v>635</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="3:3" ht="53.39999999999999857891">
-      <x:c r="C26" s="41" t="s">
+      <x:c r="C25" s="40" t="s">
+        <x:v>704</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C26" s="40" t="s">
+        <x:v>252</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C27" s="40" t="s">
+        <x:v>411</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C28" s="40" t="s">
+        <x:v>253</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C29" s="40" t="s">
+        <x:v>678</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="3:3">
+      <x:c r="C30" s="41"/>
+    </x:row>
+    <x:row r="31" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C31" s="40" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C32" s="40" t="s">
+        <x:v>178</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C33" s="40" t="s">
+        <x:v>609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C34" s="40" t="s">
+        <x:v>407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C35" s="40" t="s">
+        <x:v>403</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="3:3">
+      <x:c r="C36" s="41"/>
+    </x:row>
+    <x:row r="37" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C37" s="40" t="s">
+        <x:v>612</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C38" s="40" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C39" s="40" t="s">
+        <x:v>409</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C40" s="40" t="s">
+        <x:v>108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C41" s="40" t="s">
+        <x:v>405</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="3:3">
+      <x:c r="C42" s="41"/>
+    </x:row>
+    <x:row r="43" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C43" s="40" t="s">
+        <x:v>611</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="3:3" ht="53.39999999999999857891">
+      <x:c r="C44" s="42" t="s">
+        <x:v>311</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C45" s="40" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C46" s="40" t="s">
+        <x:v>613</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C47" s="40" t="s">
+        <x:v>108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="3:3" ht="27.10000000000000142109">
+      <x:c r="C48" s="40" t="s">
         <x:v>608</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C27" s="41" t="s">
-        <x:v>289</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C28" s="41" t="s">
-        <x:v>607</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C29" s="41" t="s">
-        <x:v>687</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="3:3">
-      <x:c r="C30" s="42"/>
-    </x:row>
-    <x:row r="31" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C31" s="41" t="s">
-        <x:v>698</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C32" s="41" t="s">
-        <x:v>697</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C33" s="41" t="s">
-        <x:v>695</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C34" s="41" t="s">
-        <x:v>290</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C35" s="41" t="s">
-        <x:v>291</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="3:3">
-      <x:c r="C36" s="42"/>
-    </x:row>
-    <x:row r="37" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C37" s="41" t="s">
-        <x:v>692</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C38" s="41" t="s">
-        <x:v>509</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C39" s="41" t="s">
-        <x:v>292</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C40" s="41" t="s">
-        <x:v>689</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C41" s="41" t="s">
-        <x:v>293</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="3:3">
-      <x:c r="C42" s="42"/>
-    </x:row>
-    <x:row r="43" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C43" s="41" t="s">
-        <x:v>693</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="3:3" ht="53.39999999999999857891">
-      <x:c r="C44" s="43" t="s">
-        <x:v>690</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C45" s="41" t="s">
-        <x:v>509</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C46" s="41" t="s">
-        <x:v>691</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C47" s="41" t="s">
-        <x:v>689</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="3:3" ht="27.10000000000000142109">
-      <x:c r="C48" s="41" t="s">
-        <x:v>694</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
@@ -5730,277 +6024,277 @@
   <x:sheetData>
     <x:row r="5" spans="3:3">
       <x:c r="C5" t="s">
-        <x:v>399</x:v>
+        <x:v>575</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="3:3">
       <x:c r="C6" s="18" t="s">
-        <x:v>74</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="3:3">
       <x:c r="C7" s="18" t="s">
-        <x:v>198</x:v>
+        <x:v>331</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="3:4">
       <x:c r="C9" t="s">
-        <x:v>513</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D9" t="s">
-        <x:v>68</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:4">
       <x:c r="C10" t="s">
-        <x:v>558</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D10" t="s">
-        <x:v>77</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:4">
       <x:c r="C11" t="s">
-        <x:v>298</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D11" s="18" t="s">
-        <x:v>674</x:v>
+        <x:v>709</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="3:4">
       <x:c r="C12" t="s">
-        <x:v>103</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="D12" t="s">
-        <x:v>446</x:v>
+        <x:v>604</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="3:4">
       <x:c r="C13" t="s">
-        <x:v>574</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="D13" t="s">
-        <x:v>199</x:v>
+        <x:v>341</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="3:4">
       <x:c r="C14" t="s">
-        <x:v>71</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D14" t="s">
-        <x:v>63</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="3:4">
       <x:c r="C15" t="s">
-        <x:v>445</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="D15" t="s">
-        <x:v>672</x:v>
+        <x:v>712</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="3:4">
       <x:c r="C17" t="s">
-        <x:v>84</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="D17" t="s">
-        <x:v>171</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="3:4">
       <x:c r="C18" t="s">
-        <x:v>548</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D18" t="s">
-        <x:v>196</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="3:4">
       <x:c r="C19" t="s">
-        <x:v>297</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="D19" t="s">
-        <x:v>163</x:v>
+        <x:v>629</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="3:4">
       <x:c r="C20" t="s">
-        <x:v>86</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="D20" t="s">
-        <x:v>678</x:v>
+        <x:v>727</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="3:4">
       <x:c r="C21" t="s">
-        <x:v>524</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D21" t="s">
-        <x:v>348</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="3:4">
       <x:c r="C22" s="18" t="s">
-        <x:v>523</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D22" s="18" t="s">
-        <x:v>191</x:v>
+        <x:v>510</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="2:3">
       <x:c r="B24" s="31" t="s">
-        <x:v>537</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C24" s="31" t="s">
-        <x:v>155</x:v>
+        <x:v>622</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="3:4">
       <x:c r="C25" s="36" t="s">
-        <x:v>87</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D25" t="s">
-        <x:v>150</x:v>
+        <x:v>616</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="3:4">
       <x:c r="C26" s="36" t="s">
-        <x:v>600</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="D26" t="s">
-        <x:v>247</x:v>
+        <x:v>384</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="3:4">
       <x:c r="C27" s="36" t="s">
-        <x:v>449</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="D27" t="s">
-        <x:v>1</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="3:4">
       <x:c r="C28" s="36" t="s">
-        <x:v>415</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="D28" t="s">
-        <x:v>625</x:v>
+        <x:v>301</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="18"/>
       <x:c r="B31" s="18" t="s">
-        <x:v>497</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="C31" s="18" t="s">
-        <x:v>0</x:v>
+        <x:v>279</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="3:4">
       <x:c r="C32" s="37" t="s">
-        <x:v>505</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="D32" t="s">
-        <x:v>173</x:v>
+        <x:v>325</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="3:4">
       <x:c r="C33" s="37" t="s">
-        <x:v>583</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="D33" t="s">
-        <x:v>247</x:v>
+        <x:v>384</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="3:4">
       <x:c r="C34" s="37" t="s">
-        <x:v>595</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="D34" t="s">
-        <x:v>347</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="3:4">
       <x:c r="C35" s="38" t="s">
-        <x:v>69</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D35" t="s">
-        <x:v>153</x:v>
+        <x:v>626</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="3:4">
       <x:c r="C36" s="37" t="s">
-        <x:v>683</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="D36" t="s">
-        <x:v>358</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="3:4">
       <x:c r="C37" s="38" t="s">
-        <x:v>551</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D37" t="s">
-        <x:v>1</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="3:4">
       <x:c r="C38" s="38" t="s">
-        <x:v>503</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="D38" t="s">
-        <x:v>625</x:v>
+        <x:v>301</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="3:4">
       <x:c r="C40" s="39" t="s">
-        <x:v>500</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="D40" t="s">
-        <x:v>154</x:v>
+        <x:v>617</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="3:4">
       <x:c r="C41" s="39" t="s">
-        <x:v>81</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="D41" t="s">
-        <x:v>159</x:v>
+        <x:v>625</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="3:4">
       <x:c r="C42" s="39" t="s">
-        <x:v>501</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="D42" t="s">
-        <x:v>606</x:v>
+        <x:v>658</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="3:4">
       <x:c r="C43" s="39" t="s">
-        <x:v>442</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="D43" t="s">
-        <x:v>662</x:v>
+        <x:v>717</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="3:3">
       <x:c r="C46" t="s">
-        <x:v>197</x:v>
+        <x:v>340</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="3:3">
       <x:c r="C47" t="s">
-        <x:v>675</x:v>
+        <x:v>724</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="3:3">
       <x:c r="C48" s="20" t="s">
-        <x:v>64</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
@@ -6013,24 +6307,24 @@
   <x:sheetData>
     <x:row r="3" spans="2:2">
       <x:c r="B3" t="s">
-        <x:v>258</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="2:3">
       <x:c r="B7" s="18" t="s">
-        <x:v>233</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="C7" s="18"/>
     </x:row>
     <x:row r="8" spans="2:3">
       <x:c r="B8" s="18" t="s">
-        <x:v>186</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C8" s="18"/>
     </x:row>
     <x:row r="9" spans="2:3">
       <x:c r="B9" s="18" t="s">
-        <x:v>157</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="C9" s="18"/>
     </x:row>
@@ -6040,52 +6334,521 @@
     </x:row>
     <x:row r="12" spans="2:2">
       <x:c r="B12" t="s">
-        <x:v>253</x:v>
+        <x:v>386</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="2:2">
       <x:c r="B13" t="s">
-        <x:v>667</x:v>
+        <x:v>706</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="2:2">
       <x:c r="B14" t="s">
-        <x:v>668</x:v>
+        <x:v>711</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="2:2">
       <x:c r="B15" t="s">
-        <x:v>200</x:v>
+        <x:v>336</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="2:2">
       <x:c r="B16" t="s">
-        <x:v>365</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="2:2">
       <x:c r="B18" t="s">
-        <x:v>265</x:v>
+        <x:v>396</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="2:2">
       <x:c r="B19" t="s">
-        <x:v>610</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="2:2">
       <x:c r="B20" t="s">
-        <x:v>248</x:v>
+        <x:v>383</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="2:2">
       <x:c r="B21" t="s">
-        <x:v>274</x:v>
+        <x:v>306</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet27"/>
+  <x:dimension ref="A1:A1"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
+  <x:sheetData/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet26"/>
+  <x:dimension ref="C18:C53"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="30" customHeight="1"/>
+  <x:cols>
+    <x:col min="3" max="3" width="177.94921875" bestFit="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="18" spans="3:3" customHeight="1">
+      <x:c r="C18" s="44" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="3:3" customHeight="1">
+      <x:c r="C19" s="44" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="3:3" customHeight="1">
+      <x:c r="C20" s="44" t="s">
+        <x:v>732</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="3:3" customHeight="1">
+      <x:c r="C21" s="44" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="3:3" customHeight="1">
+      <x:c r="C22" s="44" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="3:3" customHeight="1">
+      <x:c r="C23" s="45"/>
+    </x:row>
+    <x:row r="24" spans="3:3" customHeight="1">
+      <x:c r="C24" s="44" t="s">
+        <x:v>739</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="3:3" ht="26.35000000000000142109">
+      <x:c r="C25" s="44" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="3:3" ht="53.25" customHeight="1">
+      <x:c r="C26" s="44" t="s">
+        <x:v>269</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="3:3" customHeight="1">
+      <x:c r="C27" s="44" t="s">
+        <x:v>734</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="3:3" customHeight="1">
+      <x:c r="C28" s="44" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="3:3" customHeight="1">
+      <x:c r="C29" s="44" t="s">
+        <x:v>272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="3:3" customHeight="1">
+      <x:c r="C30" s="44" t="s">
+        <x:v>740</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="3:3" customHeight="1">
+      <x:c r="C31" s="45"/>
+    </x:row>
+    <x:row r="32" spans="3:3" customHeight="1">
+      <x:c r="C32" s="44" t="s">
+        <x:v>736</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="3:3" customHeight="1">
+      <x:c r="C33" s="44" t="s">
+        <x:v>304</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="3:3" customHeight="1">
+      <x:c r="C34" s="45"/>
+    </x:row>
+    <x:row r="35" spans="3:3" customHeight="1">
+      <x:c r="C35" s="44" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="3:3" customHeight="1">
+      <x:c r="C36" s="44" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="3:3" customHeight="1">
+      <x:c r="C37" s="45"/>
+    </x:row>
+    <x:row r="38" spans="3:3" customHeight="1">
+      <x:c r="C38" s="44" t="s">
+        <x:v>743</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="3:3" customHeight="1">
+      <x:c r="C39" s="44" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="3:3" customHeight="1">
+      <x:c r="C40" s="44" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="3:3" customHeight="1">
+      <x:c r="C41" s="45"/>
+    </x:row>
+    <x:row r="42" spans="3:3" customHeight="1">
+      <x:c r="C42" s="44" t="s">
+        <x:v>737</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="3:3" customHeight="1">
+      <x:c r="C43" s="44" t="s">
+        <x:v>730</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="3:3" customHeight="1">
+      <x:c r="C44" s="44" t="s">
+        <x:v>731</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="3:3" customHeight="1">
+      <x:c r="C45" s="45"/>
+    </x:row>
+    <x:row r="46" spans="3:3" customHeight="1">
+      <x:c r="C46" s="44" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="3:3" customHeight="1">
+      <x:c r="C47" s="44" t="s">
+        <x:v>735</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="3:3" customHeight="1">
+      <x:c r="C48" s="44" t="s">
+        <x:v>742</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="3:3" customHeight="1">
+      <x:c r="C49" s="44" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="3:3" customHeight="1">
+      <x:c r="C50" s="44" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="3:3" customHeight="1">
+      <x:c r="C51" s="44" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="3:3" customHeight="1">
+      <x:c r="C52" s="44" t="s">
+        <x:v>738</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="3:3" customHeight="1">
+      <x:c r="C53" s="44" t="s">
+        <x:v>741</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet28"/>
+  <x:dimension ref="C18:C53"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="30" customHeight="1"/>
+  <x:cols>
+    <x:col min="3" max="3" width="177.94921875" bestFit="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="18" spans="3:3" customHeight="1">
+      <x:c r="C18" s="44"/>
+    </x:row>
+    <x:row r="19" spans="3:3" customHeight="1">
+      <x:c r="C19" s="44"/>
+    </x:row>
+    <x:row r="20" spans="3:3" customHeight="1">
+      <x:c r="C20" s="44"/>
+    </x:row>
+    <x:row r="21" spans="3:3" customHeight="1">
+      <x:c r="C21" s="44"/>
+    </x:row>
+    <x:row r="22" spans="3:3" customHeight="1">
+      <x:c r="C22" s="44"/>
+    </x:row>
+    <x:row r="23" spans="3:3" customHeight="1">
+      <x:c r="C23" s="45"/>
+    </x:row>
+    <x:row r="24" spans="3:3" customHeight="1">
+      <x:c r="C24" s="44"/>
+    </x:row>
+    <x:row r="25" spans="3:3" ht="26.35000000000000142109">
+      <x:c r="C25" s="44"/>
+    </x:row>
+    <x:row r="26" spans="3:3" ht="53.25" customHeight="1">
+      <x:c r="C26" s="44"/>
+    </x:row>
+    <x:row r="27" spans="3:3" customHeight="1">
+      <x:c r="C27" s="44"/>
+    </x:row>
+    <x:row r="28" spans="3:3" customHeight="1">
+      <x:c r="C28" s="44"/>
+    </x:row>
+    <x:row r="29" spans="3:3" customHeight="1">
+      <x:c r="C29" s="44"/>
+    </x:row>
+    <x:row r="30" spans="3:3" customHeight="1">
+      <x:c r="C30" s="44"/>
+    </x:row>
+    <x:row r="31" spans="3:3" customHeight="1">
+      <x:c r="C31" s="45"/>
+    </x:row>
+    <x:row r="32" spans="3:3" customHeight="1">
+      <x:c r="C32" s="44"/>
+    </x:row>
+    <x:row r="33" spans="3:3" customHeight="1">
+      <x:c r="C33" s="44"/>
+    </x:row>
+    <x:row r="34" spans="3:3" customHeight="1">
+      <x:c r="C34" s="45"/>
+    </x:row>
+    <x:row r="35" spans="3:3" customHeight="1">
+      <x:c r="C35" s="44"/>
+    </x:row>
+    <x:row r="36" spans="3:3" customHeight="1">
+      <x:c r="C36" s="44"/>
+    </x:row>
+    <x:row r="37" spans="3:3" customHeight="1">
+      <x:c r="C37" s="45"/>
+    </x:row>
+    <x:row r="38" spans="3:3" customHeight="1">
+      <x:c r="C38" s="44"/>
+    </x:row>
+    <x:row r="39" spans="3:3" customHeight="1">
+      <x:c r="C39" s="44"/>
+    </x:row>
+    <x:row r="40" spans="3:3" customHeight="1">
+      <x:c r="C40" s="44"/>
+    </x:row>
+    <x:row r="41" spans="3:3" customHeight="1">
+      <x:c r="C41" s="45"/>
+    </x:row>
+    <x:row r="42" spans="3:3" customHeight="1">
+      <x:c r="C42" s="44"/>
+    </x:row>
+    <x:row r="43" spans="3:3" customHeight="1">
+      <x:c r="C43" s="44"/>
+    </x:row>
+    <x:row r="44" spans="3:3" customHeight="1">
+      <x:c r="C44" s="44"/>
+    </x:row>
+    <x:row r="45" spans="3:3" customHeight="1">
+      <x:c r="C45" s="45"/>
+    </x:row>
+    <x:row r="46" spans="3:3" customHeight="1">
+      <x:c r="C46" s="44"/>
+    </x:row>
+    <x:row r="47" spans="3:3" customHeight="1">
+      <x:c r="C47" s="44"/>
+    </x:row>
+    <x:row r="48" spans="3:3" customHeight="1">
+      <x:c r="C48" s="44"/>
+    </x:row>
+    <x:row r="49" spans="3:3" customHeight="1">
+      <x:c r="C49" s="44"/>
+    </x:row>
+    <x:row r="50" spans="3:3" customHeight="1">
+      <x:c r="C50" s="44"/>
+    </x:row>
+    <x:row r="51" spans="3:3" customHeight="1">
+      <x:c r="C51" s="44"/>
+    </x:row>
+    <x:row r="52" spans="3:3" customHeight="1">
+      <x:c r="C52" s="44"/>
+    </x:row>
+    <x:row r="53" spans="3:3" customHeight="1">
+      <x:c r="C53" s="44"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet29"/>
+  <x:dimension ref="A1:A1"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
+  <x:cols>
+    <x:col min="1" max="1" width="9.00390625" bestFit="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet30"/>
+  <x:dimension ref="B4:B40"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
+  <x:sheetData>
+    <x:row r="4" spans="2:2">
+      <x:c r="B4" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="2:2">
+      <x:c r="B5" s="20" t="s">
+        <x:v>271</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="2:2">
+      <x:c r="B6" s="20" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="2:2">
+      <x:c r="B7" s="20" t="s">
+        <x:v>747</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="2:2">
+      <x:c r="B8" s="20" t="s">
+        <x:v>748</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="2:2">
+      <x:c r="B11" s="18" t="s">
+        <x:v>749</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="2:2">
+      <x:c r="B12" s="20" t="s">
+        <x:v>750</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="2:2">
+      <x:c r="B13" s="20" t="s">
+        <x:v>752</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="2:2">
+      <x:c r="B14" s="20" t="s">
+        <x:v>733</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="2:2">
+      <x:c r="B16" s="18" t="s">
+        <x:v>753</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="2:2">
+      <x:c r="B17" s="20" t="s">
+        <x:v>305</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="2:2">
+      <x:c r="B19" t="s">
+        <x:v>754</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="2:2">
+      <x:c r="B20" s="20" t="s">
+        <x:v>270</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="2:2">
+      <x:c r="B22" t="s">
+        <x:v>755</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="2:2">
+      <x:c r="B23" s="20" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="2:2">
+      <x:c r="B25" t="s">
+        <x:v>757</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="2:2">
+      <x:c r="B27" t="s">
+        <x:v>756</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="2:2">
+      <x:c r="B28" s="20" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="2:2">
+      <x:c r="B30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="2:2">
+      <x:c r="B31" t="s">
+        <x:v>758</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="2:2">
+      <x:c r="B33" t="s">
+        <x:v>744</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="2:2">
+      <x:c r="B34" t="s">
+        <x:v>759</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="2:2">
+      <x:c r="B36" t="s">
+        <x:v>751</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="2:2">
+      <x:c r="B39" t="s">
+        <x:v>745</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="2:2">
+      <x:c r="B40" t="s">
+        <x:v>762</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
+  <x:drawing r:id="rId1"/>
 </x:worksheet>
 </file>
 
@@ -6097,334 +6860,409 @@
   <x:sheetData>
     <x:row r="7" spans="4:4">
       <x:c r="D7" t="s">
-        <x:v>376</x:v>
+        <x:v>540</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="4:4">
       <x:c r="D9" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:4">
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2" t="s">
-        <x:v>178</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:4">
       <x:c r="C11" s="2"/>
       <x:c r="D11" s="4" t="s">
-        <x:v>313</x:v>
+        <x:v>518</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="3:5">
       <x:c r="C12" s="1"/>
       <x:c r="E12" t="s">
-        <x:v>47</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="3:5">
       <x:c r="C13" s="1"/>
       <x:c r="E13" t="s">
-        <x:v>230</x:v>
+        <x:v>366</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="3:5">
       <x:c r="C14" s="1"/>
       <x:c r="E14" t="s">
-        <x:v>360</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="5:5">
       <x:c r="E15" t="s">
-        <x:v>180</x:v>
+        <x:v>264</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="6:6">
       <x:c r="F16" s="4" t="s">
-        <x:v>312</x:v>
+        <x:v>533</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="6:6">
       <x:c r="F17" t="s">
-        <x:v>332</x:v>
+        <x:v>502</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="6:6">
       <x:c r="F18" t="s">
-        <x:v>356</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="6:6">
       <x:c r="F19" t="s">
-        <x:v>349</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="6:6">
       <x:c r="F20" t="s">
-        <x:v>174</x:v>
+        <x:v>322</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="6:6">
       <x:c r="F21" t="s">
-        <x:v>187</x:v>
+        <x:v>511</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="4:4">
       <x:c r="D23" s="15" t="s">
-        <x:v>578</x:v>
+        <x:v>650</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="4:4">
       <x:c r="D24" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>328</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="4:4">
       <x:c r="D25" s="2" t="s">
-        <x:v>313</x:v>
+        <x:v>518</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="4:4">
       <x:c r="D26" t="s">
-        <x:v>278</x:v>
+        <x:v>316</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="4:4">
       <x:c r="D27" t="s">
-        <x:v>236</x:v>
+        <x:v>371</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="4:4">
       <x:c r="D28" t="s">
-        <x:v>181</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="4:16">
       <x:c r="D29" t="s">
-        <x:v>633</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="P29" s="18" t="s">
-        <x:v>125</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="5:16">
       <x:c r="E30" s="4" t="s">
-        <x:v>312</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="P30" t="s">
-        <x:v>48</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="5:16">
       <x:c r="E31" t="s">
-        <x:v>345</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P31" t="s">
-        <x:v>310</x:v>
+        <x:v>529</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="5:16">
       <x:c r="E32" t="s">
-        <x:v>238</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="P32" t="s">
-        <x:v>650</x:v>
+        <x:v>683</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="5:17">
       <x:c r="E33" t="s">
-        <x:v>281</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="P33" t="s">
-        <x:v>535</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="Q33" s="20" t="s">
-        <x:v>540</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="5:5">
       <x:c r="E34" t="s">
-        <x:v>632</x:v>
+        <x:v>293</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="4:4">
       <x:c r="D36" s="15" t="s">
-        <x:v>419</x:v>
+        <x:v>588</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="4:4">
       <x:c r="D37" s="2" t="s">
-        <x:v>262</x:v>
+        <x:v>400</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="4:16">
       <x:c r="D38" s="2" t="s">
-        <x:v>313</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="P38" s="18" t="s">
-        <x:v>388</x:v>
+        <x:v>564</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="4:4">
       <x:c r="D39" t="s">
-        <x:v>455</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="4:4">
       <x:c r="D40" t="s">
-        <x:v>185</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="4:4">
       <x:c r="D41" t="s">
-        <x:v>409</x:v>
+        <x:v>585</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="4:4">
       <x:c r="D42" t="s">
-        <x:v>352</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="4:5">
       <x:c r="D43" t="s">
-        <x:v>532</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E43" s="4" t="s">
-        <x:v>312</x:v>
+        <x:v>533</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="5:5">
       <x:c r="E44" t="s">
-        <x:v>654</x:v>
+        <x:v>698</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="5:5">
       <x:c r="E45" t="s">
-        <x:v>482</x:v>
+        <x:v>468</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="5:5">
       <x:c r="E46" t="s">
-        <x:v>266</x:v>
+        <x:v>398</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="5:5">
       <x:c r="E47" t="s">
-        <x:v>337</x:v>
+        <x:v>486</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="4:4">
       <x:c r="D49" s="15" t="s">
-        <x:v>396</x:v>
+        <x:v>572</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="4:4">
       <x:c r="D50" s="2" t="s">
-        <x:v>280</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="4:4">
       <x:c r="D51" s="2" t="s">
-        <x:v>313</x:v>
+        <x:v>518</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="4:4">
       <x:c r="D52" t="s">
-        <x:v>410</x:v>
+        <x:v>582</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="4:4">
       <x:c r="D53" t="s">
-        <x:v>582</x:v>
+        <x:v>641</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="4:4">
       <x:c r="D54" t="s">
-        <x:v>646</x:v>
+        <x:v>689</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="4:4">
       <x:c r="D55" t="s">
-        <x:v>643</x:v>
+        <x:v>697</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="5:5">
       <x:c r="E56" s="4" t="s">
-        <x:v>312</x:v>
+        <x:v>533</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="5:5">
       <x:c r="E57" t="s">
-        <x:v>366</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="5:5">
       <x:c r="E58" t="s">
-        <x:v>325</x:v>
+        <x:v>488</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="5:5">
       <x:c r="E59" t="s">
-        <x:v>660</x:v>
+        <x:v>701</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="4:4" ht="17.14999999999999857891">
       <x:c r="D61" s="16" t="s">
-        <x:v>565</x:v>
+        <x:v>633</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="4:4" ht="17.14999999999999857891">
       <x:c r="D62" s="6" t="s">
-        <x:v>454</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="5:5" ht="17.14999999999999857891">
       <x:c r="E63" s="6" t="s">
-        <x:v>311</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="5:5" ht="17.14999999999999857891">
       <x:c r="E64" s="6" t="s">
-        <x:v>649</x:v>
+        <x:v>695</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="5:5" ht="17.14999999999999857891">
       <x:c r="E65" s="6" t="s">
-        <x:v>228</x:v>
+        <x:v>373</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="5:5" ht="17.14999999999999857891">
       <x:c r="E66" s="6" t="s">
-        <x:v>563</x:v>
+        <x:v>648</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="5:5" ht="17.14999999999999857891">
       <x:c r="E67" s="6" t="s">
-        <x:v>226</x:v>
+        <x:v>369</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="5:6" ht="18.55000000000000071054">
       <x:c r="E68" s="7"/>
       <x:c r="F68" s="5" t="s">
-        <x:v>99</x:v>
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="5:6" ht="18.55000000000000071054">
       <x:c r="E69" s="7"/>
       <x:c r="F69" s="6" t="s">
-        <x:v>320</x:v>
+        <x:v>552</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="5:6" ht="18.55000000000000071054">
       <x:c r="E70" s="7"/>
       <x:c r="F70" s="6" t="s">
-        <x:v>569</x:v>
+        <x:v>634</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.69972223043441772461" right="0.69972223043441772461" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet31"/>
+  <x:dimension ref="B3:B14"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="25" customHeight="1"/>
+  <x:cols>
+    <x:col min="2" max="2" width="189.46875" bestFit="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="3" spans="2:2" customHeight="1">
+      <x:c r="B3" s="40" t="s">
+        <x:v>746</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="2:2" customHeight="1">
+      <x:c r="B4" s="40" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="2:2" customHeight="1">
+      <x:c r="B5" s="42" t="s">
+        <x:v>763</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="2:2" customHeight="1">
+      <x:c r="B6" s="42" t="s">
+        <x:v>765</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="2:2" customHeight="1">
+      <x:c r="B7" s="42" t="s">
+        <x:v>764</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="2:2" customHeight="1">
+      <x:c r="B8" s="42" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="2:2" customHeight="1">
+      <x:c r="B9" s="42" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="2:2" customHeight="1">
+      <x:c r="B10" s="40" t="s">
+        <x:v>760</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="2:2" customHeight="1">
+      <x:c r="B11" s="42" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="2:2" customHeight="1">
+      <x:c r="B12" s="40" t="s">
+        <x:v>761</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="2:2" customHeight="1">
+      <x:c r="B13" s="40" t="s">
+        <x:v>482</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="2:2" customHeight="1">
+      <x:c r="B14" s="40" t="s">
+        <x:v>273</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
 
@@ -6436,54 +7274,54 @@
   <x:sheetData>
     <x:row r="5" spans="5:5">
       <x:c r="E5" t="s">
-        <x:v>27</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="5:5">
       <x:c r="E6" t="s">
-        <x:v>344</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="5:5">
       <x:c r="E7" t="s">
-        <x:v>613</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="5:5">
       <x:c r="E8" t="s">
-        <x:v>231</x:v>
+        <x:v>368</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="4:5">
       <x:c r="D9" s="3"/>
       <x:c r="E9" t="s">
-        <x:v>316</x:v>
+        <x:v>536</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:5">
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
       <x:c r="E10" t="s">
-        <x:v>647</x:v>
+        <x:v>681</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:5">
       <x:c r="C11" s="2"/>
       <x:c r="D11" s="4"/>
       <x:c r="E11" t="s">
-        <x:v>618</x:v>
+        <x:v>294</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="3:5">
       <x:c r="C12" s="1"/>
       <x:c r="E12" t="s">
-        <x:v>617</x:v>
+        <x:v>297</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="3:5">
       <x:c r="C13" s="1"/>
       <x:c r="E13" s="17" t="s">
-        <x:v>7</x:v>
+        <x:v>255</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="3:3">
@@ -6550,35 +7388,35 @@
   <x:sheetData>
     <x:row r="5" spans="5:5">
       <x:c r="E5" t="s">
-        <x:v>385</x:v>
+        <x:v>563</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="5:5">
       <x:c r="E6" t="s">
-        <x:v>304</x:v>
+        <x:v>537</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="5:5">
       <x:c r="E7" t="s">
-        <x:v>299</x:v>
+        <x:v>534</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="5:5">
       <x:c r="E8" t="s">
-        <x:v>403</x:v>
+        <x:v>578</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="4:5">
       <x:c r="D9" s="3"/>
       <x:c r="E9" t="s">
-        <x:v>470</x:v>
+        <x:v>448</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:5">
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
       <x:c r="E10" t="s">
-        <x:v>309</x:v>
+        <x:v>532</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:4">
@@ -6594,122 +7432,122 @@
     <x:row r="14" spans="3:10" ht="27.10000000000000142109">
       <x:c r="C14" s="1"/>
       <x:c r="E14" s="8" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F14" s="8" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G14" s="8" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="H14" s="8" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="I14" s="8" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="J14" s="8" t="s">
         <x:v>531</x:v>
-      </x:c>
-      <x:c r="F14" s="8" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="G14" s="8" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="H14" s="8" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="I14" s="8" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J14" s="8" t="s">
-        <x:v>302</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="5:10" ht="27.10000000000000142109">
       <x:c r="E15" s="8" t="s">
-        <x:v>100</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="F15" s="8" t="s">
-        <x:v>307</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="G15" s="8" t="s">
-        <x:v>377</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="H15" s="8" t="s">
-        <x:v>526</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="I15" s="8" t="s">
-        <x:v>393</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="J15" s="8" t="s">
-        <x:v>235</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="5:10" ht="27.10000000000000142109">
       <x:c r="E16" s="8" t="s">
-        <x:v>146</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="F16" s="8" t="s">
-        <x:v>33</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G16" s="8" t="s">
-        <x:v>384</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="H16" s="8" t="s">
-        <x:v>142</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="I16" s="8" t="s">
-        <x:v>402</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="J16" s="8" t="s">
-        <x:v>193</x:v>
+        <x:v>506</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="5:10" ht="27.10000000000000142109">
       <x:c r="E17" s="8" t="s">
-        <x:v>120</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="F17" s="8" t="s">
-        <x:v>567</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="G17" s="8" t="s">
-        <x:v>640</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="H17" s="8" t="s">
-        <x:v>119</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="I17" s="8" t="s">
-        <x:v>480</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="J17" s="9" t="s">
-        <x:v>241</x:v>
+        <x:v>376</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="5:10" ht="27.10000000000000142109">
       <x:c r="E18" s="8" t="s">
-        <x:v>110</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="F18" s="8" t="s">
-        <x:v>483</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="G18" s="8" t="s">
-        <x:v>30</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="H18" s="8" t="s">
-        <x:v>489</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="I18" s="8" t="s">
-        <x:v>25</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="J18" s="8" t="s">
-        <x:v>51</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="5:10" ht="53.39999999999999857891">
       <x:c r="E19" s="8" t="s">
-        <x:v>143</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="F19" s="8" t="s">
-        <x:v>576</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="G19" s="8" t="s">
-        <x:v>639</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="H19" s="8" t="s">
-        <x:v>117</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="I19" s="8" t="s">
-        <x:v>478</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="J19" s="9" t="s">
-        <x:v>326</x:v>
+        <x:v>493</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="4:4">
@@ -6727,12 +7565,12 @@
     <x:row r="38" spans="4:6">
       <x:c r="D38" s="2"/>
       <x:c r="F38" t="s">
-        <x:v>511</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="6:6">
       <x:c r="F39" t="s">
-        <x:v>511</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="5:5">
@@ -6767,83 +7605,83 @@
   <x:sheetData>
     <x:row r="11" spans="4:4">
       <x:c r="D11" t="s">
-        <x:v>536</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="4:4">
       <x:c r="D12" t="s">
-        <x:v>473</x:v>
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="4:4">
       <x:c r="D13" t="s">
-        <x:v>684</x:v>
+        <x:v>728</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="3:4">
       <x:c r="C14" t="s">
-        <x:v>517</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D14" t="s">
-        <x:v>259</x:v>
+        <x:v>394</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="4:4">
       <x:c r="D15" t="s">
-        <x:v>686</x:v>
+        <x:v>615</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="4:4">
       <x:c r="D16" t="s">
-        <x:v>685</x:v>
+        <x:v>729</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="4:4">
       <x:c r="D17" s="2" t="s">
-        <x:v>148</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="4:4">
       <x:c r="D19" t="s">
-        <x:v>487</x:v>
+        <x:v>464</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="4:4">
       <x:c r="D20" s="2" t="s">
-        <x:v>327</x:v>
+        <x:v>483</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="4:4">
       <x:c r="D21" s="2" t="s">
-        <x:v>631</x:v>
+        <x:v>291</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="4:4">
       <x:c r="D23" t="s">
-        <x:v>387</x:v>
+        <x:v>555</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="4:4">
       <x:c r="D24" t="s">
-        <x:v>58</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="4:4">
       <x:c r="D25" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="4:9">
       <x:c r="D26" s="2" t="s">
-        <x:v>232</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="I26" t="s">
-        <x:v>511</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="4:4">
       <x:c r="D27" s="2" t="s">
-        <x:v>250</x:v>
+        <x:v>388</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6865,299 +7703,299 @@
   <x:sheetData>
     <x:row r="9" spans="3:3" ht="20.64999999999999857891">
       <x:c r="C9" s="10" t="s">
-        <x:v>109</x:v>
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:3">
       <x:c r="C10" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>330</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:3">
       <x:c r="C11" s="2" t="s">
-        <x:v>295</x:v>
+        <x:v>630</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="3:3">
       <x:c r="C12" s="2" t="s">
-        <x:v>156</x:v>
+        <x:v>624</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="3:3">
       <x:c r="C14" t="s">
-        <x:v>229</x:v>
+        <x:v>374</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="3:3">
       <x:c r="C15" s="2" t="s">
-        <x:v>237</x:v>
+        <x:v>361</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="3:3">
       <x:c r="C16" s="2" t="s">
-        <x:v>322</x:v>
+        <x:v>570</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="3:3">
       <x:c r="C17" s="2" t="s">
-        <x:v>375</x:v>
+        <x:v>553</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="3:3">
       <x:c r="C18" s="2" t="s">
-        <x:v>225</x:v>
+        <x:v>367</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="3:3">
       <x:c r="C20" s="11" t="s">
-        <x:v>491</x:v>
+        <x:v>462</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="3:3">
       <x:c r="C21" t="s">
-        <x:v>308</x:v>
+        <x:v>528</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="3:3">
       <x:c r="C22" t="s">
-        <x:v>401</x:v>
+        <x:v>595</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="3:3">
       <x:c r="C23" t="s">
-        <x:v>318</x:v>
+        <x:v>523</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="3:3">
       <x:c r="C26" s="11" t="s">
-        <x:v>472</x:v>
+        <x:v>444</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="3:3">
       <x:c r="C27" t="s">
-        <x:v>105</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="3:3">
       <x:c r="C28" t="s">
-        <x:v>398</x:v>
+        <x:v>574</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="3:3">
       <x:c r="C29" t="s">
-        <x:v>474</x:v>
+        <x:v>447</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="3:3">
       <x:c r="C30" t="s">
-        <x:v>495</x:v>
+        <x:v>461</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="3:3">
       <x:c r="C33" s="11" t="s">
-        <x:v>469</x:v>
+        <x:v>450</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="3:3">
       <x:c r="C34" t="s">
-        <x:v>128</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="3:3">
       <x:c r="C35" t="s">
-        <x:v>369</x:v>
+        <x:v>541</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="3:3">
       <x:c r="C36" t="s">
-        <x:v>391</x:v>
+        <x:v>557</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="3:3">
       <x:c r="C37" t="s">
-        <x:v>303</x:v>
+        <x:v>538</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="3:3">
       <x:c r="C39" t="s">
-        <x:v>619</x:v>
+        <x:v>298</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="3:3">
       <x:c r="C42" s="11" t="s">
-        <x:v>481</x:v>
+        <x:v>463</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="3:3">
       <x:c r="C43" t="s">
-        <x:v>122</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="3:3">
       <x:c r="C44" t="s">
-        <x:v>319</x:v>
+        <x:v>521</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="3:3">
       <x:c r="C45" t="s">
-        <x:v>16</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="3:3">
       <x:c r="C46" t="s">
-        <x:v>15</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="3:3">
       <x:c r="C47" t="s">
-        <x:v>477</x:v>
+        <x:v>441</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="3:3">
       <x:c r="C48" t="s">
-        <x:v>321</x:v>
+        <x:v>559</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="3:3">
       <x:c r="C50" s="11" t="s">
-        <x:v>490</x:v>
+        <x:v>465</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="3:3">
       <x:c r="C51" t="s">
-        <x:v>306</x:v>
+        <x:v>525</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="3:8">
       <x:c r="C52" t="s">
-        <x:v>380</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="H52" s="2" t="s">
-        <x:v>276</x:v>
+        <x:v>307</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="3:3">
       <x:c r="C53" s="2" t="s">
-        <x:v>305</x:v>
+        <x:v>515</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="3:3">
       <x:c r="C54" s="2" t="s">
-        <x:v>577</x:v>
+        <x:v>646</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="3:3">
       <x:c r="C57" s="11" t="s">
-        <x:v>476</x:v>
+        <x:v>445</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="3:3">
       <x:c r="C58" t="s">
-        <x:v>300</x:v>
+        <x:v>526</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="3:3">
       <x:c r="C59" s="2" t="s">
-        <x:v>642</x:v>
+        <x:v>702</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="3:3">
       <x:c r="C60" s="2" t="s">
-        <x:v>330</x:v>
+        <x:v>484</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="3:3">
       <x:c r="C61" s="2" t="s">
-        <x:v>227</x:v>
+        <x:v>365</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="3:3">
       <x:c r="C64" s="11" t="s">
-        <x:v>468</x:v>
+        <x:v>442</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="3:3">
       <x:c r="C65" t="s">
-        <x:v>368</x:v>
+        <x:v>551</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="3:3">
       <x:c r="C66" s="2" t="s">
-        <x:v>317</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="3:3">
       <x:c r="C67" s="2" t="s">
-        <x:v>652</x:v>
+        <x:v>684</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="3:3">
       <x:c r="C68" s="2" t="s">
-        <x:v>323</x:v>
+        <x:v>539</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="3:6">
-      <x:c r="C72" s="40" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D72" s="40"/>
+      <x:c r="C72" s="43" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D72" s="43"/>
       <x:c r="E72" s="12"/>
       <x:c r="F72" s="12"/>
     </x:row>
     <x:row r="73" spans="3:6">
       <x:c r="C73" s="14" t="s">
-        <x:v>512</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D73" s="13" t="s">
-        <x:v>496</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="E73" s="13" t="s">
-        <x:v>140</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="F73" s="13" t="s">
-        <x:v>118</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="3:6">
       <x:c r="C74" s="14" t="s">
-        <x:v>111</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="D74" s="12" t="s">
-        <x:v>493</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="E74" s="12" t="s">
-        <x:v>138</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="F74" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="3:6">
       <x:c r="C75" s="14" t="s">
-        <x:v>472</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="D75" s="12" t="s">
-        <x:v>463</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="E75" s="12" t="s">
-        <x:v>539</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F75" s="12" t="s">
-        <x:v>543</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="3:6">
       <x:c r="C76" s="14" t="s">
-        <x:v>469</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="D76" s="12" t="s">
-        <x:v>126</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="E76" s="12" t="s">
-        <x:v>107</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="F76" s="12" t="s">
-        <x:v>132</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7184,165 +8022,165 @@
   <x:sheetData>
     <x:row r="3" spans="3:3" ht="20.64999999999999857891">
       <x:c r="C3" s="19" t="s">
-        <x:v>121</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="3:3" ht="22.05000000000000071054">
       <x:c r="C6" t="s">
-        <x:v>251</x:v>
+        <x:v>391</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="3:9">
       <x:c r="C7" t="s">
-        <x:v>364</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E7" s="22" t="s">
-        <x:v>636</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="G7" s="18" t="s">
-        <x:v>561</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="I7" s="18" t="s">
-        <x:v>584</x:v>
+        <x:v>668</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="3:9">
       <x:c r="C8" s="20" t="s">
-        <x:v>378</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="E8" s="21" t="s">
-        <x:v>404</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="G8" s="21" t="s">
-        <x:v>53</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="I8" s="21" t="s">
-        <x:v>485</x:v>
+        <x:v>455</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="3:9">
       <x:c r="C9" s="20" t="s">
-        <x:v>24</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E9" s="21" t="s">
-        <x:v>659</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="G9" s="21" t="s">
-        <x:v>645</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="I9" s="21" t="s">
-        <x:v>657</x:v>
+        <x:v>690</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="3:9">
       <x:c r="C10" s="20" t="s">
-        <x:v>26</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E10" s="21" t="s">
-        <x:v>621</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="G10" s="21" t="s">
-        <x:v>32</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="I10" s="21" t="s">
-        <x:v>408</x:v>
+        <x:v>599</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="3:9">
       <x:c r="C11" s="20" t="s">
-        <x:v>115</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="E11" s="21" t="s">
-        <x:v>644</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="G11" s="21" t="s">
-        <x:v>323</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="I11" s="18"/>
     </x:row>
     <x:row r="12" spans="3:7">
       <x:c r="C12" s="20" t="s">
-        <x:v>244</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="G12" s="21" t="s">
-        <x:v>112</x:v>
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="3:3" ht="22.05000000000000071054">
       <x:c r="C15" s="24" t="s">
-        <x:v>412</x:v>
+        <x:v>594</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="3:3">
       <x:c r="C16" s="21" t="s">
-        <x:v>571</x:v>
+        <x:v>643</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="3:5">
       <x:c r="C17" t="s">
-        <x:v>18</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E17" s="23" t="s">
-        <x:v>39</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="3:5">
       <x:c r="C18" s="20" t="s">
-        <x:v>195</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="E18" s="20" t="s">
-        <x:v>245</x:v>
+        <x:v>379</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="3:5">
       <x:c r="C19" s="20" t="s">
-        <x:v>575</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="E19" s="20" t="s">
-        <x:v>234</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="3:5">
       <x:c r="C20" s="20" t="s">
-        <x:v>651</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E20" s="20" t="s">
-        <x:v>596</x:v>
+        <x:v>670</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="3:3">
       <x:c r="C21" s="20" t="s">
-        <x:v>392</x:v>
+        <x:v>567</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="3:3">
       <x:c r="C22" s="20" t="s">
-        <x:v>394</x:v>
+        <x:v>562</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="3:3" ht="22.05000000000000071054">
       <x:c r="C26" s="25" t="s">
-        <x:v>370</x:v>
+        <x:v>565</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="3:3">
       <x:c r="C27" s="20" t="s">
-        <x:v>270</x:v>
+        <x:v>315</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="3:3">
       <x:c r="C28" s="20" t="s">
-        <x:v>255</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="3:3">
       <x:c r="C30" s="18" t="s">
-        <x:v>240</x:v>
+        <x:v>364</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="3:3">
       <x:c r="C31" t="s">
-        <x:v>256</x:v>
+        <x:v>392</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7363,158 +8201,158 @@
   <x:sheetData>
     <x:row r="4" spans="21:21" ht="22.05000000000000071054">
       <x:c r="U4" s="26" t="s">
-        <x:v>488</x:v>
+        <x:v>458</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="21:21">
       <x:c r="U6" s="20" t="s">
-        <x:v>494</x:v>
+        <x:v>459</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="21:21">
       <x:c r="U7" s="20" t="s">
-        <x:v>430</x:v>
+        <x:v>428</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="21:21">
       <x:c r="U8" s="20" t="s">
-        <x:v>44</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="21:21">
       <x:c r="U9" s="20" t="s">
-        <x:v>381</x:v>
+        <x:v>549</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="21:21">
       <x:c r="U10" s="20" t="s">
-        <x:v>188</x:v>
+        <x:v>512</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="21:21">
       <x:c r="U11" s="20" t="s">
-        <x:v>254</x:v>
+        <x:v>381</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="21:21">
       <x:c r="U12" s="20" t="s">
-        <x:v>264</x:v>
+        <x:v>395</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="21:21">
       <x:c r="U14" s="21" t="s">
-        <x:v>486</x:v>
+        <x:v>467</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="22:22">
       <x:c r="V15" t="s">
-        <x:v>324</x:v>
+        <x:v>496</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="22:22">
       <x:c r="V16" t="s">
-        <x:v>616</x:v>
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="21:21">
       <x:c r="U17" s="21" t="s">
-        <x:v>374</x:v>
+        <x:v>547</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="22:22">
       <x:c r="V18" t="s">
-        <x:v>629</x:v>
+        <x:v>292</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="21:21">
       <x:c r="U19" s="20" t="s">
-        <x:v>492</x:v>
+        <x:v>456</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="22:22">
       <x:c r="V20" t="s">
-        <x:v>615</x:v>
+        <x:v>299</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="21:21">
       <x:c r="U23" s="20" t="s">
-        <x:v>3</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="21:23">
       <x:c r="U26" t="s">
-        <x:v>519</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="V26" t="s">
-        <x:v>423</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="W26" t="s">
-        <x:v>79</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="21:23">
       <x:c r="U27" t="s">
-        <x:v>557</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="V27" t="s">
-        <x:v>76</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="W27" t="s">
-        <x:v>89</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="21:23">
       <x:c r="U28" t="s">
-        <x:v>552</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="V28" t="s">
-        <x:v>328</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="W28" t="s">
-        <x:v>83</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="21:23">
       <x:c r="U29" t="s">
-        <x:v>556</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="V29" t="s">
-        <x:v>677</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="W29" t="s">
-        <x:v>82</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="21:22">
       <x:c r="U30" t="s">
-        <x:v>525</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="V30" t="s">
-        <x:v>65</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="21:22">
       <x:c r="U31" t="s">
-        <x:v>516</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="V31" t="s">
-        <x:v>587</x:v>
+        <x:v>663</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="21:22">
       <x:c r="U32" t="s">
-        <x:v>90</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="V32" t="s">
-        <x:v>422</x:v>
+        <x:v>591</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="21:22">
       <x:c r="U33" t="s">
-        <x:v>515</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="V33" t="s">
-        <x:v>342</x:v>
+        <x:v>508</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
